--- a/進捗管理表/進捗管理表_志賀.xlsx
+++ b/進捗管理表/進捗管理表_志賀.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-04\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-04\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{582C8596-5BE4-4D53-B34A-C49648D6736F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A1A28AA-6D52-4CAC-9ADF-5A6A4C5D2EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="42">
   <si>
     <t>■進捗管理表</t>
   </si>
@@ -274,6 +274,8 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
@@ -354,7 +356,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="70">
+  <borders count="67">
     <border>
       <left/>
       <right/>
@@ -1172,36 +1174,6 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="double">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="dotted">
-        <color indexed="64"/>
-      </top>
-      <bottom style="dotted">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="dotted">
-        <color indexed="64"/>
-      </top>
-      <bottom style="dotted">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -1224,21 +1196,6 @@
         <color indexed="64"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="dotted">
-        <color indexed="64"/>
-      </top>
-      <bottom style="dotted">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1275,7 +1232,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1513,21 +1470,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1537,29 +1479,35 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1630,7 +1578,13 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1848,7 +1802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AL1000"/>
+  <dimension ref="A1:AL1004"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.7109375" customWidth="1"/>
@@ -1942,142 +1896,142 @@
       <c r="AL2" s="2"/>
     </row>
     <row r="3" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A3" s="96" t="s">
+      <c r="A3" s="93" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="98" t="s">
+      <c r="B3" s="95" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="109">
+      <c r="G3" s="106">
         <v>45705</v>
       </c>
-      <c r="H3" s="110"/>
-      <c r="I3" s="110"/>
-      <c r="J3" s="110"/>
-      <c r="K3" s="110"/>
-      <c r="L3" s="110"/>
-      <c r="M3" s="110"/>
-      <c r="N3" s="110"/>
-      <c r="O3" s="110"/>
-      <c r="P3" s="110"/>
-      <c r="Q3" s="110"/>
-      <c r="R3" s="110"/>
-      <c r="S3" s="110"/>
-      <c r="T3" s="110"/>
-      <c r="U3" s="110"/>
-      <c r="V3" s="110"/>
-      <c r="W3" s="110"/>
-      <c r="X3" s="110"/>
-      <c r="Y3" s="110"/>
-      <c r="Z3" s="110"/>
-      <c r="AA3" s="110"/>
-      <c r="AB3" s="110"/>
-      <c r="AC3" s="110"/>
-      <c r="AD3" s="110"/>
-      <c r="AE3" s="110"/>
-      <c r="AF3" s="110"/>
-      <c r="AG3" s="110"/>
-      <c r="AH3" s="110"/>
-      <c r="AI3" s="110"/>
-      <c r="AJ3" s="110"/>
-      <c r="AK3" s="110"/>
-      <c r="AL3" s="111"/>
+      <c r="H3" s="107"/>
+      <c r="I3" s="107"/>
+      <c r="J3" s="107"/>
+      <c r="K3" s="107"/>
+      <c r="L3" s="107"/>
+      <c r="M3" s="107"/>
+      <c r="N3" s="107"/>
+      <c r="O3" s="107"/>
+      <c r="P3" s="107"/>
+      <c r="Q3" s="107"/>
+      <c r="R3" s="107"/>
+      <c r="S3" s="107"/>
+      <c r="T3" s="107"/>
+      <c r="U3" s="107"/>
+      <c r="V3" s="107"/>
+      <c r="W3" s="107"/>
+      <c r="X3" s="107"/>
+      <c r="Y3" s="107"/>
+      <c r="Z3" s="107"/>
+      <c r="AA3" s="107"/>
+      <c r="AB3" s="107"/>
+      <c r="AC3" s="107"/>
+      <c r="AD3" s="107"/>
+      <c r="AE3" s="107"/>
+      <c r="AF3" s="107"/>
+      <c r="AG3" s="107"/>
+      <c r="AH3" s="107"/>
+      <c r="AI3" s="107"/>
+      <c r="AJ3" s="107"/>
+      <c r="AK3" s="107"/>
+      <c r="AL3" s="108"/>
     </row>
     <row r="4" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A4" s="97"/>
-      <c r="B4" s="97"/>
-      <c r="C4" s="99" t="s">
+      <c r="A4" s="94"/>
+      <c r="B4" s="94"/>
+      <c r="C4" s="96" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="96" t="s">
+      <c r="D4" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="103" t="s">
+      <c r="E4" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="106" t="s">
+      <c r="F4" s="103" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="112"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="113"/>
-      <c r="L4" s="113"/>
-      <c r="M4" s="113"/>
-      <c r="N4" s="113"/>
-      <c r="O4" s="113"/>
-      <c r="P4" s="113"/>
-      <c r="Q4" s="113"/>
-      <c r="R4" s="113"/>
-      <c r="S4" s="113"/>
-      <c r="T4" s="113"/>
-      <c r="U4" s="113"/>
-      <c r="V4" s="113"/>
-      <c r="W4" s="113"/>
-      <c r="X4" s="113"/>
-      <c r="Y4" s="113"/>
-      <c r="Z4" s="113"/>
-      <c r="AA4" s="113"/>
-      <c r="AB4" s="113"/>
-      <c r="AC4" s="113"/>
-      <c r="AD4" s="113"/>
-      <c r="AE4" s="113"/>
-      <c r="AF4" s="113"/>
-      <c r="AG4" s="113"/>
-      <c r="AH4" s="113"/>
-      <c r="AI4" s="113"/>
-      <c r="AJ4" s="113"/>
-      <c r="AK4" s="113"/>
-      <c r="AL4" s="114"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110"/>
+      <c r="M4" s="110"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="110"/>
+      <c r="P4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="110"/>
+      <c r="S4" s="110"/>
+      <c r="T4" s="110"/>
+      <c r="U4" s="110"/>
+      <c r="V4" s="110"/>
+      <c r="W4" s="110"/>
+      <c r="X4" s="110"/>
+      <c r="Y4" s="110"/>
+      <c r="Z4" s="110"/>
+      <c r="AA4" s="110"/>
+      <c r="AB4" s="110"/>
+      <c r="AC4" s="110"/>
+      <c r="AD4" s="110"/>
+      <c r="AE4" s="110"/>
+      <c r="AF4" s="110"/>
+      <c r="AG4" s="110"/>
+      <c r="AH4" s="110"/>
+      <c r="AI4" s="110"/>
+      <c r="AJ4" s="110"/>
+      <c r="AK4" s="110"/>
+      <c r="AL4" s="111"/>
     </row>
     <row r="5" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A5" s="97"/>
-      <c r="B5" s="97"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
-      <c r="E5" s="97"/>
-      <c r="F5" s="107"/>
-      <c r="G5" s="104">
+      <c r="A5" s="94"/>
+      <c r="B5" s="94"/>
+      <c r="C5" s="94"/>
+      <c r="D5" s="94"/>
+      <c r="E5" s="94"/>
+      <c r="F5" s="104"/>
+      <c r="G5" s="101">
         <v>17</v>
       </c>
-      <c r="H5" s="105"/>
-      <c r="I5" s="100">
+      <c r="H5" s="102"/>
+      <c r="I5" s="97">
         <v>18</v>
       </c>
-      <c r="J5" s="101"/>
-      <c r="K5" s="100">
+      <c r="J5" s="98"/>
+      <c r="K5" s="97">
         <v>19</v>
       </c>
-      <c r="L5" s="101"/>
-      <c r="M5" s="100">
+      <c r="L5" s="98"/>
+      <c r="M5" s="97">
         <v>20</v>
       </c>
-      <c r="N5" s="101"/>
-      <c r="O5" s="100">
+      <c r="N5" s="98"/>
+      <c r="O5" s="97">
         <v>21</v>
       </c>
-      <c r="P5" s="101"/>
-      <c r="Q5" s="100">
+      <c r="P5" s="98"/>
+      <c r="Q5" s="97">
         <v>25</v>
       </c>
-      <c r="R5" s="102"/>
-      <c r="S5" s="104">
+      <c r="R5" s="99"/>
+      <c r="S5" s="101">
         <v>26</v>
       </c>
-      <c r="T5" s="105"/>
-      <c r="U5" s="100">
+      <c r="T5" s="102"/>
+      <c r="U5" s="97">
         <v>27</v>
       </c>
-      <c r="V5" s="105"/>
-      <c r="W5" s="100">
+      <c r="V5" s="102"/>
+      <c r="W5" s="97">
         <v>28</v>
       </c>
-      <c r="X5" s="105"/>
+      <c r="X5" s="102"/>
       <c r="Y5" s="10"/>
       <c r="Z5" s="10"/>
       <c r="AA5" s="10"/>
@@ -2094,48 +2048,48 @@
       <c r="AL5" s="11"/>
     </row>
     <row r="6" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A6" s="93"/>
-      <c r="B6" s="93"/>
-      <c r="C6" s="93"/>
-      <c r="D6" s="93"/>
-      <c r="E6" s="93"/>
-      <c r="F6" s="108"/>
-      <c r="G6" s="104" t="s">
+      <c r="A6" s="90"/>
+      <c r="B6" s="90"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="90"/>
+      <c r="F6" s="105"/>
+      <c r="G6" s="101" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="105"/>
-      <c r="I6" s="115" t="s">
+      <c r="H6" s="102"/>
+      <c r="I6" s="112" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="105"/>
-      <c r="K6" s="100" t="s">
+      <c r="J6" s="102"/>
+      <c r="K6" s="97" t="s">
         <v>9</v>
       </c>
-      <c r="L6" s="105"/>
-      <c r="M6" s="100" t="s">
+      <c r="L6" s="102"/>
+      <c r="M6" s="97" t="s">
         <v>10</v>
       </c>
-      <c r="N6" s="105"/>
-      <c r="O6" s="100" t="s">
+      <c r="N6" s="102"/>
+      <c r="O6" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="P6" s="105"/>
-      <c r="Q6" s="100" t="s">
+      <c r="P6" s="102"/>
+      <c r="Q6" s="97" t="s">
         <v>19</v>
       </c>
-      <c r="R6" s="105"/>
-      <c r="S6" s="116" t="s">
+      <c r="R6" s="102"/>
+      <c r="S6" s="113" t="s">
         <v>20</v>
       </c>
-      <c r="T6" s="105"/>
-      <c r="U6" s="117" t="s">
+      <c r="T6" s="102"/>
+      <c r="U6" s="114" t="s">
         <v>21</v>
       </c>
-      <c r="V6" s="105"/>
-      <c r="W6" s="117" t="s">
+      <c r="V6" s="102"/>
+      <c r="W6" s="114" t="s">
         <v>22</v>
       </c>
-      <c r="X6" s="105"/>
+      <c r="X6" s="102"/>
       <c r="Y6" s="10"/>
       <c r="Z6" s="10"/>
       <c r="AA6" s="10"/>
@@ -2236,19 +2190,19 @@
       <c r="AL8" s="20"/>
     </row>
     <row r="9" spans="1:38" ht="12" customHeight="1">
-      <c r="A9" s="94">
+      <c r="A9" s="89">
         <v>1</v>
       </c>
-      <c r="B9" s="92" t="s">
+      <c r="B9" s="91" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="92">
+      <c r="C9" s="91">
         <v>2</v>
       </c>
-      <c r="D9" s="92" t="s">
+      <c r="D9" s="91" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="92"/>
+      <c r="E9" s="91"/>
       <c r="F9" s="21" t="s">
         <v>13</v>
       </c>
@@ -2286,16 +2240,16 @@
       <c r="AL9" s="27"/>
     </row>
     <row r="10" spans="1:38" ht="12" customHeight="1">
-      <c r="A10" s="93"/>
-      <c r="B10" s="93"/>
-      <c r="C10" s="93"/>
-      <c r="D10" s="93"/>
-      <c r="E10" s="93"/>
+      <c r="A10" s="90"/>
+      <c r="B10" s="90"/>
+      <c r="C10" s="90"/>
+      <c r="D10" s="90"/>
+      <c r="E10" s="90"/>
       <c r="F10" s="28" t="s">
         <v>14</v>
       </c>
       <c r="G10" s="29"/>
-      <c r="H10" s="118"/>
+      <c r="H10" s="86"/>
       <c r="I10" s="30"/>
       <c r="J10" s="30"/>
       <c r="K10" s="30"/>
@@ -2328,19 +2282,19 @@
       <c r="AL10" s="32"/>
     </row>
     <row r="11" spans="1:38" ht="12" customHeight="1">
-      <c r="A11" s="94">
+      <c r="A11" s="89">
         <v>2</v>
       </c>
-      <c r="B11" s="92" t="s">
+      <c r="B11" s="91" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="92">
+      <c r="C11" s="91">
         <v>2</v>
       </c>
-      <c r="D11" s="92" t="s">
+      <c r="D11" s="91" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="92"/>
+      <c r="E11" s="91"/>
       <c r="F11" s="33" t="s">
         <v>13</v>
       </c>
@@ -2378,11 +2332,11 @@
       <c r="AL11" s="10"/>
     </row>
     <row r="12" spans="1:38" ht="12" customHeight="1">
-      <c r="A12" s="93"/>
-      <c r="B12" s="93"/>
-      <c r="C12" s="93"/>
-      <c r="D12" s="93"/>
-      <c r="E12" s="93"/>
+      <c r="A12" s="90"/>
+      <c r="B12" s="90"/>
+      <c r="C12" s="90"/>
+      <c r="D12" s="90"/>
+      <c r="E12" s="90"/>
       <c r="F12" s="37" t="s">
         <v>14</v>
       </c>
@@ -2390,8 +2344,8 @@
       <c r="H12" s="39"/>
       <c r="I12" s="39"/>
       <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="39"/>
+      <c r="K12" s="115"/>
+      <c r="L12" s="115"/>
       <c r="M12" s="39"/>
       <c r="N12" s="39"/>
       <c r="O12" s="39"/>
@@ -2420,19 +2374,19 @@
       <c r="AL12" s="41"/>
     </row>
     <row r="13" spans="1:38" ht="12" customHeight="1">
-      <c r="A13" s="94">
+      <c r="A13" s="89">
         <v>3</v>
       </c>
-      <c r="B13" s="92" t="s">
+      <c r="B13" s="91" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="92">
+      <c r="C13" s="91">
         <v>1</v>
       </c>
-      <c r="D13" s="92" t="s">
+      <c r="D13" s="91" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="92"/>
+      <c r="E13" s="91"/>
       <c r="F13" s="21" t="s">
         <v>13</v>
       </c>
@@ -2470,11 +2424,11 @@
       <c r="AL13" s="27"/>
     </row>
     <row r="14" spans="1:38" ht="12" customHeight="1">
-      <c r="A14" s="93"/>
-      <c r="B14" s="93"/>
-      <c r="C14" s="93"/>
-      <c r="D14" s="93"/>
-      <c r="E14" s="93"/>
+      <c r="A14" s="90"/>
+      <c r="B14" s="90"/>
+      <c r="C14" s="90"/>
+      <c r="D14" s="90"/>
+      <c r="E14" s="90"/>
       <c r="F14" s="42" t="s">
         <v>14</v>
       </c>
@@ -2482,8 +2436,8 @@
       <c r="H14" s="44"/>
       <c r="I14" s="44"/>
       <c r="J14" s="44"/>
-      <c r="K14" s="44"/>
-      <c r="L14" s="44"/>
+      <c r="K14" s="116"/>
+      <c r="L14" s="116"/>
       <c r="M14" s="44"/>
       <c r="N14" s="44"/>
       <c r="O14" s="44"/>
@@ -2512,13 +2466,13 @@
       <c r="AL14" s="32"/>
     </row>
     <row r="15" spans="1:38" ht="12" customHeight="1">
-      <c r="A15" s="94">
+      <c r="A15" s="89">
         <v>4</v>
       </c>
-      <c r="B15" s="92"/>
-      <c r="C15" s="92"/>
-      <c r="D15" s="92"/>
-      <c r="E15" s="92"/>
+      <c r="B15" s="91"/>
+      <c r="C15" s="91"/>
+      <c r="D15" s="91"/>
+      <c r="E15" s="91"/>
       <c r="F15" s="33" t="s">
         <v>13</v>
       </c>
@@ -2556,11 +2510,11 @@
       <c r="AL15" s="10"/>
     </row>
     <row r="16" spans="1:38" ht="12" customHeight="1">
-      <c r="A16" s="93"/>
-      <c r="B16" s="93"/>
-      <c r="C16" s="93"/>
-      <c r="D16" s="93"/>
-      <c r="E16" s="93"/>
+      <c r="A16" s="90"/>
+      <c r="B16" s="90"/>
+      <c r="C16" s="90"/>
+      <c r="D16" s="90"/>
+      <c r="E16" s="90"/>
       <c r="F16" s="37" t="s">
         <v>14</v>
       </c>
@@ -2598,17 +2552,17 @@
       <c r="AL16" s="41"/>
     </row>
     <row r="17" spans="1:38" ht="12" customHeight="1">
-      <c r="A17" s="94">
+      <c r="A17" s="89">
         <v>7</v>
       </c>
-      <c r="B17" s="92" t="s">
+      <c r="B17" s="91" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="92">
+      <c r="C17" s="91">
         <v>1</v>
       </c>
-      <c r="D17" s="92"/>
-      <c r="E17" s="92"/>
+      <c r="D17" s="91"/>
+      <c r="E17" s="91"/>
       <c r="F17" s="54" t="s">
         <v>13</v>
       </c>
@@ -2646,11 +2600,11 @@
       <c r="AL17" s="69"/>
     </row>
     <row r="18" spans="1:38" ht="12" customHeight="1">
-      <c r="A18" s="93"/>
-      <c r="B18" s="95"/>
-      <c r="C18" s="95"/>
-      <c r="D18" s="95"/>
-      <c r="E18" s="95"/>
+      <c r="A18" s="90"/>
+      <c r="B18" s="92"/>
+      <c r="C18" s="92"/>
+      <c r="D18" s="92"/>
+      <c r="E18" s="92"/>
       <c r="F18" s="37" t="s">
         <v>14</v>
       </c>
@@ -2659,7 +2613,7 @@
       <c r="I18" s="48"/>
       <c r="J18" s="48"/>
       <c r="K18" s="48"/>
-      <c r="L18" s="48"/>
+      <c r="L18" s="117"/>
       <c r="M18" s="48"/>
       <c r="N18" s="48"/>
       <c r="O18" s="48"/>
@@ -2688,13 +2642,13 @@
       <c r="AL18" s="12"/>
     </row>
     <row r="19" spans="1:38" ht="12" customHeight="1">
-      <c r="A19" s="94">
-        <v>8</v>
+      <c r="A19" s="89">
+        <v>4</v>
       </c>
-      <c r="B19" s="92"/>
-      <c r="C19" s="92"/>
-      <c r="D19" s="92"/>
-      <c r="E19" s="92"/>
+      <c r="B19" s="91"/>
+      <c r="C19" s="91"/>
+      <c r="D19" s="91"/>
+      <c r="E19" s="91"/>
       <c r="F19" s="54" t="s">
         <v>13</v>
       </c>
@@ -2731,192 +2685,186 @@
       <c r="AK19" s="69"/>
       <c r="AL19" s="69"/>
     </row>
-    <row r="20" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A20" s="93"/>
-      <c r="B20" s="95"/>
-      <c r="C20" s="95"/>
-      <c r="D20" s="95"/>
-      <c r="E20" s="95"/>
+    <row r="20" spans="1:38" ht="12" customHeight="1">
+      <c r="A20" s="90"/>
+      <c r="B20" s="90"/>
+      <c r="C20" s="90"/>
+      <c r="D20" s="90"/>
+      <c r="E20" s="90"/>
       <c r="F20" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="G20" s="47"/>
-      <c r="H20" s="48"/>
-      <c r="I20" s="48"/>
-      <c r="J20" s="48"/>
-      <c r="K20" s="48"/>
-      <c r="L20" s="48"/>
-      <c r="M20" s="48"/>
-      <c r="N20" s="48"/>
-      <c r="O20" s="48"/>
-      <c r="P20" s="48"/>
-      <c r="Q20" s="48"/>
-      <c r="R20" s="49"/>
-      <c r="S20" s="47"/>
-      <c r="T20" s="48"/>
-      <c r="U20" s="48"/>
-      <c r="V20" s="48"/>
-      <c r="W20" s="48"/>
-      <c r="X20" s="48"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="39"/>
+      <c r="L20" s="39"/>
+      <c r="M20" s="39"/>
+      <c r="N20" s="39"/>
+      <c r="O20" s="39"/>
+      <c r="P20" s="39"/>
+      <c r="Q20" s="39"/>
+      <c r="R20" s="40"/>
+      <c r="S20" s="38"/>
+      <c r="T20" s="39"/>
+      <c r="U20" s="39"/>
+      <c r="V20" s="39"/>
+      <c r="W20" s="39"/>
+      <c r="X20" s="39"/>
       <c r="Y20" s="10"/>
       <c r="Z20" s="10"/>
       <c r="AA20" s="10"/>
       <c r="AB20" s="10"/>
       <c r="AC20" s="10"/>
       <c r="AD20" s="10"/>
-      <c r="AE20" s="12"/>
-      <c r="AF20" s="12"/>
-      <c r="AG20" s="12"/>
-      <c r="AH20" s="12"/>
-      <c r="AI20" s="12"/>
-      <c r="AJ20" s="12"/>
-      <c r="AK20" s="12"/>
-      <c r="AL20" s="12"/>
+      <c r="AE20" s="41"/>
+      <c r="AF20" s="41"/>
+      <c r="AG20" s="41"/>
+      <c r="AH20" s="41"/>
+      <c r="AI20" s="41"/>
+      <c r="AJ20" s="41"/>
+      <c r="AK20" s="41"/>
+      <c r="AL20" s="41"/>
     </row>
     <row r="21" spans="1:38" ht="12" customHeight="1">
-      <c r="A21" s="94">
-        <v>9</v>
+      <c r="A21" s="89">
+        <v>4</v>
       </c>
-      <c r="B21" s="92" t="s">
-        <v>32</v>
+      <c r="B21" s="91" t="s">
+        <v>35</v>
       </c>
-      <c r="C21" s="92">
-        <v>2</v>
-      </c>
-      <c r="D21" s="92"/>
-      <c r="E21" s="92"/>
-      <c r="F21" s="21" t="s">
+      <c r="C21" s="91"/>
+      <c r="D21" s="91"/>
+      <c r="E21" s="91"/>
+      <c r="F21" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="G21" s="26"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="60"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="23"/>
-      <c r="M21" s="24"/>
-      <c r="N21" s="24"/>
-      <c r="O21" s="24"/>
-      <c r="P21" s="24"/>
-      <c r="Q21" s="24"/>
-      <c r="R21" s="25"/>
-      <c r="S21" s="26"/>
-      <c r="T21" s="24"/>
-      <c r="U21" s="24"/>
-      <c r="V21" s="24"/>
-      <c r="W21" s="24"/>
-      <c r="X21" s="24"/>
+      <c r="G21" s="55"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="57"/>
+      <c r="J21" s="57"/>
+      <c r="K21" s="57"/>
+      <c r="L21" s="68"/>
+      <c r="M21" s="56"/>
+      <c r="N21" s="56"/>
+      <c r="O21" s="56"/>
+      <c r="P21" s="56"/>
+      <c r="Q21" s="56"/>
+      <c r="R21" s="58"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="56"/>
+      <c r="U21" s="56"/>
+      <c r="V21" s="56"/>
+      <c r="W21" s="56"/>
+      <c r="X21" s="56"/>
       <c r="Y21" s="10"/>
       <c r="Z21" s="10"/>
       <c r="AA21" s="10"/>
       <c r="AB21" s="10"/>
       <c r="AC21" s="10"/>
       <c r="AD21" s="10"/>
-      <c r="AE21" s="27"/>
-      <c r="AF21" s="27"/>
-      <c r="AG21" s="27"/>
-      <c r="AH21" s="27"/>
-      <c r="AI21" s="27"/>
-      <c r="AJ21" s="27"/>
-      <c r="AK21" s="27"/>
-      <c r="AL21" s="27"/>
+      <c r="AE21" s="69"/>
+      <c r="AF21" s="69"/>
+      <c r="AG21" s="69"/>
+      <c r="AH21" s="69"/>
+      <c r="AI21" s="69"/>
+      <c r="AJ21" s="69"/>
+      <c r="AK21" s="69"/>
+      <c r="AL21" s="69"/>
     </row>
     <row r="22" spans="1:38" ht="12" customHeight="1">
-      <c r="A22" s="93"/>
-      <c r="B22" s="93"/>
-      <c r="C22" s="93"/>
-      <c r="D22" s="93"/>
-      <c r="E22" s="93"/>
-      <c r="F22" s="42" t="s">
+      <c r="A22" s="90"/>
+      <c r="B22" s="90"/>
+      <c r="C22" s="90"/>
+      <c r="D22" s="90"/>
+      <c r="E22" s="90"/>
+      <c r="F22" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="G22" s="29"/>
-      <c r="H22" s="30"/>
-      <c r="I22" s="30"/>
-      <c r="J22" s="30"/>
-      <c r="K22" s="30"/>
-      <c r="L22" s="30"/>
-      <c r="M22" s="30"/>
-      <c r="N22" s="30"/>
-      <c r="O22" s="30"/>
-      <c r="P22" s="30"/>
-      <c r="Q22" s="30"/>
-      <c r="R22" s="31"/>
-      <c r="S22" s="29"/>
-      <c r="T22" s="30"/>
-      <c r="U22" s="30"/>
-      <c r="V22" s="30"/>
-      <c r="W22" s="30"/>
-      <c r="X22" s="30"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="39"/>
+      <c r="L22" s="39"/>
+      <c r="M22" s="39"/>
+      <c r="N22" s="39"/>
+      <c r="O22" s="39"/>
+      <c r="P22" s="39"/>
+      <c r="Q22" s="39"/>
+      <c r="R22" s="40"/>
+      <c r="S22" s="38"/>
+      <c r="T22" s="39"/>
+      <c r="U22" s="39"/>
+      <c r="V22" s="39"/>
+      <c r="W22" s="39"/>
+      <c r="X22" s="39"/>
       <c r="Y22" s="10"/>
       <c r="Z22" s="10"/>
       <c r="AA22" s="10"/>
       <c r="AB22" s="10"/>
       <c r="AC22" s="10"/>
       <c r="AD22" s="10"/>
-      <c r="AE22" s="46"/>
-      <c r="AF22" s="46"/>
-      <c r="AG22" s="46"/>
-      <c r="AH22" s="46"/>
-      <c r="AI22" s="46"/>
-      <c r="AJ22" s="46"/>
-      <c r="AK22" s="46"/>
-      <c r="AL22" s="46"/>
+      <c r="AE22" s="41"/>
+      <c r="AF22" s="41"/>
+      <c r="AG22" s="41"/>
+      <c r="AH22" s="41"/>
+      <c r="AI22" s="41"/>
+      <c r="AJ22" s="41"/>
+      <c r="AK22" s="41"/>
+      <c r="AL22" s="41"/>
     </row>
     <row r="23" spans="1:38" ht="12" customHeight="1">
-      <c r="A23" s="94">
-        <v>10</v>
+      <c r="A23" s="89">
+        <v>8</v>
       </c>
-      <c r="B23" s="92" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" s="92">
-        <v>2</v>
-      </c>
-      <c r="D23" s="92"/>
-      <c r="E23" s="92"/>
-      <c r="F23" s="33" t="s">
+      <c r="B23" s="91"/>
+      <c r="C23" s="91"/>
+      <c r="D23" s="91"/>
+      <c r="E23" s="91"/>
+      <c r="F23" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="G23" s="36"/>
-      <c r="H23" s="34"/>
-      <c r="I23" s="59"/>
-      <c r="J23" s="50"/>
-      <c r="K23" s="60"/>
-      <c r="L23" s="23"/>
-      <c r="M23" s="34"/>
-      <c r="N23" s="34"/>
-      <c r="O23" s="34"/>
-      <c r="P23" s="34"/>
-      <c r="Q23" s="34"/>
-      <c r="R23" s="35"/>
-      <c r="S23" s="36"/>
-      <c r="T23" s="34"/>
-      <c r="U23" s="34"/>
-      <c r="V23" s="34"/>
-      <c r="W23" s="34"/>
-      <c r="X23" s="34"/>
+      <c r="G23" s="55"/>
+      <c r="H23" s="56"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="57"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="57"/>
+      <c r="M23" s="56"/>
+      <c r="N23" s="56"/>
+      <c r="O23" s="56"/>
+      <c r="P23" s="56"/>
+      <c r="Q23" s="56"/>
+      <c r="R23" s="58"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="56"/>
+      <c r="U23" s="56"/>
+      <c r="V23" s="56"/>
+      <c r="W23" s="56"/>
+      <c r="X23" s="56"/>
       <c r="Y23" s="10"/>
       <c r="Z23" s="10"/>
       <c r="AA23" s="10"/>
       <c r="AB23" s="10"/>
       <c r="AC23" s="10"/>
       <c r="AD23" s="10"/>
-      <c r="AE23" s="10"/>
-      <c r="AF23" s="10"/>
-      <c r="AG23" s="10"/>
-      <c r="AH23" s="10"/>
-      <c r="AI23" s="10"/>
-      <c r="AJ23" s="10"/>
-      <c r="AK23" s="10"/>
-      <c r="AL23" s="10"/>
-    </row>
-    <row r="24" spans="1:38" ht="12" customHeight="1">
-      <c r="A24" s="93"/>
-      <c r="B24" s="95"/>
-      <c r="C24" s="95"/>
-      <c r="D24" s="95"/>
-      <c r="E24" s="95"/>
+      <c r="AE23" s="69"/>
+      <c r="AF23" s="69"/>
+      <c r="AG23" s="69"/>
+      <c r="AH23" s="69"/>
+      <c r="AI23" s="69"/>
+      <c r="AJ23" s="69"/>
+      <c r="AK23" s="69"/>
+      <c r="AL23" s="69"/>
+    </row>
+    <row r="24" spans="1:38" ht="13.5" customHeight="1">
+      <c r="A24" s="90"/>
+      <c r="B24" s="92"/>
+      <c r="C24" s="92"/>
+      <c r="D24" s="92"/>
+      <c r="E24" s="92"/>
       <c r="F24" s="37" t="s">
         <v>14</v>
       </c>
@@ -2954,145 +2902,149 @@
       <c r="AL24" s="12"/>
     </row>
     <row r="25" spans="1:38" ht="12" customHeight="1">
-      <c r="A25" s="94">
-        <v>11</v>
+      <c r="A25" s="89">
+        <v>9</v>
       </c>
-      <c r="B25" s="92" t="s">
-        <v>34</v>
+      <c r="B25" s="91" t="s">
+        <v>32</v>
       </c>
-      <c r="C25" s="92">
-        <v>1</v>
+      <c r="C25" s="91">
+        <v>2</v>
       </c>
-      <c r="D25" s="92"/>
-      <c r="E25" s="92"/>
-      <c r="F25" s="54" t="s">
+      <c r="D25" s="91"/>
+      <c r="E25" s="91"/>
+      <c r="F25" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="G25" s="55"/>
-      <c r="H25" s="56"/>
-      <c r="I25" s="57"/>
-      <c r="J25" s="57"/>
-      <c r="K25" s="68"/>
-      <c r="L25" s="57"/>
-      <c r="M25" s="56"/>
-      <c r="N25" s="56"/>
-      <c r="O25" s="56"/>
-      <c r="P25" s="56"/>
-      <c r="Q25" s="56"/>
-      <c r="R25" s="58"/>
-      <c r="S25" s="55"/>
-      <c r="T25" s="56"/>
-      <c r="U25" s="56"/>
-      <c r="V25" s="56"/>
-      <c r="W25" s="56"/>
-      <c r="X25" s="56"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="60"/>
+      <c r="L25" s="23"/>
+      <c r="M25" s="24"/>
+      <c r="N25" s="24"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="24"/>
+      <c r="Q25" s="24"/>
+      <c r="R25" s="25"/>
+      <c r="S25" s="26"/>
+      <c r="T25" s="24"/>
+      <c r="U25" s="24"/>
+      <c r="V25" s="24"/>
+      <c r="W25" s="24"/>
+      <c r="X25" s="24"/>
       <c r="Y25" s="10"/>
       <c r="Z25" s="10"/>
       <c r="AA25" s="10"/>
       <c r="AB25" s="10"/>
       <c r="AC25" s="10"/>
       <c r="AD25" s="10"/>
-      <c r="AE25" s="69"/>
-      <c r="AF25" s="69"/>
-      <c r="AG25" s="69"/>
-      <c r="AH25" s="69"/>
-      <c r="AI25" s="69"/>
-      <c r="AJ25" s="69"/>
-      <c r="AK25" s="69"/>
-      <c r="AL25" s="69"/>
+      <c r="AE25" s="27"/>
+      <c r="AF25" s="27"/>
+      <c r="AG25" s="27"/>
+      <c r="AH25" s="27"/>
+      <c r="AI25" s="27"/>
+      <c r="AJ25" s="27"/>
+      <c r="AK25" s="27"/>
+      <c r="AL25" s="27"/>
     </row>
     <row r="26" spans="1:38" ht="12" customHeight="1">
-      <c r="A26" s="93"/>
-      <c r="B26" s="95"/>
-      <c r="C26" s="95"/>
-      <c r="D26" s="95"/>
-      <c r="E26" s="95"/>
-      <c r="F26" s="37" t="s">
+      <c r="A26" s="90"/>
+      <c r="B26" s="90"/>
+      <c r="C26" s="90"/>
+      <c r="D26" s="90"/>
+      <c r="E26" s="90"/>
+      <c r="F26" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="G26" s="47"/>
-      <c r="H26" s="48"/>
-      <c r="I26" s="48"/>
-      <c r="J26" s="48"/>
-      <c r="K26" s="48"/>
-      <c r="L26" s="48"/>
-      <c r="M26" s="48"/>
-      <c r="N26" s="48"/>
-      <c r="O26" s="48"/>
-      <c r="P26" s="48"/>
-      <c r="Q26" s="48"/>
-      <c r="R26" s="49"/>
-      <c r="S26" s="47"/>
-      <c r="T26" s="48"/>
-      <c r="U26" s="48"/>
-      <c r="V26" s="48"/>
-      <c r="W26" s="48"/>
-      <c r="X26" s="48"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="30"/>
+      <c r="P26" s="30"/>
+      <c r="Q26" s="30"/>
+      <c r="R26" s="31"/>
+      <c r="S26" s="29"/>
+      <c r="T26" s="30"/>
+      <c r="U26" s="30"/>
+      <c r="V26" s="30"/>
+      <c r="W26" s="30"/>
+      <c r="X26" s="30"/>
       <c r="Y26" s="10"/>
       <c r="Z26" s="10"/>
       <c r="AA26" s="10"/>
       <c r="AB26" s="10"/>
       <c r="AC26" s="10"/>
       <c r="AD26" s="10"/>
-      <c r="AE26" s="12"/>
-      <c r="AF26" s="12"/>
-      <c r="AG26" s="12"/>
-      <c r="AH26" s="12"/>
-      <c r="AI26" s="12"/>
-      <c r="AJ26" s="12"/>
-      <c r="AK26" s="12"/>
-      <c r="AL26" s="12"/>
+      <c r="AE26" s="46"/>
+      <c r="AF26" s="46"/>
+      <c r="AG26" s="46"/>
+      <c r="AH26" s="46"/>
+      <c r="AI26" s="46"/>
+      <c r="AJ26" s="46"/>
+      <c r="AK26" s="46"/>
+      <c r="AL26" s="46"/>
     </row>
     <row r="27" spans="1:38" ht="12" customHeight="1">
-      <c r="A27" s="94">
-        <v>12</v>
+      <c r="A27" s="89">
+        <v>10</v>
       </c>
-      <c r="B27" s="92"/>
-      <c r="C27" s="92"/>
-      <c r="D27" s="92"/>
-      <c r="E27" s="92"/>
-      <c r="F27" s="54" t="s">
+      <c r="B27" s="91" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="91">
+        <v>2</v>
+      </c>
+      <c r="D27" s="91"/>
+      <c r="E27" s="91"/>
+      <c r="F27" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="G27" s="55"/>
-      <c r="H27" s="56"/>
-      <c r="I27" s="57"/>
-      <c r="J27" s="57"/>
-      <c r="K27" s="57"/>
-      <c r="L27" s="57"/>
-      <c r="M27" s="56"/>
-      <c r="N27" s="56"/>
-      <c r="O27" s="56"/>
-      <c r="P27" s="56"/>
-      <c r="Q27" s="56"/>
-      <c r="R27" s="58"/>
-      <c r="S27" s="55"/>
-      <c r="T27" s="56"/>
-      <c r="U27" s="56"/>
-      <c r="V27" s="56"/>
-      <c r="W27" s="56"/>
-      <c r="X27" s="56"/>
+      <c r="G27" s="36"/>
+      <c r="H27" s="34"/>
+      <c r="I27" s="50"/>
+      <c r="J27" s="50"/>
+      <c r="K27" s="60"/>
+      <c r="L27" s="23"/>
+      <c r="M27" s="34"/>
+      <c r="N27" s="34"/>
+      <c r="O27" s="34"/>
+      <c r="P27" s="34"/>
+      <c r="Q27" s="34"/>
+      <c r="R27" s="35"/>
+      <c r="S27" s="36"/>
+      <c r="T27" s="34"/>
+      <c r="U27" s="34"/>
+      <c r="V27" s="34"/>
+      <c r="W27" s="34"/>
+      <c r="X27" s="34"/>
       <c r="Y27" s="10"/>
       <c r="Z27" s="10"/>
       <c r="AA27" s="10"/>
       <c r="AB27" s="10"/>
       <c r="AC27" s="10"/>
       <c r="AD27" s="10"/>
-      <c r="AE27" s="69"/>
-      <c r="AF27" s="69"/>
-      <c r="AG27" s="69"/>
-      <c r="AH27" s="69"/>
-      <c r="AI27" s="69"/>
-      <c r="AJ27" s="69"/>
-      <c r="AK27" s="69"/>
-      <c r="AL27" s="69"/>
-    </row>
-    <row r="28" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A28" s="93"/>
-      <c r="B28" s="95"/>
-      <c r="C28" s="95"/>
-      <c r="D28" s="95"/>
-      <c r="E28" s="95"/>
+      <c r="AE27" s="10"/>
+      <c r="AF27" s="10"/>
+      <c r="AG27" s="10"/>
+      <c r="AH27" s="10"/>
+      <c r="AI27" s="10"/>
+      <c r="AJ27" s="10"/>
+      <c r="AK27" s="10"/>
+      <c r="AL27" s="10"/>
+    </row>
+    <row r="28" spans="1:38" ht="12" customHeight="1">
+      <c r="A28" s="90"/>
+      <c r="B28" s="92"/>
+      <c r="C28" s="92"/>
+      <c r="D28" s="92"/>
+      <c r="E28" s="92"/>
       <c r="F28" s="37" t="s">
         <v>14</v>
       </c>
@@ -3130,15 +3082,17 @@
       <c r="AL28" s="12"/>
     </row>
     <row r="29" spans="1:38" ht="12" customHeight="1">
-      <c r="A29" s="94">
-        <v>12</v>
+      <c r="A29" s="89">
+        <v>11</v>
       </c>
-      <c r="B29" s="92" t="s">
-        <v>35</v>
+      <c r="B29" s="91" t="s">
+        <v>34</v>
       </c>
-      <c r="C29" s="92"/>
-      <c r="D29" s="92"/>
-      <c r="E29" s="92"/>
+      <c r="C29" s="91">
+        <v>1</v>
+      </c>
+      <c r="D29" s="91"/>
+      <c r="E29" s="91"/>
       <c r="F29" s="54" t="s">
         <v>13</v>
       </c>
@@ -3146,8 +3100,8 @@
       <c r="H29" s="56"/>
       <c r="I29" s="57"/>
       <c r="J29" s="57"/>
-      <c r="K29" s="57"/>
-      <c r="L29" s="68"/>
+      <c r="K29" s="68"/>
+      <c r="L29" s="57"/>
       <c r="M29" s="56"/>
       <c r="N29" s="56"/>
       <c r="O29" s="56"/>
@@ -3175,12 +3129,12 @@
       <c r="AK29" s="69"/>
       <c r="AL29" s="69"/>
     </row>
-    <row r="30" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A30" s="93"/>
-      <c r="B30" s="95"/>
-      <c r="C30" s="95"/>
-      <c r="D30" s="95"/>
-      <c r="E30" s="95"/>
+    <row r="30" spans="1:38" ht="12" customHeight="1">
+      <c r="A30" s="90"/>
+      <c r="B30" s="92"/>
+      <c r="C30" s="92"/>
+      <c r="D30" s="92"/>
+      <c r="E30" s="92"/>
       <c r="F30" s="37" t="s">
         <v>14</v>
       </c>
@@ -3218,238 +3172,233 @@
       <c r="AL30" s="12"/>
     </row>
     <row r="31" spans="1:38" ht="12" customHeight="1">
-      <c r="A31" s="13" t="s">
-        <v>16</v>
+      <c r="A31" s="89">
+        <v>12</v>
       </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="16"/>
-      <c r="O31" s="16"/>
-      <c r="P31" s="16"/>
-      <c r="Q31" s="16"/>
-      <c r="R31" s="18"/>
-      <c r="S31" s="19"/>
-      <c r="T31" s="16"/>
-      <c r="U31" s="16"/>
-      <c r="V31" s="16"/>
-      <c r="W31" s="16"/>
-      <c r="X31" s="16"/>
+      <c r="B31" s="91"/>
+      <c r="C31" s="91"/>
+      <c r="D31" s="91"/>
+      <c r="E31" s="91"/>
+      <c r="F31" s="54" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" s="55"/>
+      <c r="H31" s="56"/>
+      <c r="I31" s="57"/>
+      <c r="J31" s="57"/>
+      <c r="K31" s="57"/>
+      <c r="L31" s="57"/>
+      <c r="M31" s="56"/>
+      <c r="N31" s="56"/>
+      <c r="O31" s="56"/>
+      <c r="P31" s="56"/>
+      <c r="Q31" s="56"/>
+      <c r="R31" s="58"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="56"/>
+      <c r="U31" s="56"/>
+      <c r="V31" s="56"/>
+      <c r="W31" s="56"/>
+      <c r="X31" s="56"/>
       <c r="Y31" s="10"/>
       <c r="Z31" s="10"/>
       <c r="AA31" s="10"/>
       <c r="AB31" s="10"/>
       <c r="AC31" s="10"/>
       <c r="AD31" s="10"/>
-      <c r="AE31" s="20"/>
-      <c r="AF31" s="20"/>
-      <c r="AG31" s="20"/>
-      <c r="AH31" s="20"/>
-      <c r="AI31" s="20"/>
-      <c r="AJ31" s="20"/>
-      <c r="AK31" s="20"/>
-      <c r="AL31" s="20"/>
-    </row>
-    <row r="32" spans="1:38" ht="12" customHeight="1">
-      <c r="A32" s="94">
-        <v>1</v>
-      </c>
-      <c r="B32" s="92" t="s">
-        <v>36</v>
-      </c>
-      <c r="C32" s="92">
-        <v>0.5</v>
-      </c>
+      <c r="AE31" s="69"/>
+      <c r="AF31" s="69"/>
+      <c r="AG31" s="69"/>
+      <c r="AH31" s="69"/>
+      <c r="AI31" s="69"/>
+      <c r="AJ31" s="69"/>
+      <c r="AK31" s="69"/>
+      <c r="AL31" s="69"/>
+    </row>
+    <row r="32" spans="1:38" ht="13.5" customHeight="1">
+      <c r="A32" s="90"/>
+      <c r="B32" s="92"/>
+      <c r="C32" s="92"/>
       <c r="D32" s="92"/>
       <c r="E32" s="92"/>
-      <c r="F32" s="21" t="s">
-        <v>13</v>
+      <c r="F32" s="37" t="s">
+        <v>14</v>
       </c>
-      <c r="G32" s="26"/>
-      <c r="H32" s="24"/>
-      <c r="I32" s="24"/>
-      <c r="J32" s="24"/>
-      <c r="L32" s="52"/>
-      <c r="M32" s="24"/>
-      <c r="N32" s="23"/>
-      <c r="O32" s="23"/>
-      <c r="P32" s="23"/>
-      <c r="Q32" s="23"/>
-      <c r="R32" s="51"/>
-      <c r="S32" s="22"/>
-      <c r="T32" s="23"/>
-      <c r="U32" s="23"/>
-      <c r="V32" s="23"/>
-      <c r="W32" s="23"/>
-      <c r="X32" s="23"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="48"/>
+      <c r="I32" s="48"/>
+      <c r="J32" s="48"/>
+      <c r="K32" s="48"/>
+      <c r="L32" s="48"/>
+      <c r="M32" s="48"/>
+      <c r="N32" s="48"/>
+      <c r="O32" s="48"/>
+      <c r="P32" s="48"/>
+      <c r="Q32" s="48"/>
+      <c r="R32" s="49"/>
+      <c r="S32" s="47"/>
+      <c r="T32" s="48"/>
+      <c r="U32" s="48"/>
+      <c r="V32" s="48"/>
+      <c r="W32" s="48"/>
+      <c r="X32" s="48"/>
       <c r="Y32" s="10"/>
       <c r="Z32" s="10"/>
       <c r="AA32" s="10"/>
       <c r="AB32" s="10"/>
       <c r="AC32" s="10"/>
       <c r="AD32" s="10"/>
-      <c r="AE32" s="27"/>
-      <c r="AF32" s="27"/>
-      <c r="AG32" s="27"/>
-      <c r="AH32" s="27"/>
-      <c r="AI32" s="27"/>
-      <c r="AJ32" s="27"/>
-      <c r="AK32" s="27"/>
-      <c r="AL32" s="27"/>
+      <c r="AE32" s="12"/>
+      <c r="AF32" s="12"/>
+      <c r="AG32" s="12"/>
+      <c r="AH32" s="12"/>
+      <c r="AI32" s="12"/>
+      <c r="AJ32" s="12"/>
+      <c r="AK32" s="12"/>
+      <c r="AL32" s="12"/>
     </row>
     <row r="33" spans="1:38" ht="12" customHeight="1">
-      <c r="A33" s="93"/>
-      <c r="B33" s="95"/>
-      <c r="C33" s="93"/>
-      <c r="D33" s="93"/>
-      <c r="E33" s="93"/>
-      <c r="F33" s="28" t="s">
-        <v>14</v>
+      <c r="A33" s="89">
+        <v>12</v>
       </c>
-      <c r="G33" s="29"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="30"/>
-      <c r="J33" s="30"/>
-      <c r="K33" s="88"/>
-      <c r="L33" s="30"/>
-      <c r="M33" s="30"/>
-      <c r="N33" s="30"/>
-      <c r="O33" s="30"/>
-      <c r="P33" s="30"/>
-      <c r="Q33" s="30"/>
-      <c r="R33" s="31"/>
-      <c r="S33" s="29"/>
-      <c r="T33" s="30"/>
-      <c r="U33" s="30"/>
-      <c r="V33" s="30"/>
-      <c r="W33" s="30"/>
-      <c r="X33" s="30"/>
+      <c r="B33" s="91" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" s="91"/>
+      <c r="D33" s="91"/>
+      <c r="E33" s="91"/>
+      <c r="F33" s="54" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="55"/>
+      <c r="H33" s="56"/>
+      <c r="I33" s="57"/>
+      <c r="J33" s="57"/>
+      <c r="K33" s="57"/>
+      <c r="L33" s="68"/>
+      <c r="M33" s="56"/>
+      <c r="N33" s="56"/>
+      <c r="O33" s="56"/>
+      <c r="P33" s="56"/>
+      <c r="Q33" s="56"/>
+      <c r="R33" s="58"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="56"/>
+      <c r="U33" s="56"/>
+      <c r="V33" s="56"/>
+      <c r="W33" s="56"/>
+      <c r="X33" s="56"/>
       <c r="Y33" s="10"/>
       <c r="Z33" s="10"/>
       <c r="AA33" s="10"/>
       <c r="AB33" s="10"/>
       <c r="AC33" s="10"/>
       <c r="AD33" s="10"/>
-      <c r="AE33" s="32"/>
-      <c r="AF33" s="32"/>
-      <c r="AG33" s="32"/>
-      <c r="AH33" s="32"/>
-      <c r="AI33" s="32"/>
-      <c r="AJ33" s="32"/>
-      <c r="AK33" s="32"/>
-      <c r="AL33" s="32"/>
-    </row>
-    <row r="34" spans="1:38" ht="12" customHeight="1">
-      <c r="A34" s="94">
-        <v>2</v>
-      </c>
-      <c r="B34" s="92" t="s">
-        <v>37</v>
-      </c>
-      <c r="C34" s="92">
-        <v>4</v>
-      </c>
+      <c r="AE33" s="69"/>
+      <c r="AF33" s="69"/>
+      <c r="AG33" s="69"/>
+      <c r="AH33" s="69"/>
+      <c r="AI33" s="69"/>
+      <c r="AJ33" s="69"/>
+      <c r="AK33" s="69"/>
+      <c r="AL33" s="69"/>
+    </row>
+    <row r="34" spans="1:38" ht="13.5" customHeight="1">
+      <c r="A34" s="90"/>
+      <c r="B34" s="92"/>
+      <c r="C34" s="92"/>
       <c r="D34" s="92"/>
       <c r="E34" s="92"/>
-      <c r="F34" s="33" t="s">
-        <v>13</v>
+      <c r="F34" s="37" t="s">
+        <v>14</v>
       </c>
-      <c r="G34" s="36"/>
-      <c r="H34" s="34"/>
-      <c r="I34" s="34"/>
-      <c r="J34" s="34"/>
-      <c r="K34" s="90"/>
-      <c r="L34" s="53"/>
-      <c r="M34" s="53"/>
-      <c r="N34" s="23"/>
-      <c r="O34" s="23"/>
-      <c r="P34" s="23"/>
-      <c r="Q34" s="23"/>
-      <c r="R34" s="51"/>
-      <c r="S34" s="22"/>
-      <c r="T34" s="23"/>
-      <c r="U34" s="23"/>
-      <c r="V34" s="23"/>
-      <c r="W34" s="23"/>
-      <c r="X34" s="23"/>
+      <c r="G34" s="47"/>
+      <c r="H34" s="48"/>
+      <c r="I34" s="48"/>
+      <c r="J34" s="48"/>
+      <c r="K34" s="48"/>
+      <c r="L34" s="48"/>
+      <c r="M34" s="48"/>
+      <c r="N34" s="48"/>
+      <c r="O34" s="48"/>
+      <c r="P34" s="48"/>
+      <c r="Q34" s="48"/>
+      <c r="R34" s="49"/>
+      <c r="S34" s="47"/>
+      <c r="T34" s="48"/>
+      <c r="U34" s="48"/>
+      <c r="V34" s="48"/>
+      <c r="W34" s="48"/>
+      <c r="X34" s="48"/>
       <c r="Y34" s="10"/>
       <c r="Z34" s="10"/>
       <c r="AA34" s="10"/>
       <c r="AB34" s="10"/>
       <c r="AC34" s="10"/>
       <c r="AD34" s="10"/>
-      <c r="AE34" s="10"/>
-      <c r="AF34" s="10"/>
-      <c r="AG34" s="10"/>
-      <c r="AH34" s="10"/>
-      <c r="AI34" s="10"/>
-      <c r="AJ34" s="10"/>
-      <c r="AK34" s="10"/>
-      <c r="AL34" s="10"/>
+      <c r="AE34" s="12"/>
+      <c r="AF34" s="12"/>
+      <c r="AG34" s="12"/>
+      <c r="AH34" s="12"/>
+      <c r="AI34" s="12"/>
+      <c r="AJ34" s="12"/>
+      <c r="AK34" s="12"/>
+      <c r="AL34" s="12"/>
     </row>
     <row r="35" spans="1:38" ht="12" customHeight="1">
-      <c r="A35" s="93"/>
-      <c r="B35" s="95"/>
-      <c r="C35" s="93"/>
-      <c r="D35" s="93"/>
-      <c r="E35" s="93"/>
-      <c r="F35" s="37" t="s">
-        <v>14</v>
+      <c r="A35" s="13" t="s">
+        <v>16</v>
       </c>
-      <c r="G35" s="38"/>
-      <c r="H35" s="39"/>
-      <c r="I35" s="39"/>
-      <c r="J35" s="39"/>
-      <c r="K35" s="88"/>
-      <c r="L35" s="39"/>
-      <c r="M35" s="39"/>
-      <c r="N35" s="39"/>
-      <c r="O35" s="39"/>
-      <c r="P35" s="39"/>
-      <c r="Q35" s="39"/>
-      <c r="R35" s="40"/>
-      <c r="S35" s="38"/>
-      <c r="T35" s="39"/>
-      <c r="U35" s="39"/>
-      <c r="V35" s="39"/>
-      <c r="W35" s="39"/>
-      <c r="X35" s="39"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="16"/>
+      <c r="I35" s="16"/>
+      <c r="J35" s="16"/>
+      <c r="K35" s="16"/>
+      <c r="L35" s="16"/>
+      <c r="M35" s="16"/>
+      <c r="N35" s="16"/>
+      <c r="O35" s="16"/>
+      <c r="P35" s="16"/>
+      <c r="Q35" s="16"/>
+      <c r="R35" s="18"/>
+      <c r="S35" s="19"/>
+      <c r="T35" s="16"/>
+      <c r="U35" s="16"/>
+      <c r="V35" s="16"/>
+      <c r="W35" s="16"/>
+      <c r="X35" s="16"/>
       <c r="Y35" s="10"/>
       <c r="Z35" s="10"/>
       <c r="AA35" s="10"/>
       <c r="AB35" s="10"/>
       <c r="AC35" s="10"/>
       <c r="AD35" s="10"/>
-      <c r="AE35" s="41"/>
-      <c r="AF35" s="41"/>
-      <c r="AG35" s="41"/>
-      <c r="AH35" s="41"/>
-      <c r="AI35" s="41"/>
-      <c r="AJ35" s="41"/>
-      <c r="AK35" s="41"/>
-      <c r="AL35" s="41"/>
+      <c r="AE35" s="20"/>
+      <c r="AF35" s="20"/>
+      <c r="AG35" s="20"/>
+      <c r="AH35" s="20"/>
+      <c r="AI35" s="20"/>
+      <c r="AJ35" s="20"/>
+      <c r="AK35" s="20"/>
+      <c r="AL35" s="20"/>
     </row>
     <row r="36" spans="1:38" ht="12" customHeight="1">
-      <c r="A36" s="94">
-        <v>3</v>
+      <c r="A36" s="89">
+        <v>1</v>
       </c>
-      <c r="B36" s="92" t="s">
-        <v>38</v>
+      <c r="B36" s="91" t="s">
+        <v>36</v>
       </c>
-      <c r="C36" s="92">
-        <v>4</v>
+      <c r="C36" s="91">
+        <v>0.5</v>
       </c>
-      <c r="D36" s="92"/>
-      <c r="E36" s="92"/>
+      <c r="D36" s="91"/>
+      <c r="E36" s="91"/>
       <c r="F36" s="21" t="s">
         <v>13</v>
       </c>
@@ -3457,20 +3406,19 @@
       <c r="H36" s="24"/>
       <c r="I36" s="24"/>
       <c r="J36" s="24"/>
-      <c r="K36" s="90"/>
-      <c r="L36" s="24"/>
-      <c r="M36" s="52"/>
-      <c r="N36" s="52"/>
-      <c r="O36" s="24"/>
-      <c r="P36" s="24"/>
-      <c r="Q36" s="24"/>
-      <c r="R36" s="25"/>
-      <c r="S36" s="26"/>
-      <c r="T36" s="24"/>
-      <c r="U36" s="24"/>
-      <c r="V36" s="24"/>
-      <c r="W36" s="24"/>
-      <c r="X36" s="24"/>
+      <c r="L36" s="52"/>
+      <c r="M36" s="24"/>
+      <c r="N36" s="23"/>
+      <c r="O36" s="23"/>
+      <c r="P36" s="23"/>
+      <c r="Q36" s="23"/>
+      <c r="R36" s="51"/>
+      <c r="S36" s="22"/>
+      <c r="T36" s="23"/>
+      <c r="U36" s="23"/>
+      <c r="V36" s="23"/>
+      <c r="W36" s="23"/>
+      <c r="X36" s="23"/>
       <c r="Y36" s="10"/>
       <c r="Z36" s="10"/>
       <c r="AA36" s="10"/>
@@ -3487,31 +3435,32 @@
       <c r="AL36" s="27"/>
     </row>
     <row r="37" spans="1:38" ht="12" customHeight="1">
-      <c r="A37" s="93"/>
-      <c r="B37" s="95"/>
-      <c r="C37" s="93"/>
-      <c r="D37" s="93"/>
-      <c r="E37" s="93"/>
-      <c r="F37" s="42" t="s">
+      <c r="A37" s="90"/>
+      <c r="B37" s="92"/>
+      <c r="C37" s="90"/>
+      <c r="D37" s="90"/>
+      <c r="E37" s="90"/>
+      <c r="F37" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="G37" s="43"/>
-      <c r="H37" s="44"/>
-      <c r="I37" s="44"/>
-      <c r="J37" s="44"/>
-      <c r="L37" s="44"/>
-      <c r="M37" s="44"/>
-      <c r="N37" s="44"/>
-      <c r="O37" s="44"/>
-      <c r="P37" s="44"/>
-      <c r="Q37" s="44"/>
-      <c r="R37" s="45"/>
-      <c r="S37" s="43"/>
-      <c r="T37" s="44"/>
-      <c r="U37" s="44"/>
-      <c r="V37" s="44"/>
-      <c r="W37" s="44"/>
-      <c r="X37" s="44"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="83"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="30"/>
+      <c r="N37" s="30"/>
+      <c r="O37" s="30"/>
+      <c r="P37" s="30"/>
+      <c r="Q37" s="30"/>
+      <c r="R37" s="31"/>
+      <c r="S37" s="29"/>
+      <c r="T37" s="30"/>
+      <c r="U37" s="30"/>
+      <c r="V37" s="30"/>
+      <c r="W37" s="30"/>
+      <c r="X37" s="30"/>
       <c r="Y37" s="10"/>
       <c r="Z37" s="10"/>
       <c r="AA37" s="10"/>
@@ -3528,13 +3477,17 @@
       <c r="AL37" s="32"/>
     </row>
     <row r="38" spans="1:38" ht="12" customHeight="1">
-      <c r="A38" s="94">
+      <c r="A38" s="89">
+        <v>2</v>
+      </c>
+      <c r="B38" s="91" t="s">
+        <v>37</v>
+      </c>
+      <c r="C38" s="91">
         <v>4</v>
       </c>
-      <c r="B38" s="92"/>
-      <c r="C38" s="92"/>
-      <c r="D38" s="92"/>
-      <c r="E38" s="92"/>
+      <c r="D38" s="91"/>
+      <c r="E38" s="91"/>
       <c r="F38" s="33" t="s">
         <v>13</v>
       </c>
@@ -3542,20 +3495,20 @@
       <c r="H38" s="34"/>
       <c r="I38" s="34"/>
       <c r="J38" s="34"/>
-      <c r="K38" s="90"/>
-      <c r="L38" s="34"/>
-      <c r="M38" s="34"/>
-      <c r="N38" s="34"/>
-      <c r="O38" s="34"/>
-      <c r="P38" s="34"/>
-      <c r="Q38" s="34"/>
-      <c r="R38" s="35"/>
-      <c r="S38" s="36"/>
-      <c r="T38" s="34"/>
-      <c r="U38" s="34"/>
-      <c r="V38" s="34"/>
-      <c r="W38" s="34"/>
-      <c r="X38" s="34"/>
+      <c r="K38" s="84"/>
+      <c r="L38" s="53"/>
+      <c r="M38" s="53"/>
+      <c r="N38" s="23"/>
+      <c r="O38" s="23"/>
+      <c r="P38" s="23"/>
+      <c r="Q38" s="23"/>
+      <c r="R38" s="51"/>
+      <c r="S38" s="22"/>
+      <c r="T38" s="23"/>
+      <c r="U38" s="23"/>
+      <c r="V38" s="23"/>
+      <c r="W38" s="23"/>
+      <c r="X38" s="23"/>
       <c r="Y38" s="10"/>
       <c r="Z38" s="10"/>
       <c r="AA38" s="10"/>
@@ -3572,11 +3525,11 @@
       <c r="AL38" s="10"/>
     </row>
     <row r="39" spans="1:38" ht="12" customHeight="1">
-      <c r="A39" s="93"/>
-      <c r="B39" s="95"/>
-      <c r="C39" s="95"/>
-      <c r="D39" s="95"/>
-      <c r="E39" s="95"/>
+      <c r="A39" s="90"/>
+      <c r="B39" s="92"/>
+      <c r="C39" s="90"/>
+      <c r="D39" s="90"/>
+      <c r="E39" s="90"/>
       <c r="F39" s="37" t="s">
         <v>14</v>
       </c>
@@ -3584,7 +3537,7 @@
       <c r="H39" s="39"/>
       <c r="I39" s="39"/>
       <c r="J39" s="39"/>
-      <c r="K39" s="89"/>
+      <c r="K39" s="83"/>
       <c r="L39" s="39"/>
       <c r="M39" s="39"/>
       <c r="N39" s="39"/>
@@ -3614,282 +3567,278 @@
       <c r="AL39" s="41"/>
     </row>
     <row r="40" spans="1:38" ht="12" customHeight="1">
-      <c r="A40" s="94">
-        <v>5</v>
+      <c r="A40" s="89">
+        <v>3</v>
       </c>
-      <c r="B40" s="92" t="s">
-        <v>39</v>
+      <c r="B40" s="91" t="s">
+        <v>38</v>
       </c>
-      <c r="C40" s="92">
-        <v>0.5</v>
+      <c r="C40" s="91">
+        <v>4</v>
       </c>
-      <c r="D40" s="92"/>
-      <c r="E40" s="92"/>
-      <c r="F40" s="79" t="s">
+      <c r="D40" s="91"/>
+      <c r="E40" s="91"/>
+      <c r="F40" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="G40" s="80"/>
-      <c r="H40" s="81"/>
-      <c r="I40" s="81"/>
-      <c r="J40" s="81"/>
-      <c r="K40" s="89"/>
-      <c r="L40" s="81"/>
-      <c r="M40" s="81"/>
-      <c r="N40" s="82"/>
-      <c r="O40" s="81"/>
-      <c r="P40" s="81"/>
-      <c r="Q40" s="81"/>
-      <c r="R40" s="83"/>
-      <c r="S40" s="80"/>
-      <c r="T40" s="81"/>
-      <c r="U40" s="81"/>
-      <c r="V40" s="81"/>
-      <c r="W40" s="81"/>
-      <c r="X40" s="81"/>
+      <c r="G40" s="26"/>
+      <c r="H40" s="24"/>
+      <c r="I40" s="24"/>
+      <c r="J40" s="24"/>
+      <c r="K40" s="84"/>
+      <c r="L40" s="24"/>
+      <c r="M40" s="52"/>
+      <c r="N40" s="52"/>
+      <c r="O40" s="24"/>
+      <c r="P40" s="24"/>
+      <c r="Q40" s="24"/>
+      <c r="R40" s="25"/>
+      <c r="S40" s="26"/>
+      <c r="T40" s="24"/>
+      <c r="U40" s="24"/>
+      <c r="V40" s="24"/>
+      <c r="W40" s="24"/>
+      <c r="X40" s="24"/>
       <c r="Y40" s="10"/>
       <c r="Z40" s="10"/>
       <c r="AA40" s="10"/>
       <c r="AB40" s="10"/>
       <c r="AC40" s="10"/>
       <c r="AD40" s="10"/>
-      <c r="AE40" s="84"/>
-      <c r="AF40" s="84"/>
-      <c r="AG40" s="84"/>
-      <c r="AH40" s="84"/>
-      <c r="AI40" s="84"/>
-      <c r="AJ40" s="84"/>
-      <c r="AK40" s="84"/>
-      <c r="AL40" s="84"/>
+      <c r="AE40" s="27"/>
+      <c r="AF40" s="27"/>
+      <c r="AG40" s="27"/>
+      <c r="AH40" s="27"/>
+      <c r="AI40" s="27"/>
+      <c r="AJ40" s="27"/>
+      <c r="AK40" s="27"/>
+      <c r="AL40" s="27"/>
     </row>
     <row r="41" spans="1:38" ht="12" customHeight="1">
-      <c r="A41" s="93"/>
-      <c r="B41" s="95"/>
-      <c r="C41" s="95"/>
-      <c r="D41" s="95"/>
-      <c r="E41" s="95"/>
-      <c r="F41" s="37" t="s">
+      <c r="A41" s="90"/>
+      <c r="B41" s="92"/>
+      <c r="C41" s="90"/>
+      <c r="D41" s="90"/>
+      <c r="E41" s="90"/>
+      <c r="F41" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="G41" s="38"/>
-      <c r="H41" s="39"/>
-      <c r="I41" s="39"/>
-      <c r="J41" s="39"/>
-      <c r="K41" s="91"/>
-      <c r="L41" s="39"/>
-      <c r="M41" s="39"/>
-      <c r="N41" s="39"/>
-      <c r="O41" s="39"/>
-      <c r="P41" s="39"/>
-      <c r="Q41" s="39"/>
-      <c r="R41" s="40"/>
-      <c r="S41" s="38"/>
-      <c r="T41" s="39"/>
-      <c r="U41" s="39"/>
-      <c r="V41" s="39"/>
-      <c r="W41" s="39"/>
-      <c r="X41" s="39"/>
+      <c r="G41" s="43"/>
+      <c r="H41" s="44"/>
+      <c r="I41" s="44"/>
+      <c r="J41" s="44"/>
+      <c r="L41" s="44"/>
+      <c r="M41" s="44"/>
+      <c r="N41" s="44"/>
+      <c r="O41" s="44"/>
+      <c r="P41" s="44"/>
+      <c r="Q41" s="44"/>
+      <c r="R41" s="45"/>
+      <c r="S41" s="43"/>
+      <c r="T41" s="44"/>
+      <c r="U41" s="44"/>
+      <c r="V41" s="44"/>
+      <c r="W41" s="44"/>
+      <c r="X41" s="44"/>
       <c r="Y41" s="10"/>
       <c r="Z41" s="10"/>
       <c r="AA41" s="10"/>
       <c r="AB41" s="10"/>
       <c r="AC41" s="10"/>
       <c r="AD41" s="10"/>
-      <c r="AE41" s="41"/>
-      <c r="AF41" s="41"/>
-      <c r="AG41" s="41"/>
-      <c r="AH41" s="41"/>
-      <c r="AI41" s="41"/>
-      <c r="AJ41" s="41"/>
-      <c r="AK41" s="41"/>
-      <c r="AL41" s="41"/>
+      <c r="AE41" s="32"/>
+      <c r="AF41" s="32"/>
+      <c r="AG41" s="32"/>
+      <c r="AH41" s="32"/>
+      <c r="AI41" s="32"/>
+      <c r="AJ41" s="32"/>
+      <c r="AK41" s="32"/>
+      <c r="AL41" s="32"/>
     </row>
     <row r="42" spans="1:38" ht="12" customHeight="1">
-      <c r="A42" s="94">
-        <v>6</v>
+      <c r="A42" s="89">
+        <v>4</v>
       </c>
-      <c r="B42" s="92"/>
-      <c r="C42" s="92"/>
-      <c r="D42" s="92"/>
-      <c r="E42" s="92"/>
-      <c r="F42" s="21" t="s">
+      <c r="B42" s="91"/>
+      <c r="C42" s="91"/>
+      <c r="D42" s="91"/>
+      <c r="E42" s="91"/>
+      <c r="F42" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="G42" s="26"/>
-      <c r="H42" s="24"/>
-      <c r="I42" s="24"/>
-      <c r="J42" s="24"/>
-      <c r="L42" s="24"/>
-      <c r="M42" s="24"/>
-      <c r="N42" s="24"/>
-      <c r="O42" s="24"/>
-      <c r="P42" s="24"/>
-      <c r="Q42" s="24"/>
-      <c r="R42" s="25"/>
-      <c r="S42" s="26"/>
-      <c r="T42" s="24"/>
-      <c r="U42" s="24"/>
-      <c r="V42" s="24"/>
-      <c r="W42" s="24"/>
-      <c r="X42" s="24"/>
+      <c r="G42" s="36"/>
+      <c r="H42" s="34"/>
+      <c r="I42" s="34"/>
+      <c r="J42" s="34"/>
+      <c r="K42" s="84"/>
+      <c r="L42" s="34"/>
+      <c r="M42" s="34"/>
+      <c r="N42" s="34"/>
+      <c r="O42" s="34"/>
+      <c r="P42" s="34"/>
+      <c r="Q42" s="34"/>
+      <c r="R42" s="35"/>
+      <c r="S42" s="36"/>
+      <c r="T42" s="34"/>
+      <c r="U42" s="34"/>
+      <c r="V42" s="34"/>
+      <c r="W42" s="34"/>
+      <c r="X42" s="34"/>
       <c r="Y42" s="10"/>
       <c r="Z42" s="10"/>
       <c r="AA42" s="10"/>
       <c r="AB42" s="10"/>
       <c r="AC42" s="10"/>
       <c r="AD42" s="10"/>
-      <c r="AE42" s="27"/>
-      <c r="AF42" s="27"/>
-      <c r="AG42" s="27"/>
-      <c r="AH42" s="27"/>
-      <c r="AI42" s="27"/>
-      <c r="AJ42" s="27"/>
-      <c r="AK42" s="27"/>
-      <c r="AL42" s="27"/>
+      <c r="AE42" s="10"/>
+      <c r="AF42" s="10"/>
+      <c r="AG42" s="10"/>
+      <c r="AH42" s="10"/>
+      <c r="AI42" s="10"/>
+      <c r="AJ42" s="10"/>
+      <c r="AK42" s="10"/>
+      <c r="AL42" s="10"/>
     </row>
     <row r="43" spans="1:38" ht="12" customHeight="1">
-      <c r="A43" s="93"/>
-      <c r="B43" s="95"/>
-      <c r="C43" s="93"/>
-      <c r="D43" s="93"/>
-      <c r="E43" s="93"/>
-      <c r="F43" s="42" t="s">
+      <c r="A43" s="90"/>
+      <c r="B43" s="92"/>
+      <c r="C43" s="92"/>
+      <c r="D43" s="92"/>
+      <c r="E43" s="92"/>
+      <c r="F43" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="G43" s="29"/>
-      <c r="H43" s="30"/>
-      <c r="I43" s="30"/>
-      <c r="J43" s="30"/>
-      <c r="K43" s="88"/>
-      <c r="L43" s="30"/>
-      <c r="M43" s="30"/>
-      <c r="N43" s="30"/>
-      <c r="O43" s="30"/>
-      <c r="P43" s="30"/>
-      <c r="Q43" s="30"/>
-      <c r="R43" s="31"/>
-      <c r="S43" s="29"/>
-      <c r="T43" s="30"/>
-      <c r="U43" s="30"/>
-      <c r="V43" s="30"/>
-      <c r="W43" s="30"/>
-      <c r="X43" s="30"/>
+      <c r="G43" s="38"/>
+      <c r="H43" s="87"/>
+      <c r="I43" s="87"/>
+      <c r="J43" s="87"/>
+      <c r="K43" s="83"/>
+      <c r="L43" s="87"/>
+      <c r="M43" s="87"/>
+      <c r="N43" s="87"/>
+      <c r="O43" s="87"/>
+      <c r="P43" s="87"/>
+      <c r="Q43" s="87"/>
+      <c r="R43" s="40"/>
+      <c r="S43" s="38"/>
+      <c r="T43" s="87"/>
+      <c r="U43" s="87"/>
+      <c r="V43" s="87"/>
+      <c r="W43" s="87"/>
+      <c r="X43" s="87"/>
       <c r="Y43" s="10"/>
       <c r="Z43" s="10"/>
       <c r="AA43" s="10"/>
       <c r="AB43" s="10"/>
       <c r="AC43" s="10"/>
       <c r="AD43" s="10"/>
-      <c r="AE43" s="46"/>
-      <c r="AF43" s="46"/>
-      <c r="AG43" s="46"/>
-      <c r="AH43" s="46"/>
-      <c r="AI43" s="46"/>
-      <c r="AJ43" s="46"/>
-      <c r="AK43" s="46"/>
-      <c r="AL43" s="46"/>
+      <c r="AE43" s="41"/>
+      <c r="AF43" s="41"/>
+      <c r="AG43" s="41"/>
+      <c r="AH43" s="41"/>
+      <c r="AI43" s="41"/>
+      <c r="AJ43" s="41"/>
+      <c r="AK43" s="41"/>
+      <c r="AL43" s="41"/>
     </row>
     <row r="44" spans="1:38" ht="12" customHeight="1">
-      <c r="A44" s="94">
-        <v>7</v>
+      <c r="A44" s="89">
+        <v>5</v>
       </c>
-      <c r="B44" s="92" t="s">
-        <v>40</v>
+      <c r="B44" s="91" t="s">
+        <v>39</v>
       </c>
-      <c r="C44" s="92">
+      <c r="C44" s="91">
         <v>0.5</v>
       </c>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
-      <c r="F44" s="21" t="s">
+      <c r="D44" s="91"/>
+      <c r="E44" s="91"/>
+      <c r="F44" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="G44" s="26"/>
-      <c r="H44" s="24"/>
-      <c r="I44" s="24"/>
-      <c r="J44" s="24"/>
-      <c r="K44" s="90"/>
-      <c r="L44" s="24"/>
-      <c r="M44" s="24"/>
-      <c r="N44" s="24"/>
-      <c r="O44" s="52"/>
-      <c r="P44" s="24"/>
-      <c r="Q44" s="24"/>
-      <c r="R44" s="25"/>
-      <c r="S44" s="26"/>
-      <c r="T44" s="24"/>
-      <c r="U44" s="24"/>
-      <c r="V44" s="24"/>
-      <c r="W44" s="24"/>
-      <c r="X44" s="24"/>
+      <c r="G44" s="55"/>
+      <c r="H44" s="56"/>
+      <c r="I44" s="56"/>
+      <c r="J44" s="56"/>
+      <c r="K44" s="84"/>
+      <c r="L44" s="56"/>
+      <c r="M44" s="56"/>
+      <c r="N44" s="88"/>
+      <c r="O44" s="56"/>
+      <c r="P44" s="56"/>
+      <c r="Q44" s="56"/>
+      <c r="R44" s="58"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="56"/>
+      <c r="U44" s="56"/>
+      <c r="V44" s="56"/>
+      <c r="W44" s="56"/>
+      <c r="X44" s="56"/>
       <c r="Y44" s="10"/>
       <c r="Z44" s="10"/>
       <c r="AA44" s="10"/>
       <c r="AB44" s="10"/>
       <c r="AC44" s="10"/>
       <c r="AD44" s="10"/>
-      <c r="AE44" s="27"/>
-      <c r="AF44" s="27"/>
-      <c r="AG44" s="27"/>
-      <c r="AH44" s="27"/>
-      <c r="AI44" s="27"/>
-      <c r="AJ44" s="27"/>
-      <c r="AK44" s="27"/>
-      <c r="AL44" s="27"/>
+      <c r="AE44" s="79"/>
+      <c r="AF44" s="79"/>
+      <c r="AG44" s="79"/>
+      <c r="AH44" s="79"/>
+      <c r="AI44" s="79"/>
+      <c r="AJ44" s="79"/>
+      <c r="AK44" s="79"/>
+      <c r="AL44" s="79"/>
     </row>
     <row r="45" spans="1:38" ht="12" customHeight="1">
-      <c r="A45" s="93"/>
-      <c r="B45" s="95"/>
-      <c r="C45" s="93"/>
-      <c r="D45" s="93"/>
-      <c r="E45" s="93"/>
-      <c r="F45" s="42" t="s">
+      <c r="A45" s="90"/>
+      <c r="B45" s="92"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
+      <c r="F45" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="G45" s="29"/>
-      <c r="H45" s="30"/>
-      <c r="I45" s="30"/>
-      <c r="J45" s="30"/>
-      <c r="K45" s="91"/>
-      <c r="L45" s="30"/>
-      <c r="M45" s="30"/>
-      <c r="N45" s="30"/>
-      <c r="O45" s="30"/>
-      <c r="P45" s="30"/>
-      <c r="Q45" s="30"/>
-      <c r="R45" s="31"/>
-      <c r="S45" s="29"/>
-      <c r="T45" s="30"/>
-      <c r="U45" s="30"/>
-      <c r="V45" s="30"/>
-      <c r="W45" s="30"/>
-      <c r="X45" s="30"/>
+      <c r="G45" s="38"/>
+      <c r="H45" s="39"/>
+      <c r="I45" s="39"/>
+      <c r="J45" s="39"/>
+      <c r="K45" s="85"/>
+      <c r="L45" s="39"/>
+      <c r="M45" s="39"/>
+      <c r="N45" s="39"/>
+      <c r="O45" s="39"/>
+      <c r="P45" s="39"/>
+      <c r="Q45" s="39"/>
+      <c r="R45" s="40"/>
+      <c r="S45" s="38"/>
+      <c r="T45" s="39"/>
+      <c r="U45" s="39"/>
+      <c r="V45" s="39"/>
+      <c r="W45" s="39"/>
+      <c r="X45" s="39"/>
       <c r="Y45" s="10"/>
       <c r="Z45" s="10"/>
       <c r="AA45" s="10"/>
       <c r="AB45" s="10"/>
       <c r="AC45" s="10"/>
       <c r="AD45" s="10"/>
-      <c r="AE45" s="46"/>
-      <c r="AF45" s="46"/>
-      <c r="AG45" s="46"/>
-      <c r="AH45" s="46"/>
-      <c r="AI45" s="46"/>
-      <c r="AJ45" s="46"/>
-      <c r="AK45" s="46"/>
-      <c r="AL45" s="46"/>
+      <c r="AE45" s="41"/>
+      <c r="AF45" s="41"/>
+      <c r="AG45" s="41"/>
+      <c r="AH45" s="41"/>
+      <c r="AI45" s="41"/>
+      <c r="AJ45" s="41"/>
+      <c r="AK45" s="41"/>
+      <c r="AL45" s="41"/>
     </row>
     <row r="46" spans="1:38" ht="12" customHeight="1">
-      <c r="A46" s="94">
-        <v>8</v>
+      <c r="A46" s="89">
+        <v>6</v>
       </c>
-      <c r="B46" s="92" t="s">
-        <v>41</v>
-      </c>
-      <c r="C46" s="92">
-        <v>4</v>
-      </c>
-      <c r="D46" s="92"/>
-      <c r="E46" s="92"/>
+      <c r="B46" s="91"/>
+      <c r="C46" s="91"/>
+      <c r="D46" s="91"/>
+      <c r="E46" s="91"/>
       <c r="F46" s="21" t="s">
         <v>13</v>
       </c>
@@ -3900,8 +3849,8 @@
       <c r="L46" s="24"/>
       <c r="M46" s="24"/>
       <c r="N46" s="24"/>
-      <c r="O46" s="52"/>
-      <c r="P46" s="52"/>
+      <c r="O46" s="24"/>
+      <c r="P46" s="24"/>
       <c r="Q46" s="24"/>
       <c r="R46" s="25"/>
       <c r="S46" s="26"/>
@@ -3926,11 +3875,11 @@
       <c r="AL46" s="27"/>
     </row>
     <row r="47" spans="1:38" ht="12" customHeight="1">
-      <c r="A47" s="93"/>
-      <c r="B47" s="95"/>
-      <c r="C47" s="93"/>
-      <c r="D47" s="93"/>
-      <c r="E47" s="93"/>
+      <c r="A47" s="90"/>
+      <c r="B47" s="92"/>
+      <c r="C47" s="90"/>
+      <c r="D47" s="90"/>
+      <c r="E47" s="90"/>
       <c r="F47" s="42" t="s">
         <v>14</v>
       </c>
@@ -3938,7 +3887,7 @@
       <c r="H47" s="30"/>
       <c r="I47" s="30"/>
       <c r="J47" s="30"/>
-      <c r="K47" s="88"/>
+      <c r="K47" s="83"/>
       <c r="L47" s="30"/>
       <c r="M47" s="30"/>
       <c r="N47" s="30"/>
@@ -3968,13 +3917,17 @@
       <c r="AL47" s="46"/>
     </row>
     <row r="48" spans="1:38" ht="12" customHeight="1">
-      <c r="A48" s="94">
-        <v>9</v>
+      <c r="A48" s="89">
+        <v>7</v>
       </c>
-      <c r="B48" s="92"/>
-      <c r="C48" s="92"/>
-      <c r="D48" s="92"/>
-      <c r="E48" s="92"/>
+      <c r="B48" s="91" t="s">
+        <v>40</v>
+      </c>
+      <c r="C48" s="91">
+        <v>0.5</v>
+      </c>
+      <c r="D48" s="91"/>
+      <c r="E48" s="91"/>
       <c r="F48" s="21" t="s">
         <v>13</v>
       </c>
@@ -3982,11 +3935,11 @@
       <c r="H48" s="24"/>
       <c r="I48" s="24"/>
       <c r="J48" s="24"/>
-      <c r="K48" s="90"/>
+      <c r="K48" s="84"/>
       <c r="L48" s="24"/>
       <c r="M48" s="24"/>
       <c r="N48" s="24"/>
-      <c r="O48" s="24"/>
+      <c r="O48" s="52"/>
       <c r="P48" s="24"/>
       <c r="Q48" s="24"/>
       <c r="R48" s="25"/>
@@ -4012,11 +3965,11 @@
       <c r="AL48" s="27"/>
     </row>
     <row r="49" spans="1:38" ht="12" customHeight="1">
-      <c r="A49" s="93"/>
-      <c r="B49" s="95"/>
-      <c r="C49" s="93"/>
-      <c r="D49" s="93"/>
-      <c r="E49" s="93"/>
+      <c r="A49" s="90"/>
+      <c r="B49" s="92"/>
+      <c r="C49" s="90"/>
+      <c r="D49" s="90"/>
+      <c r="E49" s="90"/>
       <c r="F49" s="42" t="s">
         <v>14</v>
       </c>
@@ -4024,7 +3977,7 @@
       <c r="H49" s="30"/>
       <c r="I49" s="30"/>
       <c r="J49" s="30"/>
-      <c r="K49" s="88"/>
+      <c r="K49" s="85"/>
       <c r="L49" s="30"/>
       <c r="M49" s="30"/>
       <c r="N49" s="30"/>
@@ -4053,320 +4006,319 @@
       <c r="AK49" s="46"/>
       <c r="AL49" s="46"/>
     </row>
-    <row r="50" spans="1:38" ht="11.25" customHeight="1">
-      <c r="A50" s="94">
-        <v>10</v>
+    <row r="50" spans="1:38" ht="12" customHeight="1">
+      <c r="A50" s="89">
+        <v>8</v>
       </c>
-      <c r="B50" s="92" t="s">
-        <v>35</v>
+      <c r="B50" s="91" t="s">
+        <v>41</v>
       </c>
-      <c r="C50" s="92"/>
-      <c r="D50" s="92"/>
-      <c r="E50" s="92"/>
-      <c r="F50" s="33" t="s">
+      <c r="C50" s="91">
+        <v>4</v>
+      </c>
+      <c r="D50" s="91"/>
+      <c r="E50" s="91"/>
+      <c r="F50" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="G50" s="36"/>
-      <c r="H50" s="34"/>
-      <c r="I50" s="34"/>
-      <c r="J50" s="34"/>
-      <c r="K50" s="90"/>
-      <c r="L50" s="34"/>
-      <c r="M50" s="34"/>
-      <c r="N50" s="34"/>
-      <c r="O50" s="34"/>
-      <c r="P50" s="34"/>
-      <c r="Q50" s="87"/>
-      <c r="R50" s="35"/>
-      <c r="S50" s="36"/>
-      <c r="T50" s="34"/>
-      <c r="U50" s="34"/>
-      <c r="V50" s="34"/>
-      <c r="W50" s="34"/>
-      <c r="X50" s="34"/>
+      <c r="G50" s="26"/>
+      <c r="H50" s="24"/>
+      <c r="I50" s="24"/>
+      <c r="J50" s="24"/>
+      <c r="L50" s="24"/>
+      <c r="M50" s="24"/>
+      <c r="N50" s="24"/>
+      <c r="O50" s="52"/>
+      <c r="P50" s="52"/>
+      <c r="Q50" s="24"/>
+      <c r="R50" s="25"/>
+      <c r="S50" s="26"/>
+      <c r="T50" s="24"/>
+      <c r="U50" s="24"/>
+      <c r="V50" s="24"/>
+      <c r="W50" s="24"/>
+      <c r="X50" s="24"/>
       <c r="Y50" s="10"/>
       <c r="Z50" s="10"/>
       <c r="AA50" s="10"/>
       <c r="AB50" s="10"/>
       <c r="AC50" s="10"/>
       <c r="AD50" s="10"/>
-      <c r="AE50" s="10"/>
-      <c r="AF50" s="10"/>
-      <c r="AG50" s="10"/>
-      <c r="AH50" s="10"/>
-      <c r="AI50" s="10"/>
-      <c r="AJ50" s="10"/>
-      <c r="AK50" s="10"/>
-      <c r="AL50" s="10"/>
+      <c r="AE50" s="27"/>
+      <c r="AF50" s="27"/>
+      <c r="AG50" s="27"/>
+      <c r="AH50" s="27"/>
+      <c r="AI50" s="27"/>
+      <c r="AJ50" s="27"/>
+      <c r="AK50" s="27"/>
+      <c r="AL50" s="27"/>
     </row>
     <row r="51" spans="1:38" ht="12" customHeight="1">
-      <c r="A51" s="93"/>
-      <c r="B51" s="95"/>
-      <c r="C51" s="93"/>
-      <c r="D51" s="93"/>
-      <c r="E51" s="93"/>
-      <c r="F51" s="37" t="s">
+      <c r="A51" s="90"/>
+      <c r="B51" s="92"/>
+      <c r="C51" s="90"/>
+      <c r="D51" s="90"/>
+      <c r="E51" s="90"/>
+      <c r="F51" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="G51" s="47"/>
-      <c r="H51" s="48"/>
-      <c r="I51" s="48"/>
-      <c r="J51" s="48"/>
-      <c r="L51" s="48"/>
-      <c r="M51" s="48"/>
-      <c r="N51" s="48"/>
-      <c r="O51" s="48"/>
-      <c r="P51" s="48"/>
-      <c r="R51" s="49"/>
-      <c r="S51" s="47"/>
-      <c r="T51" s="48"/>
-      <c r="U51" s="48"/>
-      <c r="V51" s="48"/>
-      <c r="W51" s="48"/>
-      <c r="X51" s="48"/>
+      <c r="G51" s="29"/>
+      <c r="H51" s="30"/>
+      <c r="I51" s="30"/>
+      <c r="J51" s="30"/>
+      <c r="K51" s="83"/>
+      <c r="L51" s="30"/>
+      <c r="M51" s="30"/>
+      <c r="N51" s="30"/>
+      <c r="O51" s="30"/>
+      <c r="P51" s="30"/>
+      <c r="Q51" s="30"/>
+      <c r="R51" s="31"/>
+      <c r="S51" s="29"/>
+      <c r="T51" s="30"/>
+      <c r="U51" s="30"/>
+      <c r="V51" s="30"/>
+      <c r="W51" s="30"/>
+      <c r="X51" s="30"/>
       <c r="Y51" s="10"/>
       <c r="Z51" s="10"/>
       <c r="AA51" s="10"/>
       <c r="AB51" s="10"/>
       <c r="AC51" s="10"/>
       <c r="AD51" s="10"/>
-      <c r="AE51" s="12"/>
-      <c r="AF51" s="12"/>
-      <c r="AG51" s="12"/>
-      <c r="AH51" s="12"/>
-      <c r="AI51" s="12"/>
-      <c r="AJ51" s="12"/>
-      <c r="AK51" s="12"/>
-      <c r="AL51" s="12"/>
+      <c r="AE51" s="46"/>
+      <c r="AF51" s="46"/>
+      <c r="AG51" s="46"/>
+      <c r="AH51" s="46"/>
+      <c r="AI51" s="46"/>
+      <c r="AJ51" s="46"/>
+      <c r="AK51" s="46"/>
+      <c r="AL51" s="46"/>
     </row>
     <row r="52" spans="1:38" ht="12" customHeight="1">
-      <c r="A52" s="13" t="s">
-        <v>17</v>
+      <c r="A52" s="89">
+        <v>9</v>
       </c>
-      <c r="B52" s="14"/>
-      <c r="C52" s="15"/>
-      <c r="D52" s="16"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="18"/>
-      <c r="G52" s="19"/>
-      <c r="H52" s="16"/>
-      <c r="I52" s="16"/>
-      <c r="J52" s="16"/>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="16"/>
-      <c r="O52" s="16"/>
-      <c r="P52" s="16"/>
-      <c r="Q52" s="16"/>
-      <c r="R52" s="18"/>
-      <c r="S52" s="19"/>
-      <c r="T52" s="16"/>
-      <c r="U52" s="16"/>
-      <c r="V52" s="16"/>
-      <c r="W52" s="16"/>
-      <c r="X52" s="16"/>
+      <c r="B52" s="91"/>
+      <c r="C52" s="91"/>
+      <c r="D52" s="91"/>
+      <c r="E52" s="91"/>
+      <c r="F52" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G52" s="26"/>
+      <c r="H52" s="24"/>
+      <c r="I52" s="24"/>
+      <c r="J52" s="24"/>
+      <c r="K52" s="84"/>
+      <c r="L52" s="24"/>
+      <c r="M52" s="24"/>
+      <c r="N52" s="24"/>
+      <c r="O52" s="24"/>
+      <c r="P52" s="24"/>
+      <c r="Q52" s="24"/>
+      <c r="R52" s="25"/>
+      <c r="S52" s="26"/>
+      <c r="T52" s="24"/>
+      <c r="U52" s="24"/>
+      <c r="V52" s="24"/>
+      <c r="W52" s="24"/>
+      <c r="X52" s="24"/>
       <c r="Y52" s="10"/>
       <c r="Z52" s="10"/>
       <c r="AA52" s="10"/>
       <c r="AB52" s="10"/>
       <c r="AC52" s="10"/>
       <c r="AD52" s="10"/>
-      <c r="AE52" s="20"/>
-      <c r="AF52" s="20"/>
-      <c r="AG52" s="20"/>
-      <c r="AH52" s="20"/>
-      <c r="AI52" s="20"/>
-      <c r="AJ52" s="20"/>
-      <c r="AK52" s="20"/>
-      <c r="AL52" s="20"/>
+      <c r="AE52" s="27"/>
+      <c r="AF52" s="27"/>
+      <c r="AG52" s="27"/>
+      <c r="AH52" s="27"/>
+      <c r="AI52" s="27"/>
+      <c r="AJ52" s="27"/>
+      <c r="AK52" s="27"/>
+      <c r="AL52" s="27"/>
     </row>
     <row r="53" spans="1:38" ht="12" customHeight="1">
-      <c r="A53" s="94">
-        <v>1</v>
+      <c r="A53" s="90"/>
+      <c r="B53" s="92"/>
+      <c r="C53" s="90"/>
+      <c r="D53" s="90"/>
+      <c r="E53" s="90"/>
+      <c r="F53" s="42" t="s">
+        <v>14</v>
       </c>
-      <c r="B53" s="92" t="s">
-        <v>23</v>
-      </c>
-      <c r="C53" s="92"/>
-      <c r="D53" s="92"/>
-      <c r="E53" s="92"/>
-      <c r="F53" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G53" s="26"/>
-      <c r="H53" s="24"/>
-      <c r="I53" s="24"/>
-      <c r="J53" s="24"/>
-      <c r="K53" s="24"/>
-      <c r="L53" s="24"/>
-      <c r="M53" s="24"/>
-      <c r="N53" s="24"/>
-      <c r="O53" s="24"/>
-      <c r="P53" s="24"/>
-      <c r="Q53" s="62"/>
-      <c r="R53" s="70"/>
-      <c r="S53" s="77"/>
-      <c r="T53" s="24"/>
-      <c r="U53" s="24"/>
-      <c r="V53" s="24"/>
-      <c r="W53" s="24"/>
-      <c r="X53" s="24"/>
+      <c r="G53" s="29"/>
+      <c r="H53" s="30"/>
+      <c r="I53" s="30"/>
+      <c r="J53" s="30"/>
+      <c r="K53" s="83"/>
+      <c r="L53" s="30"/>
+      <c r="M53" s="30"/>
+      <c r="N53" s="30"/>
+      <c r="O53" s="30"/>
+      <c r="P53" s="30"/>
+      <c r="Q53" s="30"/>
+      <c r="R53" s="31"/>
+      <c r="S53" s="29"/>
+      <c r="T53" s="30"/>
+      <c r="U53" s="30"/>
+      <c r="V53" s="30"/>
+      <c r="W53" s="30"/>
+      <c r="X53" s="30"/>
       <c r="Y53" s="10"/>
       <c r="Z53" s="10"/>
       <c r="AA53" s="10"/>
       <c r="AB53" s="10"/>
       <c r="AC53" s="10"/>
       <c r="AD53" s="10"/>
-      <c r="AE53" s="27"/>
-      <c r="AF53" s="27"/>
-      <c r="AG53" s="27"/>
-      <c r="AH53" s="27"/>
-      <c r="AI53" s="27"/>
-      <c r="AJ53" s="27"/>
-      <c r="AK53" s="27"/>
-      <c r="AL53" s="27"/>
-    </row>
-    <row r="54" spans="1:38" ht="12" customHeight="1">
-      <c r="A54" s="93"/>
-      <c r="B54" s="93"/>
-      <c r="C54" s="93"/>
-      <c r="D54" s="93"/>
-      <c r="E54" s="93"/>
-      <c r="F54" s="28" t="s">
-        <v>14</v>
+      <c r="AE53" s="46"/>
+      <c r="AF53" s="46"/>
+      <c r="AG53" s="46"/>
+      <c r="AH53" s="46"/>
+      <c r="AI53" s="46"/>
+      <c r="AJ53" s="46"/>
+      <c r="AK53" s="46"/>
+      <c r="AL53" s="46"/>
+    </row>
+    <row r="54" spans="1:38" ht="11.25" customHeight="1">
+      <c r="A54" s="89">
+        <v>10</v>
       </c>
-      <c r="G54" s="29"/>
-      <c r="H54" s="30"/>
-      <c r="I54" s="30"/>
-      <c r="J54" s="30"/>
-      <c r="K54" s="30"/>
-      <c r="L54" s="30"/>
-      <c r="M54" s="30"/>
-      <c r="N54" s="30"/>
-      <c r="O54" s="30"/>
-      <c r="P54" s="30"/>
-      <c r="Q54" s="63"/>
-      <c r="R54" s="71"/>
-      <c r="S54" s="78"/>
-      <c r="T54" s="30"/>
-      <c r="U54" s="30"/>
-      <c r="V54" s="30"/>
-      <c r="W54" s="30"/>
-      <c r="X54" s="30"/>
+      <c r="B54" s="91" t="s">
+        <v>35</v>
+      </c>
+      <c r="C54" s="91"/>
+      <c r="D54" s="91"/>
+      <c r="E54" s="91"/>
+      <c r="F54" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="G54" s="36"/>
+      <c r="H54" s="34"/>
+      <c r="I54" s="34"/>
+      <c r="J54" s="34"/>
+      <c r="K54" s="84"/>
+      <c r="L54" s="34"/>
+      <c r="M54" s="34"/>
+      <c r="N54" s="34"/>
+      <c r="O54" s="34"/>
+      <c r="P54" s="34"/>
+      <c r="Q54" s="82"/>
+      <c r="R54" s="35"/>
+      <c r="S54" s="36"/>
+      <c r="T54" s="34"/>
+      <c r="U54" s="34"/>
+      <c r="V54" s="34"/>
+      <c r="W54" s="34"/>
+      <c r="X54" s="34"/>
       <c r="Y54" s="10"/>
       <c r="Z54" s="10"/>
       <c r="AA54" s="10"/>
       <c r="AB54" s="10"/>
       <c r="AC54" s="10"/>
       <c r="AD54" s="10"/>
-      <c r="AE54" s="32"/>
-      <c r="AF54" s="32"/>
-      <c r="AG54" s="32"/>
-      <c r="AH54" s="32"/>
-      <c r="AI54" s="32"/>
-      <c r="AJ54" s="32"/>
-      <c r="AK54" s="32"/>
-      <c r="AL54" s="32"/>
+      <c r="AE54" s="10"/>
+      <c r="AF54" s="10"/>
+      <c r="AG54" s="10"/>
+      <c r="AH54" s="10"/>
+      <c r="AI54" s="10"/>
+      <c r="AJ54" s="10"/>
+      <c r="AK54" s="10"/>
+      <c r="AL54" s="10"/>
     </row>
     <row r="55" spans="1:38" ht="12" customHeight="1">
-      <c r="A55" s="94">
-        <v>2</v>
+      <c r="A55" s="90"/>
+      <c r="B55" s="92"/>
+      <c r="C55" s="90"/>
+      <c r="D55" s="90"/>
+      <c r="E55" s="90"/>
+      <c r="F55" s="37" t="s">
+        <v>14</v>
       </c>
-      <c r="B55" s="92" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="92"/>
-      <c r="D55" s="92"/>
-      <c r="E55" s="92"/>
-      <c r="F55" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="G55" s="36"/>
-      <c r="H55" s="34"/>
-      <c r="I55" s="34"/>
-      <c r="J55" s="34"/>
-      <c r="K55" s="34"/>
-      <c r="L55" s="34"/>
-      <c r="M55" s="34"/>
-      <c r="N55" s="34"/>
-      <c r="O55" s="34"/>
-      <c r="P55" s="34"/>
-      <c r="Q55" s="64"/>
-      <c r="R55" s="86"/>
-      <c r="S55" s="85"/>
-      <c r="T55" s="34"/>
-      <c r="U55" s="34"/>
-      <c r="V55" s="34"/>
-      <c r="W55" s="34"/>
-      <c r="X55" s="34"/>
+      <c r="G55" s="47"/>
+      <c r="H55" s="48"/>
+      <c r="I55" s="48"/>
+      <c r="J55" s="48"/>
+      <c r="L55" s="48"/>
+      <c r="M55" s="48"/>
+      <c r="N55" s="48"/>
+      <c r="O55" s="48"/>
+      <c r="P55" s="48"/>
+      <c r="R55" s="49"/>
+      <c r="S55" s="47"/>
+      <c r="T55" s="48"/>
+      <c r="U55" s="48"/>
+      <c r="V55" s="48"/>
+      <c r="W55" s="48"/>
+      <c r="X55" s="48"/>
       <c r="Y55" s="10"/>
       <c r="Z55" s="10"/>
       <c r="AA55" s="10"/>
       <c r="AB55" s="10"/>
       <c r="AC55" s="10"/>
       <c r="AD55" s="10"/>
-      <c r="AE55" s="10"/>
-      <c r="AF55" s="10"/>
-      <c r="AG55" s="10"/>
-      <c r="AH55" s="10"/>
-      <c r="AI55" s="10"/>
-      <c r="AJ55" s="10"/>
-      <c r="AK55" s="10"/>
-      <c r="AL55" s="10"/>
+      <c r="AE55" s="12"/>
+      <c r="AF55" s="12"/>
+      <c r="AG55" s="12"/>
+      <c r="AH55" s="12"/>
+      <c r="AI55" s="12"/>
+      <c r="AJ55" s="12"/>
+      <c r="AK55" s="12"/>
+      <c r="AL55" s="12"/>
     </row>
     <row r="56" spans="1:38" ht="12" customHeight="1">
-      <c r="A56" s="93"/>
-      <c r="B56" s="93"/>
-      <c r="C56" s="93"/>
-      <c r="D56" s="93"/>
-      <c r="E56" s="93"/>
-      <c r="F56" s="37" t="s">
-        <v>14</v>
+      <c r="A56" s="13" t="s">
+        <v>17</v>
       </c>
-      <c r="G56" s="38"/>
-      <c r="H56" s="39"/>
-      <c r="I56" s="39"/>
-      <c r="J56" s="39"/>
-      <c r="K56" s="39"/>
-      <c r="L56" s="39"/>
-      <c r="M56" s="39"/>
-      <c r="N56" s="39"/>
-      <c r="O56" s="39"/>
-      <c r="P56" s="39"/>
-      <c r="Q56" s="65"/>
-      <c r="R56" s="4"/>
-      <c r="S56" s="78"/>
-      <c r="T56" s="39"/>
-      <c r="U56" s="39"/>
-      <c r="V56" s="39"/>
-      <c r="W56" s="39"/>
-      <c r="X56" s="39"/>
+      <c r="B56" s="14"/>
+      <c r="C56" s="15"/>
+      <c r="D56" s="16"/>
+      <c r="E56" s="17"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="19"/>
+      <c r="H56" s="16"/>
+      <c r="I56" s="16"/>
+      <c r="J56" s="16"/>
+      <c r="K56" s="16"/>
+      <c r="L56" s="16"/>
+      <c r="M56" s="16"/>
+      <c r="N56" s="16"/>
+      <c r="O56" s="16"/>
+      <c r="P56" s="16"/>
+      <c r="Q56" s="16"/>
+      <c r="R56" s="18"/>
+      <c r="S56" s="19"/>
+      <c r="T56" s="16"/>
+      <c r="U56" s="16"/>
+      <c r="V56" s="16"/>
+      <c r="W56" s="16"/>
+      <c r="X56" s="16"/>
       <c r="Y56" s="10"/>
       <c r="Z56" s="10"/>
       <c r="AA56" s="10"/>
       <c r="AB56" s="10"/>
       <c r="AC56" s="10"/>
       <c r="AD56" s="10"/>
-      <c r="AE56" s="41"/>
-      <c r="AF56" s="41"/>
-      <c r="AG56" s="41"/>
-      <c r="AH56" s="41"/>
-      <c r="AI56" s="41"/>
-      <c r="AJ56" s="41"/>
-      <c r="AK56" s="41"/>
-      <c r="AL56" s="41"/>
+      <c r="AE56" s="20"/>
+      <c r="AF56" s="20"/>
+      <c r="AG56" s="20"/>
+      <c r="AH56" s="20"/>
+      <c r="AI56" s="20"/>
+      <c r="AJ56" s="20"/>
+      <c r="AK56" s="20"/>
+      <c r="AL56" s="20"/>
     </row>
     <row r="57" spans="1:38" ht="12" customHeight="1">
-      <c r="A57" s="94">
-        <v>3</v>
+      <c r="A57" s="89">
+        <v>1</v>
       </c>
-      <c r="B57" s="92" t="s">
-        <v>25</v>
+      <c r="B57" s="91" t="s">
+        <v>23</v>
       </c>
-      <c r="C57" s="92"/>
-      <c r="D57" s="92"/>
-      <c r="E57" s="92"/>
+      <c r="C57" s="91"/>
+      <c r="D57" s="91"/>
+      <c r="E57" s="91"/>
       <c r="F57" s="21" t="s">
         <v>13</v>
       </c>
@@ -4380,11 +4332,11 @@
       <c r="N57" s="24"/>
       <c r="O57" s="24"/>
       <c r="P57" s="24"/>
-      <c r="Q57" s="66"/>
-      <c r="R57" s="72"/>
-      <c r="S57" s="75"/>
-      <c r="T57" s="52"/>
-      <c r="U57" s="52"/>
+      <c r="Q57" s="62"/>
+      <c r="R57" s="70"/>
+      <c r="S57" s="77"/>
+      <c r="T57" s="24"/>
+      <c r="U57" s="24"/>
       <c r="V57" s="24"/>
       <c r="W57" s="24"/>
       <c r="X57" s="24"/>
@@ -4404,32 +4356,32 @@
       <c r="AL57" s="27"/>
     </row>
     <row r="58" spans="1:38" ht="12" customHeight="1">
-      <c r="A58" s="93"/>
-      <c r="B58" s="93"/>
-      <c r="C58" s="93"/>
-      <c r="D58" s="93"/>
-      <c r="E58" s="93"/>
-      <c r="F58" s="42" t="s">
+      <c r="A58" s="90"/>
+      <c r="B58" s="90"/>
+      <c r="C58" s="90"/>
+      <c r="D58" s="90"/>
+      <c r="E58" s="90"/>
+      <c r="F58" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="G58" s="43"/>
-      <c r="H58" s="44"/>
-      <c r="I58" s="44"/>
-      <c r="J58" s="44"/>
-      <c r="K58" s="44"/>
-      <c r="L58" s="44"/>
-      <c r="M58" s="44"/>
-      <c r="N58" s="44"/>
-      <c r="O58" s="44"/>
-      <c r="P58" s="44"/>
-      <c r="Q58" s="67"/>
-      <c r="R58" s="73"/>
-      <c r="S58" s="76"/>
-      <c r="T58" s="44"/>
-      <c r="U58" s="44"/>
-      <c r="V58" s="44"/>
-      <c r="W58" s="44"/>
-      <c r="X58" s="44"/>
+      <c r="G58" s="29"/>
+      <c r="H58" s="30"/>
+      <c r="I58" s="30"/>
+      <c r="J58" s="30"/>
+      <c r="K58" s="30"/>
+      <c r="L58" s="30"/>
+      <c r="M58" s="30"/>
+      <c r="N58" s="30"/>
+      <c r="O58" s="30"/>
+      <c r="P58" s="30"/>
+      <c r="Q58" s="63"/>
+      <c r="R58" s="71"/>
+      <c r="S58" s="78"/>
+      <c r="T58" s="30"/>
+      <c r="U58" s="30"/>
+      <c r="V58" s="30"/>
+      <c r="W58" s="30"/>
+      <c r="X58" s="30"/>
       <c r="Y58" s="10"/>
       <c r="Z58" s="10"/>
       <c r="AA58" s="10"/>
@@ -4446,401 +4398,405 @@
       <c r="AL58" s="32"/>
     </row>
     <row r="59" spans="1:38" ht="12" customHeight="1">
-      <c r="A59" s="94">
-        <v>4</v>
+      <c r="A59" s="89">
+        <v>2</v>
       </c>
-      <c r="B59" s="92" t="s">
-        <v>26</v>
+      <c r="B59" s="91" t="s">
+        <v>24</v>
       </c>
-      <c r="C59" s="92"/>
-      <c r="D59" s="92"/>
-      <c r="E59" s="92"/>
-      <c r="F59" s="21" t="s">
+      <c r="C59" s="91"/>
+      <c r="D59" s="91"/>
+      <c r="E59" s="91"/>
+      <c r="F59" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="G59" s="26"/>
-      <c r="H59" s="24"/>
-      <c r="I59" s="24"/>
-      <c r="J59" s="24"/>
-      <c r="K59" s="24"/>
-      <c r="L59" s="24"/>
-      <c r="M59" s="24"/>
-      <c r="N59" s="24"/>
-      <c r="O59" s="24"/>
-      <c r="P59" s="24"/>
-      <c r="Q59" s="66"/>
-      <c r="R59" s="72"/>
-      <c r="S59" s="74"/>
-      <c r="T59" s="24"/>
-      <c r="U59" s="52"/>
-      <c r="V59" s="52"/>
-      <c r="W59" s="52"/>
-      <c r="X59" s="52"/>
+      <c r="G59" s="36"/>
+      <c r="H59" s="34"/>
+      <c r="I59" s="34"/>
+      <c r="J59" s="34"/>
+      <c r="K59" s="34"/>
+      <c r="L59" s="34"/>
+      <c r="M59" s="34"/>
+      <c r="N59" s="34"/>
+      <c r="O59" s="34"/>
+      <c r="P59" s="34"/>
+      <c r="Q59" s="64"/>
+      <c r="R59" s="81"/>
+      <c r="S59" s="80"/>
+      <c r="T59" s="34"/>
+      <c r="U59" s="34"/>
+      <c r="V59" s="34"/>
+      <c r="W59" s="34"/>
+      <c r="X59" s="34"/>
       <c r="Y59" s="10"/>
       <c r="Z59" s="10"/>
       <c r="AA59" s="10"/>
       <c r="AB59" s="10"/>
       <c r="AC59" s="10"/>
       <c r="AD59" s="10"/>
-      <c r="AE59" s="27"/>
-      <c r="AF59" s="27"/>
-      <c r="AG59" s="27"/>
-      <c r="AH59" s="27"/>
-      <c r="AI59" s="27"/>
-      <c r="AJ59" s="27"/>
-      <c r="AK59" s="27"/>
-      <c r="AL59" s="27"/>
+      <c r="AE59" s="10"/>
+      <c r="AF59" s="10"/>
+      <c r="AG59" s="10"/>
+      <c r="AH59" s="10"/>
+      <c r="AI59" s="10"/>
+      <c r="AJ59" s="10"/>
+      <c r="AK59" s="10"/>
+      <c r="AL59" s="10"/>
     </row>
     <row r="60" spans="1:38" ht="12" customHeight="1">
-      <c r="A60" s="93"/>
-      <c r="B60" s="93"/>
-      <c r="C60" s="93"/>
-      <c r="D60" s="93"/>
-      <c r="E60" s="93"/>
-      <c r="F60" s="42" t="s">
+      <c r="A60" s="90"/>
+      <c r="B60" s="90"/>
+      <c r="C60" s="90"/>
+      <c r="D60" s="90"/>
+      <c r="E60" s="90"/>
+      <c r="F60" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="G60" s="29"/>
-      <c r="H60" s="30"/>
-      <c r="I60" s="30"/>
-      <c r="J60" s="30"/>
-      <c r="K60" s="30"/>
-      <c r="L60" s="30"/>
-      <c r="M60" s="30"/>
-      <c r="N60" s="30"/>
-      <c r="O60" s="30"/>
-      <c r="P60" s="30"/>
-      <c r="Q60" s="63"/>
-      <c r="R60" s="61"/>
-      <c r="S60" s="30"/>
-      <c r="T60" s="30"/>
-      <c r="U60" s="30"/>
-      <c r="V60" s="30"/>
-      <c r="W60" s="30"/>
-      <c r="X60" s="30"/>
+      <c r="G60" s="38"/>
+      <c r="H60" s="39"/>
+      <c r="I60" s="39"/>
+      <c r="J60" s="39"/>
+      <c r="K60" s="39"/>
+      <c r="L60" s="39"/>
+      <c r="M60" s="39"/>
+      <c r="N60" s="39"/>
+      <c r="O60" s="39"/>
+      <c r="P60" s="39"/>
+      <c r="Q60" s="65"/>
+      <c r="R60" s="4"/>
+      <c r="S60" s="78"/>
+      <c r="T60" s="39"/>
+      <c r="U60" s="39"/>
+      <c r="V60" s="39"/>
+      <c r="W60" s="39"/>
+      <c r="X60" s="39"/>
       <c r="Y60" s="10"/>
       <c r="Z60" s="10"/>
       <c r="AA60" s="10"/>
       <c r="AB60" s="10"/>
       <c r="AC60" s="10"/>
       <c r="AD60" s="10"/>
-      <c r="AE60" s="46"/>
-      <c r="AF60" s="46"/>
-      <c r="AG60" s="46"/>
-      <c r="AH60" s="46"/>
-      <c r="AI60" s="46"/>
-      <c r="AJ60" s="46"/>
-      <c r="AK60" s="46"/>
-      <c r="AL60" s="46"/>
+      <c r="AE60" s="41"/>
+      <c r="AF60" s="41"/>
+      <c r="AG60" s="41"/>
+      <c r="AH60" s="41"/>
+      <c r="AI60" s="41"/>
+      <c r="AJ60" s="41"/>
+      <c r="AK60" s="41"/>
+      <c r="AL60" s="41"/>
     </row>
     <row r="61" spans="1:38" ht="12" customHeight="1">
-      <c r="A61" s="94">
-        <v>5</v>
+      <c r="A61" s="89">
+        <v>3</v>
       </c>
-      <c r="B61" s="92"/>
-      <c r="C61" s="92"/>
-      <c r="D61" s="92"/>
-      <c r="E61" s="92"/>
-      <c r="F61" s="33" t="s">
+      <c r="B61" s="91" t="s">
+        <v>25</v>
+      </c>
+      <c r="C61" s="91"/>
+      <c r="D61" s="91"/>
+      <c r="E61" s="91"/>
+      <c r="F61" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="G61" s="36"/>
-      <c r="H61" s="34"/>
-      <c r="I61" s="34"/>
-      <c r="J61" s="34"/>
-      <c r="K61" s="34"/>
-      <c r="L61" s="34"/>
-      <c r="M61" s="34"/>
-      <c r="N61" s="34"/>
-      <c r="O61" s="34"/>
-      <c r="P61" s="34"/>
-      <c r="Q61" s="34"/>
-      <c r="R61" s="35"/>
-      <c r="S61" s="55"/>
-      <c r="T61" s="34"/>
-      <c r="U61" s="34"/>
-      <c r="V61" s="34"/>
-      <c r="W61" s="34"/>
-      <c r="X61" s="34"/>
+      <c r="G61" s="26"/>
+      <c r="H61" s="24"/>
+      <c r="I61" s="24"/>
+      <c r="J61" s="24"/>
+      <c r="K61" s="24"/>
+      <c r="L61" s="24"/>
+      <c r="M61" s="24"/>
+      <c r="N61" s="24"/>
+      <c r="O61" s="24"/>
+      <c r="P61" s="24"/>
+      <c r="Q61" s="66"/>
+      <c r="R61" s="72"/>
+      <c r="S61" s="75"/>
+      <c r="T61" s="52"/>
+      <c r="U61" s="52"/>
+      <c r="V61" s="24"/>
+      <c r="W61" s="24"/>
+      <c r="X61" s="24"/>
       <c r="Y61" s="10"/>
       <c r="Z61" s="10"/>
       <c r="AA61" s="10"/>
       <c r="AB61" s="10"/>
       <c r="AC61" s="10"/>
       <c r="AD61" s="10"/>
-      <c r="AE61" s="10"/>
-      <c r="AF61" s="10"/>
-      <c r="AG61" s="10"/>
-      <c r="AH61" s="10"/>
-      <c r="AI61" s="10"/>
-      <c r="AJ61" s="10"/>
-      <c r="AK61" s="10"/>
-      <c r="AL61" s="10"/>
+      <c r="AE61" s="27"/>
+      <c r="AF61" s="27"/>
+      <c r="AG61" s="27"/>
+      <c r="AH61" s="27"/>
+      <c r="AI61" s="27"/>
+      <c r="AJ61" s="27"/>
+      <c r="AK61" s="27"/>
+      <c r="AL61" s="27"/>
     </row>
     <row r="62" spans="1:38" ht="12" customHeight="1">
-      <c r="A62" s="93"/>
-      <c r="B62" s="93"/>
-      <c r="C62" s="93"/>
-      <c r="D62" s="93"/>
-      <c r="E62" s="93"/>
-      <c r="F62" s="37" t="s">
+      <c r="A62" s="90"/>
+      <c r="B62" s="90"/>
+      <c r="C62" s="90"/>
+      <c r="D62" s="90"/>
+      <c r="E62" s="90"/>
+      <c r="F62" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="G62" s="47"/>
-      <c r="H62" s="48"/>
-      <c r="I62" s="48"/>
-      <c r="J62" s="48"/>
-      <c r="K62" s="48"/>
-      <c r="L62" s="48"/>
-      <c r="M62" s="48"/>
-      <c r="N62" s="48"/>
-      <c r="O62" s="48"/>
-      <c r="P62" s="48"/>
-      <c r="Q62" s="48"/>
-      <c r="R62" s="49"/>
-      <c r="S62" s="47"/>
-      <c r="T62" s="48"/>
-      <c r="U62" s="48"/>
-      <c r="V62" s="48"/>
-      <c r="W62" s="48"/>
-      <c r="X62" s="48"/>
+      <c r="G62" s="43"/>
+      <c r="H62" s="44"/>
+      <c r="I62" s="44"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="44"/>
+      <c r="L62" s="44"/>
+      <c r="M62" s="44"/>
+      <c r="N62" s="44"/>
+      <c r="O62" s="44"/>
+      <c r="P62" s="44"/>
+      <c r="Q62" s="67"/>
+      <c r="R62" s="73"/>
+      <c r="S62" s="76"/>
+      <c r="T62" s="44"/>
+      <c r="U62" s="44"/>
+      <c r="V62" s="44"/>
+      <c r="W62" s="44"/>
+      <c r="X62" s="44"/>
       <c r="Y62" s="10"/>
       <c r="Z62" s="10"/>
       <c r="AA62" s="10"/>
       <c r="AB62" s="10"/>
       <c r="AC62" s="10"/>
       <c r="AD62" s="10"/>
-      <c r="AE62" s="12"/>
-      <c r="AF62" s="12"/>
-      <c r="AG62" s="12"/>
-      <c r="AH62" s="12"/>
-      <c r="AI62" s="12"/>
-      <c r="AJ62" s="12"/>
-      <c r="AK62" s="12"/>
-      <c r="AL62" s="12"/>
+      <c r="AE62" s="32"/>
+      <c r="AF62" s="32"/>
+      <c r="AG62" s="32"/>
+      <c r="AH62" s="32"/>
+      <c r="AI62" s="32"/>
+      <c r="AJ62" s="32"/>
+      <c r="AK62" s="32"/>
+      <c r="AL62" s="32"/>
     </row>
     <row r="63" spans="1:38" ht="12" customHeight="1">
-      <c r="A63" s="13" t="s">
-        <v>18</v>
+      <c r="A63" s="89">
+        <v>4</v>
       </c>
-      <c r="B63" s="14"/>
-      <c r="C63" s="15"/>
-      <c r="D63" s="16"/>
-      <c r="E63" s="17"/>
-      <c r="F63" s="18"/>
-      <c r="G63" s="19"/>
-      <c r="H63" s="16"/>
-      <c r="I63" s="16"/>
-      <c r="J63" s="16"/>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
-      <c r="N63" s="16"/>
-      <c r="O63" s="16"/>
-      <c r="P63" s="16"/>
-      <c r="Q63" s="16"/>
-      <c r="R63" s="18"/>
-      <c r="S63" s="19"/>
-      <c r="T63" s="16"/>
-      <c r="U63" s="16"/>
-      <c r="V63" s="16"/>
-      <c r="W63" s="16"/>
-      <c r="X63" s="16"/>
+      <c r="B63" s="91" t="s">
+        <v>26</v>
+      </c>
+      <c r="C63" s="91"/>
+      <c r="D63" s="91"/>
+      <c r="E63" s="91"/>
+      <c r="F63" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G63" s="26"/>
+      <c r="H63" s="24"/>
+      <c r="I63" s="24"/>
+      <c r="J63" s="24"/>
+      <c r="K63" s="24"/>
+      <c r="L63" s="24"/>
+      <c r="M63" s="24"/>
+      <c r="N63" s="24"/>
+      <c r="O63" s="24"/>
+      <c r="P63" s="24"/>
+      <c r="Q63" s="66"/>
+      <c r="R63" s="72"/>
+      <c r="S63" s="74"/>
+      <c r="T63" s="24"/>
+      <c r="U63" s="52"/>
+      <c r="V63" s="52"/>
+      <c r="W63" s="52"/>
+      <c r="X63" s="52"/>
       <c r="Y63" s="10"/>
       <c r="Z63" s="10"/>
       <c r="AA63" s="10"/>
       <c r="AB63" s="10"/>
       <c r="AC63" s="10"/>
       <c r="AD63" s="10"/>
-      <c r="AE63" s="20"/>
-      <c r="AF63" s="20"/>
-      <c r="AG63" s="20"/>
-      <c r="AH63" s="20"/>
-      <c r="AI63" s="20"/>
-      <c r="AJ63" s="20"/>
-      <c r="AK63" s="20"/>
-      <c r="AL63" s="20"/>
+      <c r="AE63" s="27"/>
+      <c r="AF63" s="27"/>
+      <c r="AG63" s="27"/>
+      <c r="AH63" s="27"/>
+      <c r="AI63" s="27"/>
+      <c r="AJ63" s="27"/>
+      <c r="AK63" s="27"/>
+      <c r="AL63" s="27"/>
     </row>
     <row r="64" spans="1:38" ht="12" customHeight="1">
-      <c r="A64" s="94">
-        <v>1</v>
+      <c r="A64" s="90"/>
+      <c r="B64" s="90"/>
+      <c r="C64" s="90"/>
+      <c r="D64" s="90"/>
+      <c r="E64" s="90"/>
+      <c r="F64" s="42" t="s">
+        <v>14</v>
       </c>
-      <c r="B64" s="92"/>
-      <c r="C64" s="92"/>
-      <c r="D64" s="92"/>
-      <c r="E64" s="92"/>
-      <c r="F64" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G64" s="26"/>
-      <c r="H64" s="24"/>
-      <c r="I64" s="24"/>
-      <c r="J64" s="24"/>
-      <c r="K64" s="24"/>
-      <c r="L64" s="24"/>
-      <c r="M64" s="24"/>
-      <c r="N64" s="24"/>
-      <c r="O64" s="24"/>
-      <c r="P64" s="24"/>
-      <c r="Q64" s="24"/>
-      <c r="R64" s="25"/>
-      <c r="S64" s="26"/>
-      <c r="T64" s="24"/>
-      <c r="U64" s="24"/>
-      <c r="V64" s="24"/>
-      <c r="W64" s="24"/>
-      <c r="X64" s="24"/>
+      <c r="G64" s="29"/>
+      <c r="H64" s="30"/>
+      <c r="I64" s="30"/>
+      <c r="J64" s="30"/>
+      <c r="K64" s="30"/>
+      <c r="L64" s="30"/>
+      <c r="M64" s="30"/>
+      <c r="N64" s="30"/>
+      <c r="O64" s="30"/>
+      <c r="P64" s="30"/>
+      <c r="Q64" s="63"/>
+      <c r="R64" s="61"/>
+      <c r="S64" s="30"/>
+      <c r="T64" s="30"/>
+      <c r="U64" s="30"/>
+      <c r="V64" s="30"/>
+      <c r="W64" s="30"/>
+      <c r="X64" s="30"/>
       <c r="Y64" s="10"/>
       <c r="Z64" s="10"/>
       <c r="AA64" s="10"/>
       <c r="AB64" s="10"/>
       <c r="AC64" s="10"/>
       <c r="AD64" s="10"/>
-      <c r="AE64" s="27"/>
-      <c r="AF64" s="27"/>
-      <c r="AG64" s="27"/>
-      <c r="AH64" s="27"/>
-      <c r="AI64" s="27"/>
-      <c r="AJ64" s="27"/>
-      <c r="AK64" s="27"/>
-      <c r="AL64" s="27"/>
+      <c r="AE64" s="46"/>
+      <c r="AF64" s="46"/>
+      <c r="AG64" s="46"/>
+      <c r="AH64" s="46"/>
+      <c r="AI64" s="46"/>
+      <c r="AJ64" s="46"/>
+      <c r="AK64" s="46"/>
+      <c r="AL64" s="46"/>
     </row>
     <row r="65" spans="1:38" ht="12" customHeight="1">
-      <c r="A65" s="93"/>
-      <c r="B65" s="93"/>
-      <c r="C65" s="93"/>
-      <c r="D65" s="93"/>
-      <c r="E65" s="93"/>
-      <c r="F65" s="28" t="s">
-        <v>14</v>
+      <c r="A65" s="89">
+        <v>5</v>
       </c>
-      <c r="G65" s="29"/>
-      <c r="H65" s="30"/>
-      <c r="I65" s="30"/>
-      <c r="J65" s="30"/>
-      <c r="K65" s="30"/>
-      <c r="L65" s="30"/>
-      <c r="M65" s="30"/>
-      <c r="N65" s="30"/>
-      <c r="O65" s="30"/>
-      <c r="P65" s="30"/>
-      <c r="Q65" s="30"/>
-      <c r="R65" s="31"/>
-      <c r="S65" s="29"/>
-      <c r="T65" s="30"/>
-      <c r="U65" s="30"/>
-      <c r="V65" s="30"/>
-      <c r="W65" s="30"/>
-      <c r="X65" s="30"/>
+      <c r="B65" s="91"/>
+      <c r="C65" s="91"/>
+      <c r="D65" s="91"/>
+      <c r="E65" s="91"/>
+      <c r="F65" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="G65" s="36"/>
+      <c r="H65" s="34"/>
+      <c r="I65" s="34"/>
+      <c r="J65" s="34"/>
+      <c r="K65" s="34"/>
+      <c r="L65" s="34"/>
+      <c r="M65" s="34"/>
+      <c r="N65" s="34"/>
+      <c r="O65" s="34"/>
+      <c r="P65" s="34"/>
+      <c r="Q65" s="34"/>
+      <c r="R65" s="35"/>
+      <c r="S65" s="55"/>
+      <c r="T65" s="34"/>
+      <c r="U65" s="34"/>
+      <c r="V65" s="34"/>
+      <c r="W65" s="34"/>
+      <c r="X65" s="34"/>
       <c r="Y65" s="10"/>
       <c r="Z65" s="10"/>
       <c r="AA65" s="10"/>
       <c r="AB65" s="10"/>
       <c r="AC65" s="10"/>
       <c r="AD65" s="10"/>
-      <c r="AE65" s="32"/>
-      <c r="AF65" s="32"/>
-      <c r="AG65" s="32"/>
-      <c r="AH65" s="32"/>
-      <c r="AI65" s="32"/>
-      <c r="AJ65" s="32"/>
-      <c r="AK65" s="32"/>
-      <c r="AL65" s="32"/>
+      <c r="AE65" s="10"/>
+      <c r="AF65" s="10"/>
+      <c r="AG65" s="10"/>
+      <c r="AH65" s="10"/>
+      <c r="AI65" s="10"/>
+      <c r="AJ65" s="10"/>
+      <c r="AK65" s="10"/>
+      <c r="AL65" s="10"/>
     </row>
     <row r="66" spans="1:38" ht="12" customHeight="1">
-      <c r="A66" s="94">
-        <v>2</v>
+      <c r="A66" s="90"/>
+      <c r="B66" s="90"/>
+      <c r="C66" s="90"/>
+      <c r="D66" s="90"/>
+      <c r="E66" s="90"/>
+      <c r="F66" s="37" t="s">
+        <v>14</v>
       </c>
-      <c r="B66" s="92"/>
-      <c r="C66" s="92"/>
-      <c r="D66" s="92"/>
-      <c r="E66" s="92"/>
-      <c r="F66" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="G66" s="36"/>
-      <c r="H66" s="34"/>
-      <c r="I66" s="34"/>
-      <c r="J66" s="34"/>
-      <c r="K66" s="34"/>
-      <c r="L66" s="34"/>
-      <c r="M66" s="34"/>
-      <c r="N66" s="34"/>
-      <c r="O66" s="34"/>
-      <c r="P66" s="34"/>
-      <c r="Q66" s="34"/>
-      <c r="R66" s="35"/>
-      <c r="S66" s="36"/>
-      <c r="T66" s="34"/>
-      <c r="U66" s="34"/>
-      <c r="V66" s="34"/>
-      <c r="W66" s="34"/>
-      <c r="X66" s="34"/>
+      <c r="G66" s="47"/>
+      <c r="H66" s="48"/>
+      <c r="I66" s="48"/>
+      <c r="J66" s="48"/>
+      <c r="K66" s="48"/>
+      <c r="L66" s="48"/>
+      <c r="M66" s="48"/>
+      <c r="N66" s="48"/>
+      <c r="O66" s="48"/>
+      <c r="P66" s="48"/>
+      <c r="Q66" s="48"/>
+      <c r="R66" s="49"/>
+      <c r="S66" s="47"/>
+      <c r="T66" s="48"/>
+      <c r="U66" s="48"/>
+      <c r="V66" s="48"/>
+      <c r="W66" s="48"/>
+      <c r="X66" s="48"/>
       <c r="Y66" s="10"/>
       <c r="Z66" s="10"/>
       <c r="AA66" s="10"/>
       <c r="AB66" s="10"/>
       <c r="AC66" s="10"/>
       <c r="AD66" s="10"/>
-      <c r="AE66" s="10"/>
-      <c r="AF66" s="10"/>
-      <c r="AG66" s="10"/>
-      <c r="AH66" s="10"/>
-      <c r="AI66" s="10"/>
-      <c r="AJ66" s="10"/>
-      <c r="AK66" s="10"/>
-      <c r="AL66" s="10"/>
+      <c r="AE66" s="12"/>
+      <c r="AF66" s="12"/>
+      <c r="AG66" s="12"/>
+      <c r="AH66" s="12"/>
+      <c r="AI66" s="12"/>
+      <c r="AJ66" s="12"/>
+      <c r="AK66" s="12"/>
+      <c r="AL66" s="12"/>
     </row>
     <row r="67" spans="1:38" ht="12" customHeight="1">
-      <c r="A67" s="93"/>
-      <c r="B67" s="93"/>
-      <c r="C67" s="93"/>
-      <c r="D67" s="93"/>
-      <c r="E67" s="93"/>
-      <c r="F67" s="37" t="s">
-        <v>14</v>
+      <c r="A67" s="13" t="s">
+        <v>18</v>
       </c>
-      <c r="G67" s="38"/>
-      <c r="H67" s="39"/>
-      <c r="I67" s="39"/>
-      <c r="J67" s="39"/>
-      <c r="K67" s="39"/>
-      <c r="L67" s="39"/>
-      <c r="M67" s="39"/>
-      <c r="N67" s="39"/>
-      <c r="O67" s="39"/>
-      <c r="P67" s="39"/>
-      <c r="Q67" s="39"/>
-      <c r="R67" s="40"/>
-      <c r="S67" s="38"/>
-      <c r="T67" s="39"/>
-      <c r="U67" s="39"/>
-      <c r="V67" s="39"/>
-      <c r="W67" s="39"/>
-      <c r="X67" s="39"/>
+      <c r="B67" s="14"/>
+      <c r="C67" s="15"/>
+      <c r="D67" s="16"/>
+      <c r="E67" s="17"/>
+      <c r="F67" s="18"/>
+      <c r="G67" s="19"/>
+      <c r="H67" s="16"/>
+      <c r="I67" s="16"/>
+      <c r="J67" s="16"/>
+      <c r="K67" s="16"/>
+      <c r="L67" s="16"/>
+      <c r="M67" s="16"/>
+      <c r="N67" s="16"/>
+      <c r="O67" s="16"/>
+      <c r="P67" s="16"/>
+      <c r="Q67" s="16"/>
+      <c r="R67" s="18"/>
+      <c r="S67" s="19"/>
+      <c r="T67" s="16"/>
+      <c r="U67" s="16"/>
+      <c r="V67" s="16"/>
+      <c r="W67" s="16"/>
+      <c r="X67" s="16"/>
       <c r="Y67" s="10"/>
       <c r="Z67" s="10"/>
       <c r="AA67" s="10"/>
       <c r="AB67" s="10"/>
       <c r="AC67" s="10"/>
       <c r="AD67" s="10"/>
-      <c r="AE67" s="41"/>
-      <c r="AF67" s="41"/>
-      <c r="AG67" s="41"/>
-      <c r="AH67" s="41"/>
-      <c r="AI67" s="41"/>
-      <c r="AJ67" s="41"/>
-      <c r="AK67" s="41"/>
-      <c r="AL67" s="41"/>
+      <c r="AE67" s="20"/>
+      <c r="AF67" s="20"/>
+      <c r="AG67" s="20"/>
+      <c r="AH67" s="20"/>
+      <c r="AI67" s="20"/>
+      <c r="AJ67" s="20"/>
+      <c r="AK67" s="20"/>
+      <c r="AL67" s="20"/>
     </row>
     <row r="68" spans="1:38" ht="12" customHeight="1">
-      <c r="A68" s="94">
-        <v>3</v>
+      <c r="A68" s="89">
+        <v>1</v>
       </c>
-      <c r="B68" s="92"/>
-      <c r="C68" s="92"/>
-      <c r="D68" s="92"/>
-      <c r="E68" s="92"/>
+      <c r="B68" s="91"/>
+      <c r="C68" s="91"/>
+      <c r="D68" s="91"/>
+      <c r="E68" s="91"/>
       <c r="F68" s="21" t="s">
         <v>13</v>
       </c>
@@ -4878,32 +4834,32 @@
       <c r="AL68" s="27"/>
     </row>
     <row r="69" spans="1:38" ht="12" customHeight="1">
-      <c r="A69" s="93"/>
-      <c r="B69" s="93"/>
-      <c r="C69" s="93"/>
-      <c r="D69" s="93"/>
-      <c r="E69" s="93"/>
-      <c r="F69" s="42" t="s">
+      <c r="A69" s="90"/>
+      <c r="B69" s="90"/>
+      <c r="C69" s="90"/>
+      <c r="D69" s="90"/>
+      <c r="E69" s="90"/>
+      <c r="F69" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="G69" s="43"/>
-      <c r="H69" s="44"/>
-      <c r="I69" s="44"/>
-      <c r="J69" s="44"/>
-      <c r="K69" s="44"/>
-      <c r="L69" s="44"/>
-      <c r="M69" s="44"/>
-      <c r="N69" s="44"/>
-      <c r="O69" s="44"/>
-      <c r="P69" s="44"/>
-      <c r="Q69" s="44"/>
-      <c r="R69" s="45"/>
-      <c r="S69" s="43"/>
-      <c r="T69" s="44"/>
-      <c r="U69" s="44"/>
-      <c r="V69" s="44"/>
-      <c r="W69" s="44"/>
-      <c r="X69" s="44"/>
+      <c r="G69" s="29"/>
+      <c r="H69" s="30"/>
+      <c r="I69" s="30"/>
+      <c r="J69" s="30"/>
+      <c r="K69" s="30"/>
+      <c r="L69" s="30"/>
+      <c r="M69" s="30"/>
+      <c r="N69" s="30"/>
+      <c r="O69" s="30"/>
+      <c r="P69" s="30"/>
+      <c r="Q69" s="30"/>
+      <c r="R69" s="31"/>
+      <c r="S69" s="29"/>
+      <c r="T69" s="30"/>
+      <c r="U69" s="30"/>
+      <c r="V69" s="30"/>
+      <c r="W69" s="30"/>
+      <c r="X69" s="30"/>
       <c r="Y69" s="10"/>
       <c r="Z69" s="10"/>
       <c r="AA69" s="10"/>
@@ -4920,13 +4876,13 @@
       <c r="AL69" s="32"/>
     </row>
     <row r="70" spans="1:38" ht="12" customHeight="1">
-      <c r="A70" s="94">
-        <v>4</v>
+      <c r="A70" s="89">
+        <v>2</v>
       </c>
-      <c r="B70" s="92"/>
-      <c r="C70" s="92"/>
-      <c r="D70" s="92"/>
-      <c r="E70" s="92"/>
+      <c r="B70" s="91"/>
+      <c r="C70" s="91"/>
+      <c r="D70" s="91"/>
+      <c r="E70" s="91"/>
       <c r="F70" s="33" t="s">
         <v>13</v>
       </c>
@@ -4964,11 +4920,11 @@
       <c r="AL70" s="10"/>
     </row>
     <row r="71" spans="1:38" ht="12" customHeight="1">
-      <c r="A71" s="93"/>
-      <c r="B71" s="93"/>
-      <c r="C71" s="93"/>
-      <c r="D71" s="93"/>
-      <c r="E71" s="93"/>
+      <c r="A71" s="90"/>
+      <c r="B71" s="90"/>
+      <c r="C71" s="90"/>
+      <c r="D71" s="90"/>
+      <c r="E71" s="90"/>
       <c r="F71" s="37" t="s">
         <v>14</v>
       </c>
@@ -5006,13 +4962,13 @@
       <c r="AL71" s="41"/>
     </row>
     <row r="72" spans="1:38" ht="12" customHeight="1">
-      <c r="A72" s="94">
-        <v>5</v>
+      <c r="A72" s="89">
+        <v>3</v>
       </c>
-      <c r="B72" s="92"/>
-      <c r="C72" s="92"/>
-      <c r="D72" s="92"/>
-      <c r="E72" s="92"/>
+      <c r="B72" s="91"/>
+      <c r="C72" s="91"/>
+      <c r="D72" s="91"/>
+      <c r="E72" s="91"/>
       <c r="F72" s="21" t="s">
         <v>13</v>
       </c>
@@ -5050,55 +5006,55 @@
       <c r="AL72" s="27"/>
     </row>
     <row r="73" spans="1:38" ht="12" customHeight="1">
-      <c r="A73" s="93"/>
-      <c r="B73" s="93"/>
-      <c r="C73" s="93"/>
-      <c r="D73" s="93"/>
-      <c r="E73" s="93"/>
+      <c r="A73" s="90"/>
+      <c r="B73" s="90"/>
+      <c r="C73" s="90"/>
+      <c r="D73" s="90"/>
+      <c r="E73" s="90"/>
       <c r="F73" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="G73" s="29"/>
-      <c r="H73" s="30"/>
-      <c r="I73" s="30"/>
-      <c r="J73" s="30"/>
-      <c r="K73" s="30"/>
-      <c r="L73" s="30"/>
-      <c r="M73" s="30"/>
-      <c r="N73" s="30"/>
-      <c r="O73" s="30"/>
-      <c r="P73" s="30"/>
-      <c r="Q73" s="30"/>
-      <c r="R73" s="31"/>
-      <c r="S73" s="29"/>
-      <c r="T73" s="30"/>
-      <c r="U73" s="30"/>
-      <c r="V73" s="30"/>
-      <c r="W73" s="30"/>
-      <c r="X73" s="30"/>
+      <c r="G73" s="43"/>
+      <c r="H73" s="44"/>
+      <c r="I73" s="44"/>
+      <c r="J73" s="44"/>
+      <c r="K73" s="44"/>
+      <c r="L73" s="44"/>
+      <c r="M73" s="44"/>
+      <c r="N73" s="44"/>
+      <c r="O73" s="44"/>
+      <c r="P73" s="44"/>
+      <c r="Q73" s="44"/>
+      <c r="R73" s="45"/>
+      <c r="S73" s="43"/>
+      <c r="T73" s="44"/>
+      <c r="U73" s="44"/>
+      <c r="V73" s="44"/>
+      <c r="W73" s="44"/>
+      <c r="X73" s="44"/>
       <c r="Y73" s="10"/>
       <c r="Z73" s="10"/>
       <c r="AA73" s="10"/>
       <c r="AB73" s="10"/>
       <c r="AC73" s="10"/>
       <c r="AD73" s="10"/>
-      <c r="AE73" s="46"/>
-      <c r="AF73" s="46"/>
-      <c r="AG73" s="46"/>
-      <c r="AH73" s="46"/>
-      <c r="AI73" s="46"/>
-      <c r="AJ73" s="46"/>
-      <c r="AK73" s="46"/>
-      <c r="AL73" s="46"/>
+      <c r="AE73" s="32"/>
+      <c r="AF73" s="32"/>
+      <c r="AG73" s="32"/>
+      <c r="AH73" s="32"/>
+      <c r="AI73" s="32"/>
+      <c r="AJ73" s="32"/>
+      <c r="AK73" s="32"/>
+      <c r="AL73" s="32"/>
     </row>
     <row r="74" spans="1:38" ht="12" customHeight="1">
-      <c r="A74" s="94">
-        <v>6</v>
+      <c r="A74" s="89">
+        <v>4</v>
       </c>
-      <c r="B74" s="92"/>
-      <c r="C74" s="92"/>
-      <c r="D74" s="92"/>
-      <c r="E74" s="92"/>
+      <c r="B74" s="91"/>
+      <c r="C74" s="91"/>
+      <c r="D74" s="91"/>
+      <c r="E74" s="91"/>
       <c r="F74" s="33" t="s">
         <v>13</v>
       </c>
@@ -5136,267 +5092,267 @@
       <c r="AL74" s="10"/>
     </row>
     <row r="75" spans="1:38" ht="12" customHeight="1">
-      <c r="A75" s="93"/>
-      <c r="B75" s="93"/>
-      <c r="C75" s="93"/>
-      <c r="D75" s="93"/>
-      <c r="E75" s="93"/>
+      <c r="A75" s="90"/>
+      <c r="B75" s="90"/>
+      <c r="C75" s="90"/>
+      <c r="D75" s="90"/>
+      <c r="E75" s="90"/>
       <c r="F75" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="G75" s="47"/>
-      <c r="H75" s="48"/>
-      <c r="I75" s="48"/>
-      <c r="J75" s="48"/>
-      <c r="K75" s="48"/>
-      <c r="L75" s="48"/>
-      <c r="M75" s="48"/>
-      <c r="N75" s="48"/>
-      <c r="O75" s="48"/>
-      <c r="P75" s="48"/>
-      <c r="Q75" s="48"/>
-      <c r="R75" s="49"/>
-      <c r="S75" s="47"/>
-      <c r="T75" s="48"/>
-      <c r="U75" s="48"/>
-      <c r="V75" s="48"/>
-      <c r="W75" s="48"/>
-      <c r="X75" s="48"/>
+      <c r="G75" s="38"/>
+      <c r="H75" s="39"/>
+      <c r="I75" s="39"/>
+      <c r="J75" s="39"/>
+      <c r="K75" s="39"/>
+      <c r="L75" s="39"/>
+      <c r="M75" s="39"/>
+      <c r="N75" s="39"/>
+      <c r="O75" s="39"/>
+      <c r="P75" s="39"/>
+      <c r="Q75" s="39"/>
+      <c r="R75" s="40"/>
+      <c r="S75" s="38"/>
+      <c r="T75" s="39"/>
+      <c r="U75" s="39"/>
+      <c r="V75" s="39"/>
+      <c r="W75" s="39"/>
+      <c r="X75" s="39"/>
       <c r="Y75" s="10"/>
       <c r="Z75" s="10"/>
       <c r="AA75" s="10"/>
       <c r="AB75" s="10"/>
       <c r="AC75" s="10"/>
       <c r="AD75" s="10"/>
-      <c r="AE75" s="12"/>
-      <c r="AF75" s="12"/>
-      <c r="AG75" s="12"/>
-      <c r="AH75" s="12"/>
-      <c r="AI75" s="12"/>
-      <c r="AJ75" s="12"/>
-      <c r="AK75" s="12"/>
-      <c r="AL75" s="12"/>
+      <c r="AE75" s="41"/>
+      <c r="AF75" s="41"/>
+      <c r="AG75" s="41"/>
+      <c r="AH75" s="41"/>
+      <c r="AI75" s="41"/>
+      <c r="AJ75" s="41"/>
+      <c r="AK75" s="41"/>
+      <c r="AL75" s="41"/>
     </row>
     <row r="76" spans="1:38" ht="12" customHeight="1">
-      <c r="A76" s="13"/>
-      <c r="B76" s="14"/>
-      <c r="C76" s="15"/>
-      <c r="D76" s="16"/>
-      <c r="E76" s="17"/>
-      <c r="F76" s="18"/>
-      <c r="G76" s="19"/>
-      <c r="H76" s="16"/>
-      <c r="I76" s="16"/>
-      <c r="J76" s="16"/>
-      <c r="K76" s="16"/>
-      <c r="L76" s="16"/>
-      <c r="M76" s="16"/>
-      <c r="N76" s="16"/>
-      <c r="O76" s="16"/>
-      <c r="P76" s="16"/>
-      <c r="Q76" s="16"/>
-      <c r="R76" s="18"/>
-      <c r="S76" s="19"/>
-      <c r="T76" s="16"/>
-      <c r="U76" s="16"/>
-      <c r="V76" s="16"/>
-      <c r="W76" s="16"/>
-      <c r="X76" s="16"/>
+      <c r="A76" s="89">
+        <v>5</v>
+      </c>
+      <c r="B76" s="91"/>
+      <c r="C76" s="91"/>
+      <c r="D76" s="91"/>
+      <c r="E76" s="91"/>
+      <c r="F76" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G76" s="26"/>
+      <c r="H76" s="24"/>
+      <c r="I76" s="24"/>
+      <c r="J76" s="24"/>
+      <c r="K76" s="24"/>
+      <c r="L76" s="24"/>
+      <c r="M76" s="24"/>
+      <c r="N76" s="24"/>
+      <c r="O76" s="24"/>
+      <c r="P76" s="24"/>
+      <c r="Q76" s="24"/>
+      <c r="R76" s="25"/>
+      <c r="S76" s="26"/>
+      <c r="T76" s="24"/>
+      <c r="U76" s="24"/>
+      <c r="V76" s="24"/>
+      <c r="W76" s="24"/>
+      <c r="X76" s="24"/>
       <c r="Y76" s="10"/>
       <c r="Z76" s="10"/>
       <c r="AA76" s="10"/>
       <c r="AB76" s="10"/>
       <c r="AC76" s="10"/>
       <c r="AD76" s="10"/>
-      <c r="AE76" s="20"/>
-      <c r="AF76" s="20"/>
-      <c r="AG76" s="20"/>
-      <c r="AH76" s="20"/>
-      <c r="AI76" s="20"/>
-      <c r="AJ76" s="20"/>
-      <c r="AK76" s="20"/>
-      <c r="AL76" s="20"/>
+      <c r="AE76" s="27"/>
+      <c r="AF76" s="27"/>
+      <c r="AG76" s="27"/>
+      <c r="AH76" s="27"/>
+      <c r="AI76" s="27"/>
+      <c r="AJ76" s="27"/>
+      <c r="AK76" s="27"/>
+      <c r="AL76" s="27"/>
     </row>
     <row r="77" spans="1:38" ht="12" customHeight="1">
-      <c r="A77" s="94">
-        <v>1</v>
+      <c r="A77" s="90"/>
+      <c r="B77" s="90"/>
+      <c r="C77" s="90"/>
+      <c r="D77" s="90"/>
+      <c r="E77" s="90"/>
+      <c r="F77" s="42" t="s">
+        <v>14</v>
       </c>
-      <c r="B77" s="92"/>
-      <c r="C77" s="92"/>
-      <c r="D77" s="92"/>
-      <c r="E77" s="92"/>
-      <c r="F77" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G77" s="26"/>
-      <c r="H77" s="24"/>
-      <c r="I77" s="24"/>
-      <c r="J77" s="24"/>
-      <c r="K77" s="24"/>
-      <c r="L77" s="24"/>
-      <c r="M77" s="24"/>
-      <c r="N77" s="24"/>
-      <c r="O77" s="24"/>
-      <c r="P77" s="24"/>
-      <c r="Q77" s="24"/>
-      <c r="R77" s="25"/>
-      <c r="S77" s="26"/>
-      <c r="T77" s="24"/>
-      <c r="U77" s="24"/>
-      <c r="V77" s="24"/>
-      <c r="W77" s="24"/>
-      <c r="X77" s="24"/>
+      <c r="G77" s="29"/>
+      <c r="H77" s="30"/>
+      <c r="I77" s="30"/>
+      <c r="J77" s="30"/>
+      <c r="K77" s="30"/>
+      <c r="L77" s="30"/>
+      <c r="M77" s="30"/>
+      <c r="N77" s="30"/>
+      <c r="O77" s="30"/>
+      <c r="P77" s="30"/>
+      <c r="Q77" s="30"/>
+      <c r="R77" s="31"/>
+      <c r="S77" s="29"/>
+      <c r="T77" s="30"/>
+      <c r="U77" s="30"/>
+      <c r="V77" s="30"/>
+      <c r="W77" s="30"/>
+      <c r="X77" s="30"/>
       <c r="Y77" s="10"/>
       <c r="Z77" s="10"/>
       <c r="AA77" s="10"/>
       <c r="AB77" s="10"/>
       <c r="AC77" s="10"/>
       <c r="AD77" s="10"/>
-      <c r="AE77" s="27"/>
-      <c r="AF77" s="27"/>
-      <c r="AG77" s="27"/>
-      <c r="AH77" s="27"/>
-      <c r="AI77" s="27"/>
-      <c r="AJ77" s="27"/>
-      <c r="AK77" s="27"/>
-      <c r="AL77" s="27"/>
+      <c r="AE77" s="46"/>
+      <c r="AF77" s="46"/>
+      <c r="AG77" s="46"/>
+      <c r="AH77" s="46"/>
+      <c r="AI77" s="46"/>
+      <c r="AJ77" s="46"/>
+      <c r="AK77" s="46"/>
+      <c r="AL77" s="46"/>
     </row>
     <row r="78" spans="1:38" ht="12" customHeight="1">
-      <c r="A78" s="93"/>
-      <c r="B78" s="93"/>
-      <c r="C78" s="93"/>
-      <c r="D78" s="93"/>
-      <c r="E78" s="93"/>
-      <c r="F78" s="28" t="s">
-        <v>14</v>
+      <c r="A78" s="89">
+        <v>6</v>
       </c>
-      <c r="G78" s="29"/>
-      <c r="H78" s="30"/>
-      <c r="I78" s="30"/>
-      <c r="J78" s="30"/>
-      <c r="K78" s="30"/>
-      <c r="L78" s="30"/>
-      <c r="M78" s="30"/>
-      <c r="N78" s="30"/>
-      <c r="O78" s="30"/>
-      <c r="P78" s="30"/>
-      <c r="Q78" s="30"/>
-      <c r="R78" s="31"/>
-      <c r="S78" s="29"/>
-      <c r="T78" s="30"/>
-      <c r="U78" s="30"/>
-      <c r="V78" s="30"/>
-      <c r="W78" s="30"/>
-      <c r="X78" s="30"/>
+      <c r="B78" s="91"/>
+      <c r="C78" s="91"/>
+      <c r="D78" s="91"/>
+      <c r="E78" s="91"/>
+      <c r="F78" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="G78" s="36"/>
+      <c r="H78" s="34"/>
+      <c r="I78" s="34"/>
+      <c r="J78" s="34"/>
+      <c r="K78" s="34"/>
+      <c r="L78" s="34"/>
+      <c r="M78" s="34"/>
+      <c r="N78" s="34"/>
+      <c r="O78" s="34"/>
+      <c r="P78" s="34"/>
+      <c r="Q78" s="34"/>
+      <c r="R78" s="35"/>
+      <c r="S78" s="36"/>
+      <c r="T78" s="34"/>
+      <c r="U78" s="34"/>
+      <c r="V78" s="34"/>
+      <c r="W78" s="34"/>
+      <c r="X78" s="34"/>
       <c r="Y78" s="10"/>
       <c r="Z78" s="10"/>
       <c r="AA78" s="10"/>
       <c r="AB78" s="10"/>
       <c r="AC78" s="10"/>
       <c r="AD78" s="10"/>
-      <c r="AE78" s="32"/>
-      <c r="AF78" s="32"/>
-      <c r="AG78" s="32"/>
-      <c r="AH78" s="32"/>
-      <c r="AI78" s="32"/>
-      <c r="AJ78" s="32"/>
-      <c r="AK78" s="32"/>
-      <c r="AL78" s="32"/>
+      <c r="AE78" s="10"/>
+      <c r="AF78" s="10"/>
+      <c r="AG78" s="10"/>
+      <c r="AH78" s="10"/>
+      <c r="AI78" s="10"/>
+      <c r="AJ78" s="10"/>
+      <c r="AK78" s="10"/>
+      <c r="AL78" s="10"/>
     </row>
     <row r="79" spans="1:38" ht="12" customHeight="1">
-      <c r="A79" s="94">
-        <v>2</v>
+      <c r="A79" s="90"/>
+      <c r="B79" s="90"/>
+      <c r="C79" s="90"/>
+      <c r="D79" s="90"/>
+      <c r="E79" s="90"/>
+      <c r="F79" s="37" t="s">
+        <v>14</v>
       </c>
-      <c r="B79" s="92"/>
-      <c r="C79" s="92"/>
-      <c r="D79" s="92"/>
-      <c r="E79" s="92"/>
-      <c r="F79" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="G79" s="36"/>
-      <c r="H79" s="34"/>
-      <c r="I79" s="34"/>
-      <c r="J79" s="34"/>
-      <c r="K79" s="34"/>
-      <c r="L79" s="34"/>
-      <c r="M79" s="34"/>
-      <c r="N79" s="34"/>
-      <c r="O79" s="34"/>
-      <c r="P79" s="34"/>
-      <c r="Q79" s="34"/>
-      <c r="R79" s="35"/>
-      <c r="S79" s="36"/>
-      <c r="T79" s="34"/>
-      <c r="U79" s="34"/>
-      <c r="V79" s="34"/>
-      <c r="W79" s="34"/>
-      <c r="X79" s="34"/>
+      <c r="G79" s="47"/>
+      <c r="H79" s="48"/>
+      <c r="I79" s="48"/>
+      <c r="J79" s="48"/>
+      <c r="K79" s="48"/>
+      <c r="L79" s="48"/>
+      <c r="M79" s="48"/>
+      <c r="N79" s="48"/>
+      <c r="O79" s="48"/>
+      <c r="P79" s="48"/>
+      <c r="Q79" s="48"/>
+      <c r="R79" s="49"/>
+      <c r="S79" s="47"/>
+      <c r="T79" s="48"/>
+      <c r="U79" s="48"/>
+      <c r="V79" s="48"/>
+      <c r="W79" s="48"/>
+      <c r="X79" s="48"/>
       <c r="Y79" s="10"/>
       <c r="Z79" s="10"/>
       <c r="AA79" s="10"/>
       <c r="AB79" s="10"/>
       <c r="AC79" s="10"/>
       <c r="AD79" s="10"/>
-      <c r="AE79" s="10"/>
-      <c r="AF79" s="10"/>
-      <c r="AG79" s="10"/>
-      <c r="AH79" s="10"/>
-      <c r="AI79" s="10"/>
-      <c r="AJ79" s="10"/>
-      <c r="AK79" s="10"/>
-      <c r="AL79" s="10"/>
+      <c r="AE79" s="12"/>
+      <c r="AF79" s="12"/>
+      <c r="AG79" s="12"/>
+      <c r="AH79" s="12"/>
+      <c r="AI79" s="12"/>
+      <c r="AJ79" s="12"/>
+      <c r="AK79" s="12"/>
+      <c r="AL79" s="12"/>
     </row>
     <row r="80" spans="1:38" ht="12" customHeight="1">
-      <c r="A80" s="93"/>
-      <c r="B80" s="93"/>
-      <c r="C80" s="93"/>
-      <c r="D80" s="93"/>
-      <c r="E80" s="93"/>
-      <c r="F80" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="G80" s="38"/>
-      <c r="H80" s="39"/>
-      <c r="I80" s="39"/>
-      <c r="J80" s="39"/>
-      <c r="K80" s="39"/>
-      <c r="L80" s="39"/>
-      <c r="M80" s="39"/>
-      <c r="N80" s="39"/>
-      <c r="O80" s="39"/>
-      <c r="P80" s="39"/>
-      <c r="Q80" s="39"/>
-      <c r="R80" s="40"/>
-      <c r="S80" s="38"/>
-      <c r="T80" s="39"/>
-      <c r="U80" s="39"/>
-      <c r="V80" s="39"/>
-      <c r="W80" s="39"/>
-      <c r="X80" s="39"/>
+      <c r="A80" s="13"/>
+      <c r="B80" s="14"/>
+      <c r="C80" s="15"/>
+      <c r="D80" s="16"/>
+      <c r="E80" s="17"/>
+      <c r="F80" s="18"/>
+      <c r="G80" s="19"/>
+      <c r="H80" s="16"/>
+      <c r="I80" s="16"/>
+      <c r="J80" s="16"/>
+      <c r="K80" s="16"/>
+      <c r="L80" s="16"/>
+      <c r="M80" s="16"/>
+      <c r="N80" s="16"/>
+      <c r="O80" s="16"/>
+      <c r="P80" s="16"/>
+      <c r="Q80" s="16"/>
+      <c r="R80" s="18"/>
+      <c r="S80" s="19"/>
+      <c r="T80" s="16"/>
+      <c r="U80" s="16"/>
+      <c r="V80" s="16"/>
+      <c r="W80" s="16"/>
+      <c r="X80" s="16"/>
       <c r="Y80" s="10"/>
       <c r="Z80" s="10"/>
       <c r="AA80" s="10"/>
       <c r="AB80" s="10"/>
       <c r="AC80" s="10"/>
       <c r="AD80" s="10"/>
-      <c r="AE80" s="41"/>
-      <c r="AF80" s="41"/>
-      <c r="AG80" s="41"/>
-      <c r="AH80" s="41"/>
-      <c r="AI80" s="41"/>
-      <c r="AJ80" s="41"/>
-      <c r="AK80" s="41"/>
-      <c r="AL80" s="41"/>
+      <c r="AE80" s="20"/>
+      <c r="AF80" s="20"/>
+      <c r="AG80" s="20"/>
+      <c r="AH80" s="20"/>
+      <c r="AI80" s="20"/>
+      <c r="AJ80" s="20"/>
+      <c r="AK80" s="20"/>
+      <c r="AL80" s="20"/>
     </row>
     <row r="81" spans="1:38" ht="12" customHeight="1">
-      <c r="A81" s="94">
-        <v>3</v>
+      <c r="A81" s="89">
+        <v>1</v>
       </c>
-      <c r="B81" s="92"/>
-      <c r="C81" s="92"/>
-      <c r="D81" s="92"/>
-      <c r="E81" s="92"/>
+      <c r="B81" s="91"/>
+      <c r="C81" s="91"/>
+      <c r="D81" s="91"/>
+      <c r="E81" s="91"/>
       <c r="F81" s="21" t="s">
         <v>13</v>
       </c>
@@ -5434,32 +5390,32 @@
       <c r="AL81" s="27"/>
     </row>
     <row r="82" spans="1:38" ht="12" customHeight="1">
-      <c r="A82" s="93"/>
-      <c r="B82" s="93"/>
-      <c r="C82" s="93"/>
-      <c r="D82" s="93"/>
-      <c r="E82" s="93"/>
-      <c r="F82" s="42" t="s">
+      <c r="A82" s="90"/>
+      <c r="B82" s="90"/>
+      <c r="C82" s="90"/>
+      <c r="D82" s="90"/>
+      <c r="E82" s="90"/>
+      <c r="F82" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="G82" s="43"/>
-      <c r="H82" s="44"/>
-      <c r="I82" s="44"/>
-      <c r="J82" s="44"/>
-      <c r="K82" s="44"/>
-      <c r="L82" s="44"/>
-      <c r="M82" s="44"/>
-      <c r="N82" s="44"/>
-      <c r="O82" s="44"/>
-      <c r="P82" s="44"/>
-      <c r="Q82" s="44"/>
-      <c r="R82" s="45"/>
-      <c r="S82" s="43"/>
-      <c r="T82" s="44"/>
-      <c r="U82" s="44"/>
-      <c r="V82" s="44"/>
-      <c r="W82" s="44"/>
-      <c r="X82" s="44"/>
+      <c r="G82" s="29"/>
+      <c r="H82" s="30"/>
+      <c r="I82" s="30"/>
+      <c r="J82" s="30"/>
+      <c r="K82" s="30"/>
+      <c r="L82" s="30"/>
+      <c r="M82" s="30"/>
+      <c r="N82" s="30"/>
+      <c r="O82" s="30"/>
+      <c r="P82" s="30"/>
+      <c r="Q82" s="30"/>
+      <c r="R82" s="31"/>
+      <c r="S82" s="29"/>
+      <c r="T82" s="30"/>
+      <c r="U82" s="30"/>
+      <c r="V82" s="30"/>
+      <c r="W82" s="30"/>
+      <c r="X82" s="30"/>
       <c r="Y82" s="10"/>
       <c r="Z82" s="10"/>
       <c r="AA82" s="10"/>
@@ -5476,13 +5432,13 @@
       <c r="AL82" s="32"/>
     </row>
     <row r="83" spans="1:38" ht="12" customHeight="1">
-      <c r="A83" s="94">
-        <v>4</v>
+      <c r="A83" s="89">
+        <v>2</v>
       </c>
-      <c r="B83" s="92"/>
-      <c r="C83" s="92"/>
-      <c r="D83" s="92"/>
-      <c r="E83" s="92"/>
+      <c r="B83" s="91"/>
+      <c r="C83" s="91"/>
+      <c r="D83" s="91"/>
+      <c r="E83" s="91"/>
       <c r="F83" s="33" t="s">
         <v>13</v>
       </c>
@@ -5520,206 +5476,218 @@
       <c r="AL83" s="10"/>
     </row>
     <row r="84" spans="1:38" ht="12" customHeight="1">
-      <c r="A84" s="93"/>
-      <c r="B84" s="93"/>
-      <c r="C84" s="93"/>
-      <c r="D84" s="93"/>
-      <c r="E84" s="93"/>
-      <c r="F84" s="42" t="s">
+      <c r="A84" s="90"/>
+      <c r="B84" s="90"/>
+      <c r="C84" s="90"/>
+      <c r="D84" s="90"/>
+      <c r="E84" s="90"/>
+      <c r="F84" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="G84" s="43"/>
-      <c r="H84" s="44"/>
-      <c r="I84" s="44"/>
-      <c r="J84" s="44"/>
-      <c r="K84" s="44"/>
-      <c r="L84" s="44"/>
-      <c r="M84" s="44"/>
-      <c r="N84" s="44"/>
-      <c r="O84" s="44"/>
-      <c r="P84" s="44"/>
-      <c r="Q84" s="44"/>
-      <c r="R84" s="45"/>
-      <c r="S84" s="43"/>
-      <c r="T84" s="44"/>
-      <c r="U84" s="44"/>
-      <c r="V84" s="44"/>
-      <c r="W84" s="44"/>
-      <c r="X84" s="44"/>
+      <c r="G84" s="38"/>
+      <c r="H84" s="39"/>
+      <c r="I84" s="39"/>
+      <c r="J84" s="39"/>
+      <c r="K84" s="39"/>
+      <c r="L84" s="39"/>
+      <c r="M84" s="39"/>
+      <c r="N84" s="39"/>
+      <c r="O84" s="39"/>
+      <c r="P84" s="39"/>
+      <c r="Q84" s="39"/>
+      <c r="R84" s="40"/>
+      <c r="S84" s="38"/>
+      <c r="T84" s="39"/>
+      <c r="U84" s="39"/>
+      <c r="V84" s="39"/>
+      <c r="W84" s="39"/>
+      <c r="X84" s="39"/>
       <c r="Y84" s="10"/>
       <c r="Z84" s="10"/>
       <c r="AA84" s="10"/>
       <c r="AB84" s="10"/>
       <c r="AC84" s="10"/>
       <c r="AD84" s="10"/>
-      <c r="AE84" s="32"/>
-      <c r="AF84" s="32"/>
-      <c r="AG84" s="32"/>
-      <c r="AH84" s="32"/>
-      <c r="AI84" s="32"/>
-      <c r="AJ84" s="32"/>
-      <c r="AK84" s="32"/>
-      <c r="AL84" s="32"/>
-    </row>
-    <row r="85" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A85" s="6"/>
-      <c r="B85" s="2"/>
-      <c r="C85" s="3"/>
-      <c r="D85" s="4"/>
-      <c r="E85" s="4"/>
-      <c r="F85" s="4"/>
-      <c r="G85" s="2"/>
-      <c r="H85" s="2"/>
-      <c r="I85" s="2"/>
-      <c r="J85" s="2"/>
-      <c r="K85" s="2"/>
-      <c r="L85" s="2"/>
-      <c r="M85" s="2"/>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
-      <c r="P85" s="2"/>
-      <c r="Q85" s="2"/>
-      <c r="R85" s="2"/>
-      <c r="S85" s="2"/>
-      <c r="T85" s="2"/>
-      <c r="U85" s="2"/>
-      <c r="V85" s="2"/>
-      <c r="W85" s="2"/>
-      <c r="X85" s="2"/>
-      <c r="Y85" s="2"/>
-      <c r="Z85" s="2"/>
-      <c r="AA85" s="2"/>
-      <c r="AB85" s="2"/>
-      <c r="AC85" s="2"/>
-      <c r="AD85" s="2"/>
-      <c r="AE85" s="2"/>
-      <c r="AF85" s="2"/>
-      <c r="AG85" s="2"/>
-      <c r="AH85" s="2"/>
-      <c r="AI85" s="2"/>
-      <c r="AJ85" s="2"/>
-      <c r="AK85" s="2"/>
-      <c r="AL85" s="2"/>
-    </row>
-    <row r="86" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A86" s="6"/>
-      <c r="B86" s="2"/>
-      <c r="C86" s="3"/>
-      <c r="D86" s="4"/>
-      <c r="E86" s="4"/>
-      <c r="F86" s="4"/>
-      <c r="G86" s="2"/>
-      <c r="H86" s="2"/>
-      <c r="I86" s="2"/>
-      <c r="J86" s="2"/>
-      <c r="K86" s="2"/>
-      <c r="L86" s="2"/>
-      <c r="M86" s="2"/>
-      <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
-      <c r="P86" s="2"/>
-      <c r="Q86" s="2"/>
-      <c r="R86" s="2"/>
-      <c r="S86" s="2"/>
-      <c r="T86" s="2"/>
-      <c r="U86" s="2"/>
-      <c r="V86" s="2"/>
-      <c r="W86" s="2"/>
-      <c r="X86" s="2"/>
-      <c r="Y86" s="2"/>
-      <c r="Z86" s="2"/>
-      <c r="AA86" s="2"/>
-      <c r="AB86" s="2"/>
-      <c r="AC86" s="2"/>
-      <c r="AD86" s="2"/>
-      <c r="AE86" s="2"/>
-      <c r="AF86" s="2"/>
-      <c r="AG86" s="2"/>
-      <c r="AH86" s="2"/>
-      <c r="AI86" s="2"/>
-      <c r="AJ86" s="2"/>
-      <c r="AK86" s="2"/>
-      <c r="AL86" s="2"/>
-    </row>
-    <row r="87" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A87" s="6"/>
-      <c r="B87" s="2"/>
-      <c r="C87" s="3"/>
-      <c r="D87" s="4"/>
-      <c r="E87" s="4"/>
-      <c r="F87" s="4"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="2"/>
-      <c r="I87" s="2"/>
-      <c r="J87" s="2"/>
-      <c r="K87" s="2"/>
-      <c r="L87" s="2"/>
-      <c r="M87" s="2"/>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
-      <c r="P87" s="2"/>
-      <c r="Q87" s="2"/>
-      <c r="R87" s="2"/>
-      <c r="S87" s="2"/>
-      <c r="T87" s="2"/>
-      <c r="U87" s="2"/>
-      <c r="V87" s="2"/>
-      <c r="W87" s="2"/>
-      <c r="X87" s="2"/>
-      <c r="Y87" s="2"/>
-      <c r="Z87" s="2"/>
-      <c r="AA87" s="2"/>
-      <c r="AB87" s="2"/>
-      <c r="AC87" s="2"/>
-      <c r="AD87" s="2"/>
-      <c r="AE87" s="2"/>
-      <c r="AF87" s="2"/>
-      <c r="AG87" s="2"/>
-      <c r="AH87" s="2"/>
-      <c r="AI87" s="2"/>
-      <c r="AJ87" s="2"/>
-      <c r="AK87" s="2"/>
-      <c r="AL87" s="2"/>
-    </row>
-    <row r="88" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A88" s="6"/>
-      <c r="B88" s="2"/>
-      <c r="C88" s="3"/>
-      <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
-      <c r="F88" s="4"/>
-      <c r="G88" s="2"/>
-      <c r="H88" s="2"/>
-      <c r="I88" s="2"/>
-      <c r="J88" s="2"/>
-      <c r="K88" s="2"/>
-      <c r="L88" s="2"/>
-      <c r="M88" s="2"/>
-      <c r="N88" s="2"/>
-      <c r="O88" s="2"/>
-      <c r="P88" s="2"/>
-      <c r="Q88" s="2"/>
-      <c r="R88" s="2"/>
-      <c r="S88" s="2"/>
-      <c r="T88" s="2"/>
-      <c r="U88" s="2"/>
-      <c r="V88" s="2"/>
-      <c r="W88" s="2"/>
-      <c r="X88" s="2"/>
-      <c r="Y88" s="2"/>
-      <c r="Z88" s="2"/>
-      <c r="AA88" s="2"/>
-      <c r="AB88" s="2"/>
-      <c r="AC88" s="2"/>
-      <c r="AD88" s="2"/>
-      <c r="AE88" s="2"/>
-      <c r="AF88" s="2"/>
-      <c r="AG88" s="2"/>
-      <c r="AH88" s="2"/>
-      <c r="AI88" s="2"/>
-      <c r="AJ88" s="2"/>
-      <c r="AK88" s="2"/>
-      <c r="AL88" s="2"/>
+      <c r="AE84" s="41"/>
+      <c r="AF84" s="41"/>
+      <c r="AG84" s="41"/>
+      <c r="AH84" s="41"/>
+      <c r="AI84" s="41"/>
+      <c r="AJ84" s="41"/>
+      <c r="AK84" s="41"/>
+      <c r="AL84" s="41"/>
+    </row>
+    <row r="85" spans="1:38" ht="12" customHeight="1">
+      <c r="A85" s="89">
+        <v>3</v>
+      </c>
+      <c r="B85" s="91"/>
+      <c r="C85" s="91"/>
+      <c r="D85" s="91"/>
+      <c r="E85" s="91"/>
+      <c r="F85" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G85" s="26"/>
+      <c r="H85" s="24"/>
+      <c r="I85" s="24"/>
+      <c r="J85" s="24"/>
+      <c r="K85" s="24"/>
+      <c r="L85" s="24"/>
+      <c r="M85" s="24"/>
+      <c r="N85" s="24"/>
+      <c r="O85" s="24"/>
+      <c r="P85" s="24"/>
+      <c r="Q85" s="24"/>
+      <c r="R85" s="25"/>
+      <c r="S85" s="26"/>
+      <c r="T85" s="24"/>
+      <c r="U85" s="24"/>
+      <c r="V85" s="24"/>
+      <c r="W85" s="24"/>
+      <c r="X85" s="24"/>
+      <c r="Y85" s="10"/>
+      <c r="Z85" s="10"/>
+      <c r="AA85" s="10"/>
+      <c r="AB85" s="10"/>
+      <c r="AC85" s="10"/>
+      <c r="AD85" s="10"/>
+      <c r="AE85" s="27"/>
+      <c r="AF85" s="27"/>
+      <c r="AG85" s="27"/>
+      <c r="AH85" s="27"/>
+      <c r="AI85" s="27"/>
+      <c r="AJ85" s="27"/>
+      <c r="AK85" s="27"/>
+      <c r="AL85" s="27"/>
+    </row>
+    <row r="86" spans="1:38" ht="12" customHeight="1">
+      <c r="A86" s="90"/>
+      <c r="B86" s="90"/>
+      <c r="C86" s="90"/>
+      <c r="D86" s="90"/>
+      <c r="E86" s="90"/>
+      <c r="F86" s="42" t="s">
+        <v>14</v>
+      </c>
+      <c r="G86" s="43"/>
+      <c r="H86" s="44"/>
+      <c r="I86" s="44"/>
+      <c r="J86" s="44"/>
+      <c r="K86" s="44"/>
+      <c r="L86" s="44"/>
+      <c r="M86" s="44"/>
+      <c r="N86" s="44"/>
+      <c r="O86" s="44"/>
+      <c r="P86" s="44"/>
+      <c r="Q86" s="44"/>
+      <c r="R86" s="45"/>
+      <c r="S86" s="43"/>
+      <c r="T86" s="44"/>
+      <c r="U86" s="44"/>
+      <c r="V86" s="44"/>
+      <c r="W86" s="44"/>
+      <c r="X86" s="44"/>
+      <c r="Y86" s="10"/>
+      <c r="Z86" s="10"/>
+      <c r="AA86" s="10"/>
+      <c r="AB86" s="10"/>
+      <c r="AC86" s="10"/>
+      <c r="AD86" s="10"/>
+      <c r="AE86" s="32"/>
+      <c r="AF86" s="32"/>
+      <c r="AG86" s="32"/>
+      <c r="AH86" s="32"/>
+      <c r="AI86" s="32"/>
+      <c r="AJ86" s="32"/>
+      <c r="AK86" s="32"/>
+      <c r="AL86" s="32"/>
+    </row>
+    <row r="87" spans="1:38" ht="12" customHeight="1">
+      <c r="A87" s="89">
+        <v>4</v>
+      </c>
+      <c r="B87" s="91"/>
+      <c r="C87" s="91"/>
+      <c r="D87" s="91"/>
+      <c r="E87" s="91"/>
+      <c r="F87" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="G87" s="36"/>
+      <c r="H87" s="34"/>
+      <c r="I87" s="34"/>
+      <c r="J87" s="34"/>
+      <c r="K87" s="34"/>
+      <c r="L87" s="34"/>
+      <c r="M87" s="34"/>
+      <c r="N87" s="34"/>
+      <c r="O87" s="34"/>
+      <c r="P87" s="34"/>
+      <c r="Q87" s="34"/>
+      <c r="R87" s="35"/>
+      <c r="S87" s="36"/>
+      <c r="T87" s="34"/>
+      <c r="U87" s="34"/>
+      <c r="V87" s="34"/>
+      <c r="W87" s="34"/>
+      <c r="X87" s="34"/>
+      <c r="Y87" s="10"/>
+      <c r="Z87" s="10"/>
+      <c r="AA87" s="10"/>
+      <c r="AB87" s="10"/>
+      <c r="AC87" s="10"/>
+      <c r="AD87" s="10"/>
+      <c r="AE87" s="10"/>
+      <c r="AF87" s="10"/>
+      <c r="AG87" s="10"/>
+      <c r="AH87" s="10"/>
+      <c r="AI87" s="10"/>
+      <c r="AJ87" s="10"/>
+      <c r="AK87" s="10"/>
+      <c r="AL87" s="10"/>
+    </row>
+    <row r="88" spans="1:38" ht="12" customHeight="1">
+      <c r="A88" s="90"/>
+      <c r="B88" s="90"/>
+      <c r="C88" s="90"/>
+      <c r="D88" s="90"/>
+      <c r="E88" s="90"/>
+      <c r="F88" s="42" t="s">
+        <v>14</v>
+      </c>
+      <c r="G88" s="43"/>
+      <c r="H88" s="44"/>
+      <c r="I88" s="44"/>
+      <c r="J88" s="44"/>
+      <c r="K88" s="44"/>
+      <c r="L88" s="44"/>
+      <c r="M88" s="44"/>
+      <c r="N88" s="44"/>
+      <c r="O88" s="44"/>
+      <c r="P88" s="44"/>
+      <c r="Q88" s="44"/>
+      <c r="R88" s="45"/>
+      <c r="S88" s="43"/>
+      <c r="T88" s="44"/>
+      <c r="U88" s="44"/>
+      <c r="V88" s="44"/>
+      <c r="W88" s="44"/>
+      <c r="X88" s="44"/>
+      <c r="Y88" s="10"/>
+      <c r="Z88" s="10"/>
+      <c r="AA88" s="10"/>
+      <c r="AB88" s="10"/>
+      <c r="AC88" s="10"/>
+      <c r="AD88" s="10"/>
+      <c r="AE88" s="32"/>
+      <c r="AF88" s="32"/>
+      <c r="AG88" s="32"/>
+      <c r="AH88" s="32"/>
+      <c r="AI88" s="32"/>
+      <c r="AJ88" s="32"/>
+      <c r="AK88" s="32"/>
+      <c r="AL88" s="32"/>
     </row>
     <row r="89" spans="1:38" ht="13.5" customHeight="1">
       <c r="A89" s="6"/>
@@ -42201,104 +42169,265 @@
       <c r="AK1000" s="2"/>
       <c r="AL1000" s="2"/>
     </row>
+    <row r="1001" spans="1:38" ht="13.5" customHeight="1">
+      <c r="A1001" s="6"/>
+      <c r="B1001" s="2"/>
+      <c r="C1001" s="3"/>
+      <c r="D1001" s="4"/>
+      <c r="E1001" s="4"/>
+      <c r="F1001" s="4"/>
+      <c r="G1001" s="2"/>
+      <c r="H1001" s="2"/>
+      <c r="I1001" s="2"/>
+      <c r="J1001" s="2"/>
+      <c r="K1001" s="2"/>
+      <c r="L1001" s="2"/>
+      <c r="M1001" s="2"/>
+      <c r="N1001" s="2"/>
+      <c r="O1001" s="2"/>
+      <c r="P1001" s="2"/>
+      <c r="Q1001" s="2"/>
+      <c r="R1001" s="2"/>
+      <c r="S1001" s="2"/>
+      <c r="T1001" s="2"/>
+      <c r="U1001" s="2"/>
+      <c r="V1001" s="2"/>
+      <c r="W1001" s="2"/>
+      <c r="X1001" s="2"/>
+      <c r="Y1001" s="2"/>
+      <c r="Z1001" s="2"/>
+      <c r="AA1001" s="2"/>
+      <c r="AB1001" s="2"/>
+      <c r="AC1001" s="2"/>
+      <c r="AD1001" s="2"/>
+      <c r="AE1001" s="2"/>
+      <c r="AF1001" s="2"/>
+      <c r="AG1001" s="2"/>
+      <c r="AH1001" s="2"/>
+      <c r="AI1001" s="2"/>
+      <c r="AJ1001" s="2"/>
+      <c r="AK1001" s="2"/>
+      <c r="AL1001" s="2"/>
+    </row>
+    <row r="1002" spans="1:38" ht="13.5" customHeight="1">
+      <c r="A1002" s="6"/>
+      <c r="B1002" s="2"/>
+      <c r="C1002" s="3"/>
+      <c r="D1002" s="4"/>
+      <c r="E1002" s="4"/>
+      <c r="F1002" s="4"/>
+      <c r="G1002" s="2"/>
+      <c r="H1002" s="2"/>
+      <c r="I1002" s="2"/>
+      <c r="J1002" s="2"/>
+      <c r="K1002" s="2"/>
+      <c r="L1002" s="2"/>
+      <c r="M1002" s="2"/>
+      <c r="N1002" s="2"/>
+      <c r="O1002" s="2"/>
+      <c r="P1002" s="2"/>
+      <c r="Q1002" s="2"/>
+      <c r="R1002" s="2"/>
+      <c r="S1002" s="2"/>
+      <c r="T1002" s="2"/>
+      <c r="U1002" s="2"/>
+      <c r="V1002" s="2"/>
+      <c r="W1002" s="2"/>
+      <c r="X1002" s="2"/>
+      <c r="Y1002" s="2"/>
+      <c r="Z1002" s="2"/>
+      <c r="AA1002" s="2"/>
+      <c r="AB1002" s="2"/>
+      <c r="AC1002" s="2"/>
+      <c r="AD1002" s="2"/>
+      <c r="AE1002" s="2"/>
+      <c r="AF1002" s="2"/>
+      <c r="AG1002" s="2"/>
+      <c r="AH1002" s="2"/>
+      <c r="AI1002" s="2"/>
+      <c r="AJ1002" s="2"/>
+      <c r="AK1002" s="2"/>
+      <c r="AL1002" s="2"/>
+    </row>
+    <row r="1003" spans="1:38" ht="13.5" customHeight="1">
+      <c r="A1003" s="6"/>
+      <c r="B1003" s="2"/>
+      <c r="C1003" s="3"/>
+      <c r="D1003" s="4"/>
+      <c r="E1003" s="4"/>
+      <c r="F1003" s="4"/>
+      <c r="G1003" s="2"/>
+      <c r="H1003" s="2"/>
+      <c r="I1003" s="2"/>
+      <c r="J1003" s="2"/>
+      <c r="K1003" s="2"/>
+      <c r="L1003" s="2"/>
+      <c r="M1003" s="2"/>
+      <c r="N1003" s="2"/>
+      <c r="O1003" s="2"/>
+      <c r="P1003" s="2"/>
+      <c r="Q1003" s="2"/>
+      <c r="R1003" s="2"/>
+      <c r="S1003" s="2"/>
+      <c r="T1003" s="2"/>
+      <c r="U1003" s="2"/>
+      <c r="V1003" s="2"/>
+      <c r="W1003" s="2"/>
+      <c r="X1003" s="2"/>
+      <c r="Y1003" s="2"/>
+      <c r="Z1003" s="2"/>
+      <c r="AA1003" s="2"/>
+      <c r="AB1003" s="2"/>
+      <c r="AC1003" s="2"/>
+      <c r="AD1003" s="2"/>
+      <c r="AE1003" s="2"/>
+      <c r="AF1003" s="2"/>
+      <c r="AG1003" s="2"/>
+      <c r="AH1003" s="2"/>
+      <c r="AI1003" s="2"/>
+      <c r="AJ1003" s="2"/>
+      <c r="AK1003" s="2"/>
+      <c r="AL1003" s="2"/>
+    </row>
+    <row r="1004" spans="1:38" ht="13.5" customHeight="1">
+      <c r="A1004" s="6"/>
+      <c r="B1004" s="2"/>
+      <c r="C1004" s="3"/>
+      <c r="D1004" s="4"/>
+      <c r="E1004" s="4"/>
+      <c r="F1004" s="4"/>
+      <c r="G1004" s="2"/>
+      <c r="H1004" s="2"/>
+      <c r="I1004" s="2"/>
+      <c r="J1004" s="2"/>
+      <c r="K1004" s="2"/>
+      <c r="L1004" s="2"/>
+      <c r="M1004" s="2"/>
+      <c r="N1004" s="2"/>
+      <c r="O1004" s="2"/>
+      <c r="P1004" s="2"/>
+      <c r="Q1004" s="2"/>
+      <c r="R1004" s="2"/>
+      <c r="S1004" s="2"/>
+      <c r="T1004" s="2"/>
+      <c r="U1004" s="2"/>
+      <c r="V1004" s="2"/>
+      <c r="W1004" s="2"/>
+      <c r="X1004" s="2"/>
+      <c r="Y1004" s="2"/>
+      <c r="Z1004" s="2"/>
+      <c r="AA1004" s="2"/>
+      <c r="AB1004" s="2"/>
+      <c r="AC1004" s="2"/>
+      <c r="AD1004" s="2"/>
+      <c r="AE1004" s="2"/>
+      <c r="AF1004" s="2"/>
+      <c r="AG1004" s="2"/>
+      <c r="AH1004" s="2"/>
+      <c r="AI1004" s="2"/>
+      <c r="AJ1004" s="2"/>
+      <c r="AK1004" s="2"/>
+      <c r="AL1004" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="205">
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="E50:E51"/>
+  <mergeCells count="215">
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="E52:E53"/>
     <mergeCell ref="A48:A49"/>
     <mergeCell ref="B48:B49"/>
     <mergeCell ref="C48:C49"/>
     <mergeCell ref="D48:D49"/>
     <mergeCell ref="E48:E49"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="D53:D54"/>
-    <mergeCell ref="E53:E54"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="E68:E69"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="E70:E71"/>
-    <mergeCell ref="B59:B60"/>
-    <mergeCell ref="C59:C60"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="D61:D62"/>
-    <mergeCell ref="E61:E62"/>
-    <mergeCell ref="D59:D60"/>
-    <mergeCell ref="E59:E60"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="E57:E58"/>
+    <mergeCell ref="C74:C75"/>
     <mergeCell ref="D74:D75"/>
-    <mergeCell ref="E74:E75"/>
-    <mergeCell ref="A70:A71"/>
     <mergeCell ref="A72:A73"/>
     <mergeCell ref="B72:B73"/>
     <mergeCell ref="C72:C73"/>
     <mergeCell ref="D72:D73"/>
     <mergeCell ref="E72:E73"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="E74:E75"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C65:C66"/>
+    <mergeCell ref="D65:D66"/>
+    <mergeCell ref="E65:E66"/>
+    <mergeCell ref="D63:D64"/>
+    <mergeCell ref="E63:E64"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="D78:D79"/>
+    <mergeCell ref="E78:E79"/>
     <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="C77:C78"/>
-    <mergeCell ref="D77:D78"/>
-    <mergeCell ref="E77:E78"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="D76:D77"/>
+    <mergeCell ref="E76:E77"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="B81:B82"/>
     <mergeCell ref="C81:C82"/>
     <mergeCell ref="D81:D82"/>
-    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="E81:E82"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="E87:E88"/>
     <mergeCell ref="A83:A84"/>
     <mergeCell ref="B83:B84"/>
     <mergeCell ref="C83:C84"/>
     <mergeCell ref="D83:D84"/>
     <mergeCell ref="E83:E84"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="C79:C80"/>
-    <mergeCell ref="D79:D80"/>
-    <mergeCell ref="E79:E80"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="E81:E82"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="E85:E86"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="A44:A45"/>
     <mergeCell ref="A36:A37"/>
     <mergeCell ref="B36:B37"/>
     <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
     <mergeCell ref="S5:T5"/>
     <mergeCell ref="U5:V5"/>
     <mergeCell ref="W5:X5"/>
@@ -42344,74 +42473,83 @@
     <mergeCell ref="C15:C16"/>
     <mergeCell ref="D15:D16"/>
     <mergeCell ref="E15:E16"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="D57:D58"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="E57:E58"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="D59:D60"/>
+    <mergeCell ref="E59:E60"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="E61:E62"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:E39"/>
     <mergeCell ref="D40:D41"/>
     <mergeCell ref="E40:E41"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="D66:D67"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="E64:E65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="E66:E67"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="E68:E69"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="E70:E71"/>
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="B17:B18"/>
     <mergeCell ref="C17:C18"/>
     <mergeCell ref="D17:D18"/>
     <mergeCell ref="E17:E18"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E22"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="C19:C20"/>
     <mergeCell ref="D19:D20"/>
     <mergeCell ref="E19:E20"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C22"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E9 E11 E13 E15 E32 E34 E36 E40 E42 E50 E53 E55 E57 E59 E61 E64 E66 E68 E70 E72 E74 E77 E79 E81 E83 E17 E29 E21 E23 E25 E19 E38 E48 E44 E46 E27" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E9 E11 E13 E15 E36 E38 E40 E44 E46 E54 E57 E59 E61 E63 E65 E68 E70 E72 E74 E76 E78 E81 E83 E85 E87 E17 E33 E25 E27 E29 E23 E42 E52 E48 E50 E31 E21 E19" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"未着手,作成中,作成完了,レビュー中,レビュー完了,FIX"</formula1>
     </dataValidation>
   </dataValidations>

--- a/進捗管理表/進捗管理表_志賀.xlsx
+++ b/進捗管理表/進捗管理表_志賀.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-04\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-04\Documents\プロジェクト演習\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A1A28AA-6D52-4CAC-9ADF-5A6A4C5D2EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8584B592-CEC5-432D-90F6-E3F3E39C22A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1500,6 +1500,15 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="179" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1512,35 +1521,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1578,14 +1566,26 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1896,142 +1896,142 @@
       <c r="AL2" s="2"/>
     </row>
     <row r="3" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="95" t="s">
+      <c r="B3" s="113" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="106">
+      <c r="G3" s="102">
         <v>45705</v>
       </c>
-      <c r="H3" s="107"/>
-      <c r="I3" s="107"/>
-      <c r="J3" s="107"/>
-      <c r="K3" s="107"/>
-      <c r="L3" s="107"/>
-      <c r="M3" s="107"/>
-      <c r="N3" s="107"/>
-      <c r="O3" s="107"/>
-      <c r="P3" s="107"/>
-      <c r="Q3" s="107"/>
-      <c r="R3" s="107"/>
-      <c r="S3" s="107"/>
-      <c r="T3" s="107"/>
-      <c r="U3" s="107"/>
-      <c r="V3" s="107"/>
-      <c r="W3" s="107"/>
-      <c r="X3" s="107"/>
-      <c r="Y3" s="107"/>
-      <c r="Z3" s="107"/>
-      <c r="AA3" s="107"/>
-      <c r="AB3" s="107"/>
-      <c r="AC3" s="107"/>
-      <c r="AD3" s="107"/>
-      <c r="AE3" s="107"/>
-      <c r="AF3" s="107"/>
-      <c r="AG3" s="107"/>
-      <c r="AH3" s="107"/>
-      <c r="AI3" s="107"/>
-      <c r="AJ3" s="107"/>
-      <c r="AK3" s="107"/>
-      <c r="AL3" s="108"/>
+      <c r="H3" s="103"/>
+      <c r="I3" s="103"/>
+      <c r="J3" s="103"/>
+      <c r="K3" s="103"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="103"/>
+      <c r="N3" s="103"/>
+      <c r="O3" s="103"/>
+      <c r="P3" s="103"/>
+      <c r="Q3" s="103"/>
+      <c r="R3" s="103"/>
+      <c r="S3" s="103"/>
+      <c r="T3" s="103"/>
+      <c r="U3" s="103"/>
+      <c r="V3" s="103"/>
+      <c r="W3" s="103"/>
+      <c r="X3" s="103"/>
+      <c r="Y3" s="103"/>
+      <c r="Z3" s="103"/>
+      <c r="AA3" s="103"/>
+      <c r="AB3" s="103"/>
+      <c r="AC3" s="103"/>
+      <c r="AD3" s="103"/>
+      <c r="AE3" s="103"/>
+      <c r="AF3" s="103"/>
+      <c r="AG3" s="103"/>
+      <c r="AH3" s="103"/>
+      <c r="AI3" s="103"/>
+      <c r="AJ3" s="103"/>
+      <c r="AK3" s="103"/>
+      <c r="AL3" s="104"/>
     </row>
     <row r="4" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A4" s="94"/>
-      <c r="B4" s="94"/>
-      <c r="C4" s="96" t="s">
+      <c r="A4" s="112"/>
+      <c r="B4" s="112"/>
+      <c r="C4" s="114" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="93" t="s">
+      <c r="D4" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="100" t="s">
+      <c r="E4" s="117" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="103" t="s">
+      <c r="F4" s="99" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="109"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="110"/>
-      <c r="L4" s="110"/>
-      <c r="M4" s="110"/>
-      <c r="N4" s="110"/>
-      <c r="O4" s="110"/>
-      <c r="P4" s="110"/>
-      <c r="Q4" s="110"/>
-      <c r="R4" s="110"/>
-      <c r="S4" s="110"/>
-      <c r="T4" s="110"/>
-      <c r="U4" s="110"/>
-      <c r="V4" s="110"/>
-      <c r="W4" s="110"/>
-      <c r="X4" s="110"/>
-      <c r="Y4" s="110"/>
-      <c r="Z4" s="110"/>
-      <c r="AA4" s="110"/>
-      <c r="AB4" s="110"/>
-      <c r="AC4" s="110"/>
-      <c r="AD4" s="110"/>
-      <c r="AE4" s="110"/>
-      <c r="AF4" s="110"/>
-      <c r="AG4" s="110"/>
-      <c r="AH4" s="110"/>
-      <c r="AI4" s="110"/>
-      <c r="AJ4" s="110"/>
-      <c r="AK4" s="110"/>
-      <c r="AL4" s="111"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
+      <c r="J4" s="106"/>
+      <c r="K4" s="106"/>
+      <c r="L4" s="106"/>
+      <c r="M4" s="106"/>
+      <c r="N4" s="106"/>
+      <c r="O4" s="106"/>
+      <c r="P4" s="106"/>
+      <c r="Q4" s="106"/>
+      <c r="R4" s="106"/>
+      <c r="S4" s="106"/>
+      <c r="T4" s="106"/>
+      <c r="U4" s="106"/>
+      <c r="V4" s="106"/>
+      <c r="W4" s="106"/>
+      <c r="X4" s="106"/>
+      <c r="Y4" s="106"/>
+      <c r="Z4" s="106"/>
+      <c r="AA4" s="106"/>
+      <c r="AB4" s="106"/>
+      <c r="AC4" s="106"/>
+      <c r="AD4" s="106"/>
+      <c r="AE4" s="106"/>
+      <c r="AF4" s="106"/>
+      <c r="AG4" s="106"/>
+      <c r="AH4" s="106"/>
+      <c r="AI4" s="106"/>
+      <c r="AJ4" s="106"/>
+      <c r="AK4" s="106"/>
+      <c r="AL4" s="107"/>
     </row>
     <row r="5" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A5" s="94"/>
-      <c r="B5" s="94"/>
-      <c r="C5" s="94"/>
-      <c r="D5" s="94"/>
-      <c r="E5" s="94"/>
-      <c r="F5" s="104"/>
-      <c r="G5" s="101">
+      <c r="A5" s="112"/>
+      <c r="B5" s="112"/>
+      <c r="C5" s="112"/>
+      <c r="D5" s="112"/>
+      <c r="E5" s="112"/>
+      <c r="F5" s="100"/>
+      <c r="G5" s="96">
         <v>17</v>
       </c>
-      <c r="H5" s="102"/>
-      <c r="I5" s="97">
+      <c r="H5" s="97"/>
+      <c r="I5" s="98">
         <v>18</v>
       </c>
-      <c r="J5" s="98"/>
-      <c r="K5" s="97">
+      <c r="J5" s="115"/>
+      <c r="K5" s="98">
         <v>19</v>
       </c>
-      <c r="L5" s="98"/>
-      <c r="M5" s="97">
+      <c r="L5" s="115"/>
+      <c r="M5" s="98">
         <v>20</v>
       </c>
-      <c r="N5" s="98"/>
-      <c r="O5" s="97">
+      <c r="N5" s="115"/>
+      <c r="O5" s="98">
         <v>21</v>
       </c>
-      <c r="P5" s="98"/>
-      <c r="Q5" s="97">
+      <c r="P5" s="115"/>
+      <c r="Q5" s="98">
         <v>25</v>
       </c>
-      <c r="R5" s="99"/>
-      <c r="S5" s="101">
+      <c r="R5" s="116"/>
+      <c r="S5" s="96">
         <v>26</v>
       </c>
-      <c r="T5" s="102"/>
-      <c r="U5" s="97">
+      <c r="T5" s="97"/>
+      <c r="U5" s="98">
         <v>27</v>
       </c>
-      <c r="V5" s="102"/>
-      <c r="W5" s="97">
+      <c r="V5" s="97"/>
+      <c r="W5" s="98">
         <v>28</v>
       </c>
-      <c r="X5" s="102"/>
+      <c r="X5" s="97"/>
       <c r="Y5" s="10"/>
       <c r="Z5" s="10"/>
       <c r="AA5" s="10"/>
@@ -2048,48 +2048,48 @@
       <c r="AL5" s="11"/>
     </row>
     <row r="6" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A6" s="90"/>
-      <c r="B6" s="90"/>
-      <c r="C6" s="90"/>
-      <c r="D6" s="90"/>
-      <c r="E6" s="90"/>
-      <c r="F6" s="105"/>
-      <c r="G6" s="101" t="s">
+      <c r="A6" s="93"/>
+      <c r="B6" s="93"/>
+      <c r="C6" s="93"/>
+      <c r="D6" s="93"/>
+      <c r="E6" s="93"/>
+      <c r="F6" s="101"/>
+      <c r="G6" s="96" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="102"/>
-      <c r="I6" s="112" t="s">
+      <c r="H6" s="97"/>
+      <c r="I6" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="102"/>
-      <c r="K6" s="97" t="s">
+      <c r="J6" s="97"/>
+      <c r="K6" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="L6" s="102"/>
-      <c r="M6" s="97" t="s">
+      <c r="L6" s="97"/>
+      <c r="M6" s="98" t="s">
         <v>10</v>
       </c>
-      <c r="N6" s="102"/>
-      <c r="O6" s="97" t="s">
+      <c r="N6" s="97"/>
+      <c r="O6" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="P6" s="102"/>
-      <c r="Q6" s="97" t="s">
+      <c r="P6" s="97"/>
+      <c r="Q6" s="98" t="s">
         <v>19</v>
       </c>
-      <c r="R6" s="102"/>
-      <c r="S6" s="113" t="s">
+      <c r="R6" s="97"/>
+      <c r="S6" s="109" t="s">
         <v>20</v>
       </c>
-      <c r="T6" s="102"/>
-      <c r="U6" s="114" t="s">
+      <c r="T6" s="97"/>
+      <c r="U6" s="110" t="s">
         <v>21</v>
       </c>
-      <c r="V6" s="102"/>
-      <c r="W6" s="114" t="s">
+      <c r="V6" s="97"/>
+      <c r="W6" s="110" t="s">
         <v>22</v>
       </c>
-      <c r="X6" s="102"/>
+      <c r="X6" s="97"/>
       <c r="Y6" s="10"/>
       <c r="Z6" s="10"/>
       <c r="AA6" s="10"/>
@@ -2190,19 +2190,19 @@
       <c r="AL8" s="20"/>
     </row>
     <row r="9" spans="1:38" ht="12" customHeight="1">
-      <c r="A9" s="89">
+      <c r="A9" s="92">
         <v>1</v>
       </c>
-      <c r="B9" s="91" t="s">
+      <c r="B9" s="94" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="91">
+      <c r="C9" s="94">
         <v>2</v>
       </c>
-      <c r="D9" s="91" t="s">
+      <c r="D9" s="94" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="91"/>
+      <c r="E9" s="94"/>
       <c r="F9" s="21" t="s">
         <v>13</v>
       </c>
@@ -2240,11 +2240,11 @@
       <c r="AL9" s="27"/>
     </row>
     <row r="10" spans="1:38" ht="12" customHeight="1">
-      <c r="A10" s="90"/>
-      <c r="B10" s="90"/>
-      <c r="C10" s="90"/>
-      <c r="D10" s="90"/>
-      <c r="E10" s="90"/>
+      <c r="A10" s="93"/>
+      <c r="B10" s="93"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="93"/>
+      <c r="E10" s="93"/>
       <c r="F10" s="28" t="s">
         <v>14</v>
       </c>
@@ -2282,19 +2282,19 @@
       <c r="AL10" s="32"/>
     </row>
     <row r="11" spans="1:38" ht="12" customHeight="1">
-      <c r="A11" s="89">
+      <c r="A11" s="92">
         <v>2</v>
       </c>
-      <c r="B11" s="91" t="s">
+      <c r="B11" s="94" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="91">
+      <c r="C11" s="94">
         <v>2</v>
       </c>
-      <c r="D11" s="91" t="s">
+      <c r="D11" s="94" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="91"/>
+      <c r="E11" s="94"/>
       <c r="F11" s="33" t="s">
         <v>13</v>
       </c>
@@ -2332,11 +2332,11 @@
       <c r="AL11" s="10"/>
     </row>
     <row r="12" spans="1:38" ht="12" customHeight="1">
-      <c r="A12" s="90"/>
-      <c r="B12" s="90"/>
-      <c r="C12" s="90"/>
-      <c r="D12" s="90"/>
-      <c r="E12" s="90"/>
+      <c r="A12" s="93"/>
+      <c r="B12" s="93"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="93"/>
       <c r="F12" s="37" t="s">
         <v>14</v>
       </c>
@@ -2344,8 +2344,8 @@
       <c r="H12" s="39"/>
       <c r="I12" s="39"/>
       <c r="J12" s="39"/>
-      <c r="K12" s="115"/>
-      <c r="L12" s="115"/>
+      <c r="K12" s="89"/>
+      <c r="L12" s="89"/>
       <c r="M12" s="39"/>
       <c r="N12" s="39"/>
       <c r="O12" s="39"/>
@@ -2374,19 +2374,19 @@
       <c r="AL12" s="41"/>
     </row>
     <row r="13" spans="1:38" ht="12" customHeight="1">
-      <c r="A13" s="89">
+      <c r="A13" s="92">
         <v>3</v>
       </c>
-      <c r="B13" s="91" t="s">
+      <c r="B13" s="94" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="91">
+      <c r="C13" s="94">
         <v>1</v>
       </c>
-      <c r="D13" s="91" t="s">
+      <c r="D13" s="94" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="91"/>
+      <c r="E13" s="94"/>
       <c r="F13" s="21" t="s">
         <v>13</v>
       </c>
@@ -2424,11 +2424,11 @@
       <c r="AL13" s="27"/>
     </row>
     <row r="14" spans="1:38" ht="12" customHeight="1">
-      <c r="A14" s="90"/>
-      <c r="B14" s="90"/>
-      <c r="C14" s="90"/>
-      <c r="D14" s="90"/>
-      <c r="E14" s="90"/>
+      <c r="A14" s="93"/>
+      <c r="B14" s="93"/>
+      <c r="C14" s="93"/>
+      <c r="D14" s="93"/>
+      <c r="E14" s="93"/>
       <c r="F14" s="42" t="s">
         <v>14</v>
       </c>
@@ -2436,8 +2436,8 @@
       <c r="H14" s="44"/>
       <c r="I14" s="44"/>
       <c r="J14" s="44"/>
-      <c r="K14" s="116"/>
-      <c r="L14" s="116"/>
+      <c r="K14" s="90"/>
+      <c r="L14" s="90"/>
       <c r="M14" s="44"/>
       <c r="N14" s="44"/>
       <c r="O14" s="44"/>
@@ -2466,13 +2466,13 @@
       <c r="AL14" s="32"/>
     </row>
     <row r="15" spans="1:38" ht="12" customHeight="1">
-      <c r="A15" s="89">
+      <c r="A15" s="92">
         <v>4</v>
       </c>
-      <c r="B15" s="91"/>
-      <c r="C15" s="91"/>
-      <c r="D15" s="91"/>
-      <c r="E15" s="91"/>
+      <c r="B15" s="94"/>
+      <c r="C15" s="94"/>
+      <c r="D15" s="94"/>
+      <c r="E15" s="94"/>
       <c r="F15" s="33" t="s">
         <v>13</v>
       </c>
@@ -2510,11 +2510,11 @@
       <c r="AL15" s="10"/>
     </row>
     <row r="16" spans="1:38" ht="12" customHeight="1">
-      <c r="A16" s="90"/>
-      <c r="B16" s="90"/>
-      <c r="C16" s="90"/>
-      <c r="D16" s="90"/>
-      <c r="E16" s="90"/>
+      <c r="A16" s="93"/>
+      <c r="B16" s="93"/>
+      <c r="C16" s="93"/>
+      <c r="D16" s="93"/>
+      <c r="E16" s="93"/>
       <c r="F16" s="37" t="s">
         <v>14</v>
       </c>
@@ -2552,17 +2552,17 @@
       <c r="AL16" s="41"/>
     </row>
     <row r="17" spans="1:38" ht="12" customHeight="1">
-      <c r="A17" s="89">
+      <c r="A17" s="92">
         <v>7</v>
       </c>
-      <c r="B17" s="91" t="s">
+      <c r="B17" s="94" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="91">
+      <c r="C17" s="94">
         <v>1</v>
       </c>
-      <c r="D17" s="91"/>
-      <c r="E17" s="91"/>
+      <c r="D17" s="94"/>
+      <c r="E17" s="94"/>
       <c r="F17" s="54" t="s">
         <v>13</v>
       </c>
@@ -2600,11 +2600,11 @@
       <c r="AL17" s="69"/>
     </row>
     <row r="18" spans="1:38" ht="12" customHeight="1">
-      <c r="A18" s="90"/>
-      <c r="B18" s="92"/>
-      <c r="C18" s="92"/>
-      <c r="D18" s="92"/>
-      <c r="E18" s="92"/>
+      <c r="A18" s="93"/>
+      <c r="B18" s="95"/>
+      <c r="C18" s="95"/>
+      <c r="D18" s="95"/>
+      <c r="E18" s="95"/>
       <c r="F18" s="37" t="s">
         <v>14</v>
       </c>
@@ -2613,7 +2613,7 @@
       <c r="I18" s="48"/>
       <c r="J18" s="48"/>
       <c r="K18" s="48"/>
-      <c r="L18" s="117"/>
+      <c r="L18" s="91"/>
       <c r="M18" s="48"/>
       <c r="N18" s="48"/>
       <c r="O18" s="48"/>
@@ -2642,13 +2642,13 @@
       <c r="AL18" s="12"/>
     </row>
     <row r="19" spans="1:38" ht="12" customHeight="1">
-      <c r="A19" s="89">
+      <c r="A19" s="92">
         <v>4</v>
       </c>
-      <c r="B19" s="91"/>
-      <c r="C19" s="91"/>
-      <c r="D19" s="91"/>
-      <c r="E19" s="91"/>
+      <c r="B19" s="94"/>
+      <c r="C19" s="94"/>
+      <c r="D19" s="94"/>
+      <c r="E19" s="94"/>
       <c r="F19" s="54" t="s">
         <v>13</v>
       </c>
@@ -2686,11 +2686,11 @@
       <c r="AL19" s="69"/>
     </row>
     <row r="20" spans="1:38" ht="12" customHeight="1">
-      <c r="A20" s="90"/>
-      <c r="B20" s="90"/>
-      <c r="C20" s="90"/>
-      <c r="D20" s="90"/>
-      <c r="E20" s="90"/>
+      <c r="A20" s="93"/>
+      <c r="B20" s="93"/>
+      <c r="C20" s="93"/>
+      <c r="D20" s="93"/>
+      <c r="E20" s="93"/>
       <c r="F20" s="37" t="s">
         <v>14</v>
       </c>
@@ -2728,15 +2728,15 @@
       <c r="AL20" s="41"/>
     </row>
     <row r="21" spans="1:38" ht="12" customHeight="1">
-      <c r="A21" s="89">
+      <c r="A21" s="92">
         <v>4</v>
       </c>
-      <c r="B21" s="91" t="s">
+      <c r="B21" s="94" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="91"/>
-      <c r="D21" s="91"/>
-      <c r="E21" s="91"/>
+      <c r="C21" s="94"/>
+      <c r="D21" s="94"/>
+      <c r="E21" s="94"/>
       <c r="F21" s="54" t="s">
         <v>13</v>
       </c>
@@ -2774,11 +2774,11 @@
       <c r="AL21" s="69"/>
     </row>
     <row r="22" spans="1:38" ht="12" customHeight="1">
-      <c r="A22" s="90"/>
-      <c r="B22" s="90"/>
-      <c r="C22" s="90"/>
-      <c r="D22" s="90"/>
-      <c r="E22" s="90"/>
+      <c r="A22" s="93"/>
+      <c r="B22" s="93"/>
+      <c r="C22" s="93"/>
+      <c r="D22" s="93"/>
+      <c r="E22" s="93"/>
       <c r="F22" s="37" t="s">
         <v>14</v>
       </c>
@@ -2789,7 +2789,7 @@
       <c r="K22" s="39"/>
       <c r="L22" s="39"/>
       <c r="M22" s="39"/>
-      <c r="N22" s="39"/>
+      <c r="N22" s="89"/>
       <c r="O22" s="39"/>
       <c r="P22" s="39"/>
       <c r="Q22" s="39"/>
@@ -2816,13 +2816,13 @@
       <c r="AL22" s="41"/>
     </row>
     <row r="23" spans="1:38" ht="12" customHeight="1">
-      <c r="A23" s="89">
+      <c r="A23" s="92">
         <v>8</v>
       </c>
-      <c r="B23" s="91"/>
-      <c r="C23" s="91"/>
-      <c r="D23" s="91"/>
-      <c r="E23" s="91"/>
+      <c r="B23" s="94"/>
+      <c r="C23" s="94"/>
+      <c r="D23" s="94"/>
+      <c r="E23" s="94"/>
       <c r="F23" s="54" t="s">
         <v>13</v>
       </c>
@@ -2860,11 +2860,11 @@
       <c r="AL23" s="69"/>
     </row>
     <row r="24" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A24" s="90"/>
-      <c r="B24" s="92"/>
-      <c r="C24" s="92"/>
-      <c r="D24" s="92"/>
-      <c r="E24" s="92"/>
+      <c r="A24" s="93"/>
+      <c r="B24" s="95"/>
+      <c r="C24" s="95"/>
+      <c r="D24" s="95"/>
+      <c r="E24" s="95"/>
       <c r="F24" s="37" t="s">
         <v>14</v>
       </c>
@@ -2902,17 +2902,17 @@
       <c r="AL24" s="12"/>
     </row>
     <row r="25" spans="1:38" ht="12" customHeight="1">
-      <c r="A25" s="89">
+      <c r="A25" s="92">
         <v>9</v>
       </c>
-      <c r="B25" s="91" t="s">
+      <c r="B25" s="94" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="91">
+      <c r="C25" s="94">
         <v>2</v>
       </c>
-      <c r="D25" s="91"/>
-      <c r="E25" s="91"/>
+      <c r="D25" s="94"/>
+      <c r="E25" s="94"/>
       <c r="F25" s="21" t="s">
         <v>13</v>
       </c>
@@ -2950,11 +2950,11 @@
       <c r="AL25" s="27"/>
     </row>
     <row r="26" spans="1:38" ht="12" customHeight="1">
-      <c r="A26" s="90"/>
-      <c r="B26" s="90"/>
-      <c r="C26" s="90"/>
-      <c r="D26" s="90"/>
-      <c r="E26" s="90"/>
+      <c r="A26" s="93"/>
+      <c r="B26" s="93"/>
+      <c r="C26" s="93"/>
+      <c r="D26" s="93"/>
+      <c r="E26" s="93"/>
       <c r="F26" s="42" t="s">
         <v>14</v>
       </c>
@@ -2965,7 +2965,7 @@
       <c r="K26" s="30"/>
       <c r="L26" s="30"/>
       <c r="M26" s="30"/>
-      <c r="N26" s="30"/>
+      <c r="N26" s="86"/>
       <c r="O26" s="30"/>
       <c r="P26" s="30"/>
       <c r="Q26" s="30"/>
@@ -2992,17 +2992,17 @@
       <c r="AL26" s="46"/>
     </row>
     <row r="27" spans="1:38" ht="12" customHeight="1">
-      <c r="A27" s="89">
+      <c r="A27" s="92">
         <v>10</v>
       </c>
-      <c r="B27" s="91" t="s">
+      <c r="B27" s="94" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="91">
+      <c r="C27" s="94">
         <v>2</v>
       </c>
-      <c r="D27" s="91"/>
-      <c r="E27" s="91"/>
+      <c r="D27" s="94"/>
+      <c r="E27" s="94"/>
       <c r="F27" s="33" t="s">
         <v>13</v>
       </c>
@@ -3040,11 +3040,11 @@
       <c r="AL27" s="10"/>
     </row>
     <row r="28" spans="1:38" ht="12" customHeight="1">
-      <c r="A28" s="90"/>
-      <c r="B28" s="92"/>
-      <c r="C28" s="92"/>
-      <c r="D28" s="92"/>
-      <c r="E28" s="92"/>
+      <c r="A28" s="93"/>
+      <c r="B28" s="95"/>
+      <c r="C28" s="95"/>
+      <c r="D28" s="95"/>
+      <c r="E28" s="95"/>
       <c r="F28" s="37" t="s">
         <v>14</v>
       </c>
@@ -3055,7 +3055,7 @@
       <c r="K28" s="48"/>
       <c r="L28" s="48"/>
       <c r="M28" s="48"/>
-      <c r="N28" s="48"/>
+      <c r="N28" s="91"/>
       <c r="O28" s="48"/>
       <c r="P28" s="48"/>
       <c r="Q28" s="48"/>
@@ -3082,17 +3082,17 @@
       <c r="AL28" s="12"/>
     </row>
     <row r="29" spans="1:38" ht="12" customHeight="1">
-      <c r="A29" s="89">
+      <c r="A29" s="92">
         <v>11</v>
       </c>
-      <c r="B29" s="91" t="s">
+      <c r="B29" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="91">
+      <c r="C29" s="94">
         <v>1</v>
       </c>
-      <c r="D29" s="91"/>
-      <c r="E29" s="91"/>
+      <c r="D29" s="94"/>
+      <c r="E29" s="94"/>
       <c r="F29" s="54" t="s">
         <v>13</v>
       </c>
@@ -3130,11 +3130,11 @@
       <c r="AL29" s="69"/>
     </row>
     <row r="30" spans="1:38" ht="12" customHeight="1">
-      <c r="A30" s="90"/>
-      <c r="B30" s="92"/>
-      <c r="C30" s="92"/>
-      <c r="D30" s="92"/>
-      <c r="E30" s="92"/>
+      <c r="A30" s="93"/>
+      <c r="B30" s="95"/>
+      <c r="C30" s="95"/>
+      <c r="D30" s="95"/>
+      <c r="E30" s="95"/>
       <c r="F30" s="37" t="s">
         <v>14</v>
       </c>
@@ -3145,7 +3145,7 @@
       <c r="K30" s="48"/>
       <c r="L30" s="48"/>
       <c r="M30" s="48"/>
-      <c r="N30" s="48"/>
+      <c r="N30" s="91"/>
       <c r="O30" s="48"/>
       <c r="P30" s="48"/>
       <c r="Q30" s="48"/>
@@ -3172,13 +3172,13 @@
       <c r="AL30" s="12"/>
     </row>
     <row r="31" spans="1:38" ht="12" customHeight="1">
-      <c r="A31" s="89">
+      <c r="A31" s="92">
         <v>12</v>
       </c>
-      <c r="B31" s="91"/>
-      <c r="C31" s="91"/>
-      <c r="D31" s="91"/>
-      <c r="E31" s="91"/>
+      <c r="B31" s="94"/>
+      <c r="C31" s="94"/>
+      <c r="D31" s="94"/>
+      <c r="E31" s="94"/>
       <c r="F31" s="54" t="s">
         <v>13</v>
       </c>
@@ -3216,11 +3216,11 @@
       <c r="AL31" s="69"/>
     </row>
     <row r="32" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A32" s="90"/>
-      <c r="B32" s="92"/>
-      <c r="C32" s="92"/>
-      <c r="D32" s="92"/>
-      <c r="E32" s="92"/>
+      <c r="A32" s="93"/>
+      <c r="B32" s="95"/>
+      <c r="C32" s="95"/>
+      <c r="D32" s="95"/>
+      <c r="E32" s="95"/>
       <c r="F32" s="37" t="s">
         <v>14</v>
       </c>
@@ -3258,15 +3258,15 @@
       <c r="AL32" s="12"/>
     </row>
     <row r="33" spans="1:38" ht="12" customHeight="1">
-      <c r="A33" s="89">
+      <c r="A33" s="92">
         <v>12</v>
       </c>
-      <c r="B33" s="91" t="s">
+      <c r="B33" s="94" t="s">
         <v>35</v>
       </c>
-      <c r="C33" s="91"/>
-      <c r="D33" s="91"/>
-      <c r="E33" s="91"/>
+      <c r="C33" s="94"/>
+      <c r="D33" s="94"/>
+      <c r="E33" s="94"/>
       <c r="F33" s="54" t="s">
         <v>13</v>
       </c>
@@ -3304,11 +3304,11 @@
       <c r="AL33" s="69"/>
     </row>
     <row r="34" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A34" s="90"/>
-      <c r="B34" s="92"/>
-      <c r="C34" s="92"/>
-      <c r="D34" s="92"/>
-      <c r="E34" s="92"/>
+      <c r="A34" s="93"/>
+      <c r="B34" s="95"/>
+      <c r="C34" s="95"/>
+      <c r="D34" s="95"/>
+      <c r="E34" s="95"/>
       <c r="F34" s="37" t="s">
         <v>14</v>
       </c>
@@ -3319,7 +3319,7 @@
       <c r="K34" s="48"/>
       <c r="L34" s="48"/>
       <c r="M34" s="48"/>
-      <c r="N34" s="48"/>
+      <c r="N34" s="91"/>
       <c r="O34" s="48"/>
       <c r="P34" s="48"/>
       <c r="Q34" s="48"/>
@@ -3388,17 +3388,17 @@
       <c r="AL35" s="20"/>
     </row>
     <row r="36" spans="1:38" ht="12" customHeight="1">
-      <c r="A36" s="89">
+      <c r="A36" s="92">
         <v>1</v>
       </c>
-      <c r="B36" s="91" t="s">
+      <c r="B36" s="94" t="s">
         <v>36</v>
       </c>
-      <c r="C36" s="91">
+      <c r="C36" s="94">
         <v>0.5</v>
       </c>
-      <c r="D36" s="91"/>
-      <c r="E36" s="91"/>
+      <c r="D36" s="94"/>
+      <c r="E36" s="94"/>
       <c r="F36" s="21" t="s">
         <v>13</v>
       </c>
@@ -3435,11 +3435,11 @@
       <c r="AL36" s="27"/>
     </row>
     <row r="37" spans="1:38" ht="12" customHeight="1">
-      <c r="A37" s="90"/>
-      <c r="B37" s="92"/>
-      <c r="C37" s="90"/>
-      <c r="D37" s="90"/>
-      <c r="E37" s="90"/>
+      <c r="A37" s="93"/>
+      <c r="B37" s="95"/>
+      <c r="C37" s="93"/>
+      <c r="D37" s="93"/>
+      <c r="E37" s="93"/>
       <c r="F37" s="28" t="s">
         <v>14</v>
       </c>
@@ -3477,17 +3477,17 @@
       <c r="AL37" s="32"/>
     </row>
     <row r="38" spans="1:38" ht="12" customHeight="1">
-      <c r="A38" s="89">
+      <c r="A38" s="92">
         <v>2</v>
       </c>
-      <c r="B38" s="91" t="s">
+      <c r="B38" s="94" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="91">
+      <c r="C38" s="94">
         <v>4</v>
       </c>
-      <c r="D38" s="91"/>
-      <c r="E38" s="91"/>
+      <c r="D38" s="94"/>
+      <c r="E38" s="94"/>
       <c r="F38" s="33" t="s">
         <v>13</v>
       </c>
@@ -3525,11 +3525,11 @@
       <c r="AL38" s="10"/>
     </row>
     <row r="39" spans="1:38" ht="12" customHeight="1">
-      <c r="A39" s="90"/>
-      <c r="B39" s="92"/>
-      <c r="C39" s="90"/>
-      <c r="D39" s="90"/>
-      <c r="E39" s="90"/>
+      <c r="A39" s="93"/>
+      <c r="B39" s="95"/>
+      <c r="C39" s="93"/>
+      <c r="D39" s="93"/>
+      <c r="E39" s="93"/>
       <c r="F39" s="37" t="s">
         <v>14</v>
       </c>
@@ -3567,17 +3567,17 @@
       <c r="AL39" s="41"/>
     </row>
     <row r="40" spans="1:38" ht="12" customHeight="1">
-      <c r="A40" s="89">
+      <c r="A40" s="92">
         <v>3</v>
       </c>
-      <c r="B40" s="91" t="s">
+      <c r="B40" s="94" t="s">
         <v>38</v>
       </c>
-      <c r="C40" s="91">
+      <c r="C40" s="94">
         <v>4</v>
       </c>
-      <c r="D40" s="91"/>
-      <c r="E40" s="91"/>
+      <c r="D40" s="94"/>
+      <c r="E40" s="94"/>
       <c r="F40" s="21" t="s">
         <v>13</v>
       </c>
@@ -3615,11 +3615,11 @@
       <c r="AL40" s="27"/>
     </row>
     <row r="41" spans="1:38" ht="12" customHeight="1">
-      <c r="A41" s="90"/>
-      <c r="B41" s="92"/>
-      <c r="C41" s="90"/>
-      <c r="D41" s="90"/>
-      <c r="E41" s="90"/>
+      <c r="A41" s="93"/>
+      <c r="B41" s="95"/>
+      <c r="C41" s="93"/>
+      <c r="D41" s="93"/>
+      <c r="E41" s="93"/>
       <c r="F41" s="42" t="s">
         <v>14</v>
       </c>
@@ -3656,13 +3656,13 @@
       <c r="AL41" s="32"/>
     </row>
     <row r="42" spans="1:38" ht="12" customHeight="1">
-      <c r="A42" s="89">
+      <c r="A42" s="92">
         <v>4</v>
       </c>
-      <c r="B42" s="91"/>
-      <c r="C42" s="91"/>
-      <c r="D42" s="91"/>
-      <c r="E42" s="91"/>
+      <c r="B42" s="94"/>
+      <c r="C42" s="94"/>
+      <c r="D42" s="94"/>
+      <c r="E42" s="94"/>
       <c r="F42" s="33" t="s">
         <v>13</v>
       </c>
@@ -3700,11 +3700,11 @@
       <c r="AL42" s="10"/>
     </row>
     <row r="43" spans="1:38" ht="12" customHeight="1">
-      <c r="A43" s="90"/>
-      <c r="B43" s="92"/>
-      <c r="C43" s="92"/>
-      <c r="D43" s="92"/>
-      <c r="E43" s="92"/>
+      <c r="A43" s="93"/>
+      <c r="B43" s="95"/>
+      <c r="C43" s="95"/>
+      <c r="D43" s="95"/>
+      <c r="E43" s="95"/>
       <c r="F43" s="37" t="s">
         <v>14</v>
       </c>
@@ -3742,17 +3742,17 @@
       <c r="AL43" s="41"/>
     </row>
     <row r="44" spans="1:38" ht="12" customHeight="1">
-      <c r="A44" s="89">
+      <c r="A44" s="92">
         <v>5</v>
       </c>
-      <c r="B44" s="91" t="s">
+      <c r="B44" s="94" t="s">
         <v>39</v>
       </c>
-      <c r="C44" s="91">
+      <c r="C44" s="94">
         <v>0.5</v>
       </c>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="D44" s="94"/>
+      <c r="E44" s="94"/>
       <c r="F44" s="54" t="s">
         <v>13</v>
       </c>
@@ -3790,11 +3790,11 @@
       <c r="AL44" s="79"/>
     </row>
     <row r="45" spans="1:38" ht="12" customHeight="1">
-      <c r="A45" s="90"/>
-      <c r="B45" s="92"/>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="A45" s="93"/>
+      <c r="B45" s="95"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
       <c r="F45" s="37" t="s">
         <v>14</v>
       </c>
@@ -3832,13 +3832,13 @@
       <c r="AL45" s="41"/>
     </row>
     <row r="46" spans="1:38" ht="12" customHeight="1">
-      <c r="A46" s="89">
+      <c r="A46" s="92">
         <v>6</v>
       </c>
-      <c r="B46" s="91"/>
-      <c r="C46" s="91"/>
-      <c r="D46" s="91"/>
-      <c r="E46" s="91"/>
+      <c r="B46" s="94"/>
+      <c r="C46" s="94"/>
+      <c r="D46" s="94"/>
+      <c r="E46" s="94"/>
       <c r="F46" s="21" t="s">
         <v>13</v>
       </c>
@@ -3875,11 +3875,11 @@
       <c r="AL46" s="27"/>
     </row>
     <row r="47" spans="1:38" ht="12" customHeight="1">
-      <c r="A47" s="90"/>
-      <c r="B47" s="92"/>
-      <c r="C47" s="90"/>
-      <c r="D47" s="90"/>
-      <c r="E47" s="90"/>
+      <c r="A47" s="93"/>
+      <c r="B47" s="95"/>
+      <c r="C47" s="93"/>
+      <c r="D47" s="93"/>
+      <c r="E47" s="93"/>
       <c r="F47" s="42" t="s">
         <v>14</v>
       </c>
@@ -3917,17 +3917,17 @@
       <c r="AL47" s="46"/>
     </row>
     <row r="48" spans="1:38" ht="12" customHeight="1">
-      <c r="A48" s="89">
+      <c r="A48" s="92">
         <v>7</v>
       </c>
-      <c r="B48" s="91" t="s">
+      <c r="B48" s="94" t="s">
         <v>40</v>
       </c>
-      <c r="C48" s="91">
+      <c r="C48" s="94">
         <v>0.5</v>
       </c>
-      <c r="D48" s="91"/>
-      <c r="E48" s="91"/>
+      <c r="D48" s="94"/>
+      <c r="E48" s="94"/>
       <c r="F48" s="21" t="s">
         <v>13</v>
       </c>
@@ -3965,11 +3965,11 @@
       <c r="AL48" s="27"/>
     </row>
     <row r="49" spans="1:38" ht="12" customHeight="1">
-      <c r="A49" s="90"/>
-      <c r="B49" s="92"/>
-      <c r="C49" s="90"/>
-      <c r="D49" s="90"/>
-      <c r="E49" s="90"/>
+      <c r="A49" s="93"/>
+      <c r="B49" s="95"/>
+      <c r="C49" s="93"/>
+      <c r="D49" s="93"/>
+      <c r="E49" s="93"/>
       <c r="F49" s="42" t="s">
         <v>14</v>
       </c>
@@ -4007,17 +4007,17 @@
       <c r="AL49" s="46"/>
     </row>
     <row r="50" spans="1:38" ht="12" customHeight="1">
-      <c r="A50" s="89">
+      <c r="A50" s="92">
         <v>8</v>
       </c>
-      <c r="B50" s="91" t="s">
+      <c r="B50" s="94" t="s">
         <v>41</v>
       </c>
-      <c r="C50" s="91">
+      <c r="C50" s="94">
         <v>4</v>
       </c>
-      <c r="D50" s="91"/>
-      <c r="E50" s="91"/>
+      <c r="D50" s="94"/>
+      <c r="E50" s="94"/>
       <c r="F50" s="21" t="s">
         <v>13</v>
       </c>
@@ -4054,11 +4054,11 @@
       <c r="AL50" s="27"/>
     </row>
     <row r="51" spans="1:38" ht="12" customHeight="1">
-      <c r="A51" s="90"/>
-      <c r="B51" s="92"/>
-      <c r="C51" s="90"/>
-      <c r="D51" s="90"/>
-      <c r="E51" s="90"/>
+      <c r="A51" s="93"/>
+      <c r="B51" s="95"/>
+      <c r="C51" s="93"/>
+      <c r="D51" s="93"/>
+      <c r="E51" s="93"/>
       <c r="F51" s="42" t="s">
         <v>14</v>
       </c>
@@ -4096,13 +4096,13 @@
       <c r="AL51" s="46"/>
     </row>
     <row r="52" spans="1:38" ht="12" customHeight="1">
-      <c r="A52" s="89">
+      <c r="A52" s="92">
         <v>9</v>
       </c>
-      <c r="B52" s="91"/>
-      <c r="C52" s="91"/>
-      <c r="D52" s="91"/>
-      <c r="E52" s="91"/>
+      <c r="B52" s="94"/>
+      <c r="C52" s="94"/>
+      <c r="D52" s="94"/>
+      <c r="E52" s="94"/>
       <c r="F52" s="21" t="s">
         <v>13</v>
       </c>
@@ -4140,11 +4140,11 @@
       <c r="AL52" s="27"/>
     </row>
     <row r="53" spans="1:38" ht="12" customHeight="1">
-      <c r="A53" s="90"/>
-      <c r="B53" s="92"/>
-      <c r="C53" s="90"/>
-      <c r="D53" s="90"/>
-      <c r="E53" s="90"/>
+      <c r="A53" s="93"/>
+      <c r="B53" s="95"/>
+      <c r="C53" s="93"/>
+      <c r="D53" s="93"/>
+      <c r="E53" s="93"/>
       <c r="F53" s="42" t="s">
         <v>14</v>
       </c>
@@ -4182,15 +4182,15 @@
       <c r="AL53" s="46"/>
     </row>
     <row r="54" spans="1:38" ht="11.25" customHeight="1">
-      <c r="A54" s="89">
+      <c r="A54" s="92">
         <v>10</v>
       </c>
-      <c r="B54" s="91" t="s">
+      <c r="B54" s="94" t="s">
         <v>35</v>
       </c>
-      <c r="C54" s="91"/>
-      <c r="D54" s="91"/>
-      <c r="E54" s="91"/>
+      <c r="C54" s="94"/>
+      <c r="D54" s="94"/>
+      <c r="E54" s="94"/>
       <c r="F54" s="33" t="s">
         <v>13</v>
       </c>
@@ -4228,11 +4228,11 @@
       <c r="AL54" s="10"/>
     </row>
     <row r="55" spans="1:38" ht="12" customHeight="1">
-      <c r="A55" s="90"/>
-      <c r="B55" s="92"/>
-      <c r="C55" s="90"/>
-      <c r="D55" s="90"/>
-      <c r="E55" s="90"/>
+      <c r="A55" s="93"/>
+      <c r="B55" s="95"/>
+      <c r="C55" s="93"/>
+      <c r="D55" s="93"/>
+      <c r="E55" s="93"/>
       <c r="F55" s="37" t="s">
         <v>14</v>
       </c>
@@ -4310,15 +4310,15 @@
       <c r="AL56" s="20"/>
     </row>
     <row r="57" spans="1:38" ht="12" customHeight="1">
-      <c r="A57" s="89">
+      <c r="A57" s="92">
         <v>1</v>
       </c>
-      <c r="B57" s="91" t="s">
+      <c r="B57" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="C57" s="91"/>
-      <c r="D57" s="91"/>
-      <c r="E57" s="91"/>
+      <c r="C57" s="94"/>
+      <c r="D57" s="94"/>
+      <c r="E57" s="94"/>
       <c r="F57" s="21" t="s">
         <v>13</v>
       </c>
@@ -4356,11 +4356,11 @@
       <c r="AL57" s="27"/>
     </row>
     <row r="58" spans="1:38" ht="12" customHeight="1">
-      <c r="A58" s="90"/>
-      <c r="B58" s="90"/>
-      <c r="C58" s="90"/>
-      <c r="D58" s="90"/>
-      <c r="E58" s="90"/>
+      <c r="A58" s="93"/>
+      <c r="B58" s="93"/>
+      <c r="C58" s="93"/>
+      <c r="D58" s="93"/>
+      <c r="E58" s="93"/>
       <c r="F58" s="28" t="s">
         <v>14</v>
       </c>
@@ -4398,15 +4398,15 @@
       <c r="AL58" s="32"/>
     </row>
     <row r="59" spans="1:38" ht="12" customHeight="1">
-      <c r="A59" s="89">
+      <c r="A59" s="92">
         <v>2</v>
       </c>
-      <c r="B59" s="91" t="s">
+      <c r="B59" s="94" t="s">
         <v>24</v>
       </c>
-      <c r="C59" s="91"/>
-      <c r="D59" s="91"/>
-      <c r="E59" s="91"/>
+      <c r="C59" s="94"/>
+      <c r="D59" s="94"/>
+      <c r="E59" s="94"/>
       <c r="F59" s="33" t="s">
         <v>13</v>
       </c>
@@ -4444,11 +4444,11 @@
       <c r="AL59" s="10"/>
     </row>
     <row r="60" spans="1:38" ht="12" customHeight="1">
-      <c r="A60" s="90"/>
-      <c r="B60" s="90"/>
-      <c r="C60" s="90"/>
-      <c r="D60" s="90"/>
-      <c r="E60" s="90"/>
+      <c r="A60" s="93"/>
+      <c r="B60" s="93"/>
+      <c r="C60" s="93"/>
+      <c r="D60" s="93"/>
+      <c r="E60" s="93"/>
       <c r="F60" s="37" t="s">
         <v>14</v>
       </c>
@@ -4486,15 +4486,15 @@
       <c r="AL60" s="41"/>
     </row>
     <row r="61" spans="1:38" ht="12" customHeight="1">
-      <c r="A61" s="89">
+      <c r="A61" s="92">
         <v>3</v>
       </c>
-      <c r="B61" s="91" t="s">
+      <c r="B61" s="94" t="s">
         <v>25</v>
       </c>
-      <c r="C61" s="91"/>
-      <c r="D61" s="91"/>
-      <c r="E61" s="91"/>
+      <c r="C61" s="94"/>
+      <c r="D61" s="94"/>
+      <c r="E61" s="94"/>
       <c r="F61" s="21" t="s">
         <v>13</v>
       </c>
@@ -4532,11 +4532,11 @@
       <c r="AL61" s="27"/>
     </row>
     <row r="62" spans="1:38" ht="12" customHeight="1">
-      <c r="A62" s="90"/>
-      <c r="B62" s="90"/>
-      <c r="C62" s="90"/>
-      <c r="D62" s="90"/>
-      <c r="E62" s="90"/>
+      <c r="A62" s="93"/>
+      <c r="B62" s="93"/>
+      <c r="C62" s="93"/>
+      <c r="D62" s="93"/>
+      <c r="E62" s="93"/>
       <c r="F62" s="42" t="s">
         <v>14</v>
       </c>
@@ -4574,15 +4574,15 @@
       <c r="AL62" s="32"/>
     </row>
     <row r="63" spans="1:38" ht="12" customHeight="1">
-      <c r="A63" s="89">
+      <c r="A63" s="92">
         <v>4</v>
       </c>
-      <c r="B63" s="91" t="s">
+      <c r="B63" s="94" t="s">
         <v>26</v>
       </c>
-      <c r="C63" s="91"/>
-      <c r="D63" s="91"/>
-      <c r="E63" s="91"/>
+      <c r="C63" s="94"/>
+      <c r="D63" s="94"/>
+      <c r="E63" s="94"/>
       <c r="F63" s="21" t="s">
         <v>13</v>
       </c>
@@ -4620,11 +4620,11 @@
       <c r="AL63" s="27"/>
     </row>
     <row r="64" spans="1:38" ht="12" customHeight="1">
-      <c r="A64" s="90"/>
-      <c r="B64" s="90"/>
-      <c r="C64" s="90"/>
-      <c r="D64" s="90"/>
-      <c r="E64" s="90"/>
+      <c r="A64" s="93"/>
+      <c r="B64" s="93"/>
+      <c r="C64" s="93"/>
+      <c r="D64" s="93"/>
+      <c r="E64" s="93"/>
       <c r="F64" s="42" t="s">
         <v>14</v>
       </c>
@@ -4662,13 +4662,13 @@
       <c r="AL64" s="46"/>
     </row>
     <row r="65" spans="1:38" ht="12" customHeight="1">
-      <c r="A65" s="89">
+      <c r="A65" s="92">
         <v>5</v>
       </c>
-      <c r="B65" s="91"/>
-      <c r="C65" s="91"/>
-      <c r="D65" s="91"/>
-      <c r="E65" s="91"/>
+      <c r="B65" s="94"/>
+      <c r="C65" s="94"/>
+      <c r="D65" s="94"/>
+      <c r="E65" s="94"/>
       <c r="F65" s="33" t="s">
         <v>13</v>
       </c>
@@ -4706,11 +4706,11 @@
       <c r="AL65" s="10"/>
     </row>
     <row r="66" spans="1:38" ht="12" customHeight="1">
-      <c r="A66" s="90"/>
-      <c r="B66" s="90"/>
-      <c r="C66" s="90"/>
-      <c r="D66" s="90"/>
-      <c r="E66" s="90"/>
+      <c r="A66" s="93"/>
+      <c r="B66" s="93"/>
+      <c r="C66" s="93"/>
+      <c r="D66" s="93"/>
+      <c r="E66" s="93"/>
       <c r="F66" s="37" t="s">
         <v>14</v>
       </c>
@@ -4790,13 +4790,13 @@
       <c r="AL67" s="20"/>
     </row>
     <row r="68" spans="1:38" ht="12" customHeight="1">
-      <c r="A68" s="89">
+      <c r="A68" s="92">
         <v>1</v>
       </c>
-      <c r="B68" s="91"/>
-      <c r="C68" s="91"/>
-      <c r="D68" s="91"/>
-      <c r="E68" s="91"/>
+      <c r="B68" s="94"/>
+      <c r="C68" s="94"/>
+      <c r="D68" s="94"/>
+      <c r="E68" s="94"/>
       <c r="F68" s="21" t="s">
         <v>13</v>
       </c>
@@ -4834,11 +4834,11 @@
       <c r="AL68" s="27"/>
     </row>
     <row r="69" spans="1:38" ht="12" customHeight="1">
-      <c r="A69" s="90"/>
-      <c r="B69" s="90"/>
-      <c r="C69" s="90"/>
-      <c r="D69" s="90"/>
-      <c r="E69" s="90"/>
+      <c r="A69" s="93"/>
+      <c r="B69" s="93"/>
+      <c r="C69" s="93"/>
+      <c r="D69" s="93"/>
+      <c r="E69" s="93"/>
       <c r="F69" s="28" t="s">
         <v>14</v>
       </c>
@@ -4876,13 +4876,13 @@
       <c r="AL69" s="32"/>
     </row>
     <row r="70" spans="1:38" ht="12" customHeight="1">
-      <c r="A70" s="89">
+      <c r="A70" s="92">
         <v>2</v>
       </c>
-      <c r="B70" s="91"/>
-      <c r="C70" s="91"/>
-      <c r="D70" s="91"/>
-      <c r="E70" s="91"/>
+      <c r="B70" s="94"/>
+      <c r="C70" s="94"/>
+      <c r="D70" s="94"/>
+      <c r="E70" s="94"/>
       <c r="F70" s="33" t="s">
         <v>13</v>
       </c>
@@ -4920,11 +4920,11 @@
       <c r="AL70" s="10"/>
     </row>
     <row r="71" spans="1:38" ht="12" customHeight="1">
-      <c r="A71" s="90"/>
-      <c r="B71" s="90"/>
-      <c r="C71" s="90"/>
-      <c r="D71" s="90"/>
-      <c r="E71" s="90"/>
+      <c r="A71" s="93"/>
+      <c r="B71" s="93"/>
+      <c r="C71" s="93"/>
+      <c r="D71" s="93"/>
+      <c r="E71" s="93"/>
       <c r="F71" s="37" t="s">
         <v>14</v>
       </c>
@@ -4962,13 +4962,13 @@
       <c r="AL71" s="41"/>
     </row>
     <row r="72" spans="1:38" ht="12" customHeight="1">
-      <c r="A72" s="89">
+      <c r="A72" s="92">
         <v>3</v>
       </c>
-      <c r="B72" s="91"/>
-      <c r="C72" s="91"/>
-      <c r="D72" s="91"/>
-      <c r="E72" s="91"/>
+      <c r="B72" s="94"/>
+      <c r="C72" s="94"/>
+      <c r="D72" s="94"/>
+      <c r="E72" s="94"/>
       <c r="F72" s="21" t="s">
         <v>13</v>
       </c>
@@ -5006,11 +5006,11 @@
       <c r="AL72" s="27"/>
     </row>
     <row r="73" spans="1:38" ht="12" customHeight="1">
-      <c r="A73" s="90"/>
-      <c r="B73" s="90"/>
-      <c r="C73" s="90"/>
-      <c r="D73" s="90"/>
-      <c r="E73" s="90"/>
+      <c r="A73" s="93"/>
+      <c r="B73" s="93"/>
+      <c r="C73" s="93"/>
+      <c r="D73" s="93"/>
+      <c r="E73" s="93"/>
       <c r="F73" s="42" t="s">
         <v>14</v>
       </c>
@@ -5048,13 +5048,13 @@
       <c r="AL73" s="32"/>
     </row>
     <row r="74" spans="1:38" ht="12" customHeight="1">
-      <c r="A74" s="89">
+      <c r="A74" s="92">
         <v>4</v>
       </c>
-      <c r="B74" s="91"/>
-      <c r="C74" s="91"/>
-      <c r="D74" s="91"/>
-      <c r="E74" s="91"/>
+      <c r="B74" s="94"/>
+      <c r="C74" s="94"/>
+      <c r="D74" s="94"/>
+      <c r="E74" s="94"/>
       <c r="F74" s="33" t="s">
         <v>13</v>
       </c>
@@ -5092,11 +5092,11 @@
       <c r="AL74" s="10"/>
     </row>
     <row r="75" spans="1:38" ht="12" customHeight="1">
-      <c r="A75" s="90"/>
-      <c r="B75" s="90"/>
-      <c r="C75" s="90"/>
-      <c r="D75" s="90"/>
-      <c r="E75" s="90"/>
+      <c r="A75" s="93"/>
+      <c r="B75" s="93"/>
+      <c r="C75" s="93"/>
+      <c r="D75" s="93"/>
+      <c r="E75" s="93"/>
       <c r="F75" s="37" t="s">
         <v>14</v>
       </c>
@@ -5134,13 +5134,13 @@
       <c r="AL75" s="41"/>
     </row>
     <row r="76" spans="1:38" ht="12" customHeight="1">
-      <c r="A76" s="89">
+      <c r="A76" s="92">
         <v>5</v>
       </c>
-      <c r="B76" s="91"/>
-      <c r="C76" s="91"/>
-      <c r="D76" s="91"/>
-      <c r="E76" s="91"/>
+      <c r="B76" s="94"/>
+      <c r="C76" s="94"/>
+      <c r="D76" s="94"/>
+      <c r="E76" s="94"/>
       <c r="F76" s="21" t="s">
         <v>13</v>
       </c>
@@ -5178,11 +5178,11 @@
       <c r="AL76" s="27"/>
     </row>
     <row r="77" spans="1:38" ht="12" customHeight="1">
-      <c r="A77" s="90"/>
-      <c r="B77" s="90"/>
-      <c r="C77" s="90"/>
-      <c r="D77" s="90"/>
-      <c r="E77" s="90"/>
+      <c r="A77" s="93"/>
+      <c r="B77" s="93"/>
+      <c r="C77" s="93"/>
+      <c r="D77" s="93"/>
+      <c r="E77" s="93"/>
       <c r="F77" s="42" t="s">
         <v>14</v>
       </c>
@@ -5220,13 +5220,13 @@
       <c r="AL77" s="46"/>
     </row>
     <row r="78" spans="1:38" ht="12" customHeight="1">
-      <c r="A78" s="89">
+      <c r="A78" s="92">
         <v>6</v>
       </c>
-      <c r="B78" s="91"/>
-      <c r="C78" s="91"/>
-      <c r="D78" s="91"/>
-      <c r="E78" s="91"/>
+      <c r="B78" s="94"/>
+      <c r="C78" s="94"/>
+      <c r="D78" s="94"/>
+      <c r="E78" s="94"/>
       <c r="F78" s="33" t="s">
         <v>13</v>
       </c>
@@ -5264,11 +5264,11 @@
       <c r="AL78" s="10"/>
     </row>
     <row r="79" spans="1:38" ht="12" customHeight="1">
-      <c r="A79" s="90"/>
-      <c r="B79" s="90"/>
-      <c r="C79" s="90"/>
-      <c r="D79" s="90"/>
-      <c r="E79" s="90"/>
+      <c r="A79" s="93"/>
+      <c r="B79" s="93"/>
+      <c r="C79" s="93"/>
+      <c r="D79" s="93"/>
+      <c r="E79" s="93"/>
       <c r="F79" s="37" t="s">
         <v>14</v>
       </c>
@@ -5346,13 +5346,13 @@
       <c r="AL80" s="20"/>
     </row>
     <row r="81" spans="1:38" ht="12" customHeight="1">
-      <c r="A81" s="89">
+      <c r="A81" s="92">
         <v>1</v>
       </c>
-      <c r="B81" s="91"/>
-      <c r="C81" s="91"/>
-      <c r="D81" s="91"/>
-      <c r="E81" s="91"/>
+      <c r="B81" s="94"/>
+      <c r="C81" s="94"/>
+      <c r="D81" s="94"/>
+      <c r="E81" s="94"/>
       <c r="F81" s="21" t="s">
         <v>13</v>
       </c>
@@ -5390,11 +5390,11 @@
       <c r="AL81" s="27"/>
     </row>
     <row r="82" spans="1:38" ht="12" customHeight="1">
-      <c r="A82" s="90"/>
-      <c r="B82" s="90"/>
-      <c r="C82" s="90"/>
-      <c r="D82" s="90"/>
-      <c r="E82" s="90"/>
+      <c r="A82" s="93"/>
+      <c r="B82" s="93"/>
+      <c r="C82" s="93"/>
+      <c r="D82" s="93"/>
+      <c r="E82" s="93"/>
       <c r="F82" s="28" t="s">
         <v>14</v>
       </c>
@@ -5432,13 +5432,13 @@
       <c r="AL82" s="32"/>
     </row>
     <row r="83" spans="1:38" ht="12" customHeight="1">
-      <c r="A83" s="89">
+      <c r="A83" s="92">
         <v>2</v>
       </c>
-      <c r="B83" s="91"/>
-      <c r="C83" s="91"/>
-      <c r="D83" s="91"/>
-      <c r="E83" s="91"/>
+      <c r="B83" s="94"/>
+      <c r="C83" s="94"/>
+      <c r="D83" s="94"/>
+      <c r="E83" s="94"/>
       <c r="F83" s="33" t="s">
         <v>13</v>
       </c>
@@ -5476,11 +5476,11 @@
       <c r="AL83" s="10"/>
     </row>
     <row r="84" spans="1:38" ht="12" customHeight="1">
-      <c r="A84" s="90"/>
-      <c r="B84" s="90"/>
-      <c r="C84" s="90"/>
-      <c r="D84" s="90"/>
-      <c r="E84" s="90"/>
+      <c r="A84" s="93"/>
+      <c r="B84" s="93"/>
+      <c r="C84" s="93"/>
+      <c r="D84" s="93"/>
+      <c r="E84" s="93"/>
       <c r="F84" s="37" t="s">
         <v>14</v>
       </c>
@@ -5518,13 +5518,13 @@
       <c r="AL84" s="41"/>
     </row>
     <row r="85" spans="1:38" ht="12" customHeight="1">
-      <c r="A85" s="89">
+      <c r="A85" s="92">
         <v>3</v>
       </c>
-      <c r="B85" s="91"/>
-      <c r="C85" s="91"/>
-      <c r="D85" s="91"/>
-      <c r="E85" s="91"/>
+      <c r="B85" s="94"/>
+      <c r="C85" s="94"/>
+      <c r="D85" s="94"/>
+      <c r="E85" s="94"/>
       <c r="F85" s="21" t="s">
         <v>13</v>
       </c>
@@ -5562,11 +5562,11 @@
       <c r="AL85" s="27"/>
     </row>
     <row r="86" spans="1:38" ht="12" customHeight="1">
-      <c r="A86" s="90"/>
-      <c r="B86" s="90"/>
-      <c r="C86" s="90"/>
-      <c r="D86" s="90"/>
-      <c r="E86" s="90"/>
+      <c r="A86" s="93"/>
+      <c r="B86" s="93"/>
+      <c r="C86" s="93"/>
+      <c r="D86" s="93"/>
+      <c r="E86" s="93"/>
       <c r="F86" s="42" t="s">
         <v>14</v>
       </c>
@@ -5604,13 +5604,13 @@
       <c r="AL86" s="32"/>
     </row>
     <row r="87" spans="1:38" ht="12" customHeight="1">
-      <c r="A87" s="89">
+      <c r="A87" s="92">
         <v>4</v>
       </c>
-      <c r="B87" s="91"/>
-      <c r="C87" s="91"/>
-      <c r="D87" s="91"/>
-      <c r="E87" s="91"/>
+      <c r="B87" s="94"/>
+      <c r="C87" s="94"/>
+      <c r="D87" s="94"/>
+      <c r="E87" s="94"/>
       <c r="F87" s="33" t="s">
         <v>13</v>
       </c>
@@ -5648,11 +5648,11 @@
       <c r="AL87" s="10"/>
     </row>
     <row r="88" spans="1:38" ht="12" customHeight="1">
-      <c r="A88" s="90"/>
-      <c r="B88" s="90"/>
-      <c r="C88" s="90"/>
-      <c r="D88" s="90"/>
-      <c r="E88" s="90"/>
+      <c r="A88" s="93"/>
+      <c r="B88" s="93"/>
+      <c r="C88" s="93"/>
+      <c r="D88" s="93"/>
+      <c r="E88" s="93"/>
       <c r="F88" s="42" t="s">
         <v>14</v>
       </c>
@@ -42331,6 +42331,197 @@
     </row>
   </sheetData>
   <mergeCells count="215">
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="E68:E69"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="E70:E71"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="D59:D60"/>
+    <mergeCell ref="E59:E60"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="E61:E62"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="Q5:R5"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="U5:V5"/>
+    <mergeCell ref="W5:X5"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G3:AL4"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="U6:V6"/>
+    <mergeCell ref="W6:X6"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="C81:C82"/>
+    <mergeCell ref="D81:D82"/>
+    <mergeCell ref="E81:E82"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="C83:C84"/>
+    <mergeCell ref="D83:D84"/>
+    <mergeCell ref="E83:E84"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="E85:E86"/>
+    <mergeCell ref="D78:D79"/>
+    <mergeCell ref="E78:E79"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="D76:D77"/>
+    <mergeCell ref="E76:E77"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="E57:E58"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="D74:D75"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="E74:E75"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C65:C66"/>
+    <mergeCell ref="D65:D66"/>
+    <mergeCell ref="E65:E66"/>
+    <mergeCell ref="D63:D64"/>
+    <mergeCell ref="E63:E64"/>
+    <mergeCell ref="A63:A64"/>
     <mergeCell ref="A46:A47"/>
     <mergeCell ref="B46:B47"/>
     <mergeCell ref="C46:C47"/>
@@ -42355,197 +42546,6 @@
     <mergeCell ref="B50:B51"/>
     <mergeCell ref="C50:C51"/>
     <mergeCell ref="D50:D51"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="D57:D58"/>
-    <mergeCell ref="E57:E58"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="D74:D75"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="E74:E75"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C65:C66"/>
-    <mergeCell ref="D65:D66"/>
-    <mergeCell ref="E65:E66"/>
-    <mergeCell ref="D63:D64"/>
-    <mergeCell ref="E63:E64"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="D78:D79"/>
-    <mergeCell ref="E78:E79"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="C76:C77"/>
-    <mergeCell ref="D76:D77"/>
-    <mergeCell ref="E76:E77"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="A81:A82"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="C81:C82"/>
-    <mergeCell ref="D81:D82"/>
-    <mergeCell ref="E81:E82"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="C83:C84"/>
-    <mergeCell ref="D83:D84"/>
-    <mergeCell ref="E83:E84"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="E85:E86"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="W5:X5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G3:AL4"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="Q6:R6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="U6:V6"/>
-    <mergeCell ref="W6:X6"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="Q5:R5"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="D61:D62"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="B59:B60"/>
-    <mergeCell ref="C59:C60"/>
-    <mergeCell ref="D59:D60"/>
-    <mergeCell ref="E59:E60"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="E61:E62"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="E68:E69"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="E70:E71"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="E50:E51"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="E19:E20"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <dataValidations count="1">

--- a/進捗管理表/進捗管理表_志賀.xlsx
+++ b/進捗管理表/進捗管理表_志賀.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-04\Documents\プロジェクト演習\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8584B592-CEC5-432D-90F6-E3F3E39C22A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{254DE6FB-A013-4EE8-9F6B-0D70DE7D7931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5175" yWindow="0" windowWidth="15315" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="小工程" sheetId="1" r:id="rId1"/>
@@ -1232,7 +1232,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1464,9 +1464,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1509,26 +1506,47 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1566,26 +1584,29 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1896,142 +1917,142 @@
       <c r="AL2" s="2"/>
     </row>
     <row r="3" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A3" s="111" t="s">
+      <c r="A3" s="95" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="113" t="s">
+      <c r="B3" s="97" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="102">
+      <c r="G3" s="108">
         <v>45705</v>
       </c>
-      <c r="H3" s="103"/>
-      <c r="I3" s="103"/>
-      <c r="J3" s="103"/>
-      <c r="K3" s="103"/>
-      <c r="L3" s="103"/>
-      <c r="M3" s="103"/>
-      <c r="N3" s="103"/>
-      <c r="O3" s="103"/>
-      <c r="P3" s="103"/>
-      <c r="Q3" s="103"/>
-      <c r="R3" s="103"/>
-      <c r="S3" s="103"/>
-      <c r="T3" s="103"/>
-      <c r="U3" s="103"/>
-      <c r="V3" s="103"/>
-      <c r="W3" s="103"/>
-      <c r="X3" s="103"/>
-      <c r="Y3" s="103"/>
-      <c r="Z3" s="103"/>
-      <c r="AA3" s="103"/>
-      <c r="AB3" s="103"/>
-      <c r="AC3" s="103"/>
-      <c r="AD3" s="103"/>
-      <c r="AE3" s="103"/>
-      <c r="AF3" s="103"/>
-      <c r="AG3" s="103"/>
-      <c r="AH3" s="103"/>
-      <c r="AI3" s="103"/>
-      <c r="AJ3" s="103"/>
-      <c r="AK3" s="103"/>
-      <c r="AL3" s="104"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="109"/>
+      <c r="K3" s="109"/>
+      <c r="L3" s="109"/>
+      <c r="M3" s="109"/>
+      <c r="N3" s="109"/>
+      <c r="O3" s="109"/>
+      <c r="P3" s="109"/>
+      <c r="Q3" s="109"/>
+      <c r="R3" s="109"/>
+      <c r="S3" s="109"/>
+      <c r="T3" s="109"/>
+      <c r="U3" s="109"/>
+      <c r="V3" s="109"/>
+      <c r="W3" s="109"/>
+      <c r="X3" s="109"/>
+      <c r="Y3" s="109"/>
+      <c r="Z3" s="109"/>
+      <c r="AA3" s="109"/>
+      <c r="AB3" s="109"/>
+      <c r="AC3" s="109"/>
+      <c r="AD3" s="109"/>
+      <c r="AE3" s="109"/>
+      <c r="AF3" s="109"/>
+      <c r="AG3" s="109"/>
+      <c r="AH3" s="109"/>
+      <c r="AI3" s="109"/>
+      <c r="AJ3" s="109"/>
+      <c r="AK3" s="109"/>
+      <c r="AL3" s="110"/>
     </row>
     <row r="4" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A4" s="112"/>
-      <c r="B4" s="112"/>
-      <c r="C4" s="114" t="s">
+      <c r="A4" s="96"/>
+      <c r="B4" s="96"/>
+      <c r="C4" s="98" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="111" t="s">
+      <c r="D4" s="95" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="117" t="s">
+      <c r="E4" s="102" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="99" t="s">
+      <c r="F4" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="105"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="106"/>
-      <c r="K4" s="106"/>
-      <c r="L4" s="106"/>
-      <c r="M4" s="106"/>
-      <c r="N4" s="106"/>
-      <c r="O4" s="106"/>
-      <c r="P4" s="106"/>
-      <c r="Q4" s="106"/>
-      <c r="R4" s="106"/>
-      <c r="S4" s="106"/>
-      <c r="T4" s="106"/>
-      <c r="U4" s="106"/>
-      <c r="V4" s="106"/>
-      <c r="W4" s="106"/>
-      <c r="X4" s="106"/>
-      <c r="Y4" s="106"/>
-      <c r="Z4" s="106"/>
-      <c r="AA4" s="106"/>
-      <c r="AB4" s="106"/>
-      <c r="AC4" s="106"/>
-      <c r="AD4" s="106"/>
-      <c r="AE4" s="106"/>
-      <c r="AF4" s="106"/>
-      <c r="AG4" s="106"/>
-      <c r="AH4" s="106"/>
-      <c r="AI4" s="106"/>
-      <c r="AJ4" s="106"/>
-      <c r="AK4" s="106"/>
-      <c r="AL4" s="107"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="112"/>
+      <c r="L4" s="112"/>
+      <c r="M4" s="112"/>
+      <c r="N4" s="112"/>
+      <c r="O4" s="112"/>
+      <c r="P4" s="112"/>
+      <c r="Q4" s="112"/>
+      <c r="R4" s="112"/>
+      <c r="S4" s="112"/>
+      <c r="T4" s="112"/>
+      <c r="U4" s="112"/>
+      <c r="V4" s="112"/>
+      <c r="W4" s="112"/>
+      <c r="X4" s="112"/>
+      <c r="Y4" s="112"/>
+      <c r="Z4" s="112"/>
+      <c r="AA4" s="112"/>
+      <c r="AB4" s="112"/>
+      <c r="AC4" s="112"/>
+      <c r="AD4" s="112"/>
+      <c r="AE4" s="112"/>
+      <c r="AF4" s="112"/>
+      <c r="AG4" s="112"/>
+      <c r="AH4" s="112"/>
+      <c r="AI4" s="112"/>
+      <c r="AJ4" s="112"/>
+      <c r="AK4" s="112"/>
+      <c r="AL4" s="113"/>
     </row>
     <row r="5" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A5" s="112"/>
-      <c r="B5" s="112"/>
-      <c r="C5" s="112"/>
-      <c r="D5" s="112"/>
-      <c r="E5" s="112"/>
-      <c r="F5" s="100"/>
-      <c r="G5" s="96">
+      <c r="A5" s="96"/>
+      <c r="B5" s="96"/>
+      <c r="C5" s="96"/>
+      <c r="D5" s="96"/>
+      <c r="E5" s="96"/>
+      <c r="F5" s="106"/>
+      <c r="G5" s="103">
         <v>17</v>
       </c>
-      <c r="H5" s="97"/>
-      <c r="I5" s="98">
+      <c r="H5" s="104"/>
+      <c r="I5" s="99">
         <v>18</v>
       </c>
-      <c r="J5" s="115"/>
-      <c r="K5" s="98">
+      <c r="J5" s="100"/>
+      <c r="K5" s="99">
         <v>19</v>
       </c>
-      <c r="L5" s="115"/>
-      <c r="M5" s="98">
+      <c r="L5" s="100"/>
+      <c r="M5" s="99">
         <v>20</v>
       </c>
-      <c r="N5" s="115"/>
-      <c r="O5" s="98">
+      <c r="N5" s="100"/>
+      <c r="O5" s="99">
         <v>21</v>
       </c>
-      <c r="P5" s="115"/>
-      <c r="Q5" s="98">
+      <c r="P5" s="100"/>
+      <c r="Q5" s="99">
         <v>25</v>
       </c>
-      <c r="R5" s="116"/>
-      <c r="S5" s="96">
+      <c r="R5" s="101"/>
+      <c r="S5" s="103">
         <v>26</v>
       </c>
-      <c r="T5" s="97"/>
-      <c r="U5" s="98">
+      <c r="T5" s="104"/>
+      <c r="U5" s="99">
         <v>27</v>
       </c>
-      <c r="V5" s="97"/>
-      <c r="W5" s="98">
+      <c r="V5" s="104"/>
+      <c r="W5" s="99">
         <v>28</v>
       </c>
-      <c r="X5" s="97"/>
+      <c r="X5" s="104"/>
       <c r="Y5" s="10"/>
       <c r="Z5" s="10"/>
       <c r="AA5" s="10"/>
@@ -2048,48 +2069,48 @@
       <c r="AL5" s="11"/>
     </row>
     <row r="6" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A6" s="93"/>
-      <c r="B6" s="93"/>
-      <c r="C6" s="93"/>
-      <c r="D6" s="93"/>
-      <c r="E6" s="93"/>
-      <c r="F6" s="101"/>
-      <c r="G6" s="96" t="s">
+      <c r="A6" s="92"/>
+      <c r="B6" s="92"/>
+      <c r="C6" s="92"/>
+      <c r="D6" s="92"/>
+      <c r="E6" s="92"/>
+      <c r="F6" s="107"/>
+      <c r="G6" s="103" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="97"/>
-      <c r="I6" s="108" t="s">
+      <c r="H6" s="104"/>
+      <c r="I6" s="114" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="97"/>
-      <c r="K6" s="98" t="s">
+      <c r="J6" s="104"/>
+      <c r="K6" s="99" t="s">
         <v>9</v>
       </c>
-      <c r="L6" s="97"/>
-      <c r="M6" s="98" t="s">
+      <c r="L6" s="104"/>
+      <c r="M6" s="99" t="s">
         <v>10</v>
       </c>
-      <c r="N6" s="97"/>
-      <c r="O6" s="98" t="s">
+      <c r="N6" s="104"/>
+      <c r="O6" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="P6" s="97"/>
-      <c r="Q6" s="98" t="s">
+      <c r="P6" s="104"/>
+      <c r="Q6" s="99" t="s">
         <v>19</v>
       </c>
-      <c r="R6" s="97"/>
-      <c r="S6" s="109" t="s">
+      <c r="R6" s="104"/>
+      <c r="S6" s="115" t="s">
         <v>20</v>
       </c>
-      <c r="T6" s="97"/>
-      <c r="U6" s="110" t="s">
+      <c r="T6" s="104"/>
+      <c r="U6" s="116" t="s">
         <v>21</v>
       </c>
-      <c r="V6" s="97"/>
-      <c r="W6" s="110" t="s">
+      <c r="V6" s="104"/>
+      <c r="W6" s="116" t="s">
         <v>22</v>
       </c>
-      <c r="X6" s="97"/>
+      <c r="X6" s="104"/>
       <c r="Y6" s="10"/>
       <c r="Z6" s="10"/>
       <c r="AA6" s="10"/>
@@ -2190,19 +2211,19 @@
       <c r="AL8" s="20"/>
     </row>
     <row r="9" spans="1:38" ht="12" customHeight="1">
-      <c r="A9" s="92">
+      <c r="A9" s="93">
         <v>1</v>
       </c>
-      <c r="B9" s="94" t="s">
+      <c r="B9" s="91" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="94">
+      <c r="C9" s="91">
         <v>2</v>
       </c>
-      <c r="D9" s="94" t="s">
+      <c r="D9" s="91" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="94"/>
+      <c r="E9" s="91"/>
       <c r="F9" s="21" t="s">
         <v>13</v>
       </c>
@@ -2240,16 +2261,16 @@
       <c r="AL9" s="27"/>
     </row>
     <row r="10" spans="1:38" ht="12" customHeight="1">
-      <c r="A10" s="93"/>
-      <c r="B10" s="93"/>
-      <c r="C10" s="93"/>
-      <c r="D10" s="93"/>
-      <c r="E10" s="93"/>
+      <c r="A10" s="92"/>
+      <c r="B10" s="92"/>
+      <c r="C10" s="92"/>
+      <c r="D10" s="92"/>
+      <c r="E10" s="92"/>
       <c r="F10" s="28" t="s">
         <v>14</v>
       </c>
       <c r="G10" s="29"/>
-      <c r="H10" s="86"/>
+      <c r="H10" s="85"/>
       <c r="I10" s="30"/>
       <c r="J10" s="30"/>
       <c r="K10" s="30"/>
@@ -2282,19 +2303,19 @@
       <c r="AL10" s="32"/>
     </row>
     <row r="11" spans="1:38" ht="12" customHeight="1">
-      <c r="A11" s="92">
+      <c r="A11" s="93">
         <v>2</v>
       </c>
-      <c r="B11" s="94" t="s">
+      <c r="B11" s="91" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="94">
+      <c r="C11" s="91">
         <v>2</v>
       </c>
-      <c r="D11" s="94" t="s">
+      <c r="D11" s="91" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="94"/>
+      <c r="E11" s="91"/>
       <c r="F11" s="33" t="s">
         <v>13</v>
       </c>
@@ -2332,11 +2353,11 @@
       <c r="AL11" s="10"/>
     </row>
     <row r="12" spans="1:38" ht="12" customHeight="1">
-      <c r="A12" s="93"/>
-      <c r="B12" s="93"/>
-      <c r="C12" s="93"/>
-      <c r="D12" s="93"/>
-      <c r="E12" s="93"/>
+      <c r="A12" s="92"/>
+      <c r="B12" s="92"/>
+      <c r="C12" s="92"/>
+      <c r="D12" s="92"/>
+      <c r="E12" s="92"/>
       <c r="F12" s="37" t="s">
         <v>14</v>
       </c>
@@ -2344,8 +2365,8 @@
       <c r="H12" s="39"/>
       <c r="I12" s="39"/>
       <c r="J12" s="39"/>
-      <c r="K12" s="89"/>
-      <c r="L12" s="89"/>
+      <c r="K12" s="88"/>
+      <c r="L12" s="88"/>
       <c r="M12" s="39"/>
       <c r="N12" s="39"/>
       <c r="O12" s="39"/>
@@ -2374,19 +2395,19 @@
       <c r="AL12" s="41"/>
     </row>
     <row r="13" spans="1:38" ht="12" customHeight="1">
-      <c r="A13" s="92">
+      <c r="A13" s="93">
         <v>3</v>
       </c>
-      <c r="B13" s="94" t="s">
+      <c r="B13" s="91" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="94">
+      <c r="C13" s="91">
         <v>1</v>
       </c>
-      <c r="D13" s="94" t="s">
+      <c r="D13" s="91" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="94"/>
+      <c r="E13" s="91"/>
       <c r="F13" s="21" t="s">
         <v>13</v>
       </c>
@@ -2424,11 +2445,11 @@
       <c r="AL13" s="27"/>
     </row>
     <row r="14" spans="1:38" ht="12" customHeight="1">
-      <c r="A14" s="93"/>
-      <c r="B14" s="93"/>
-      <c r="C14" s="93"/>
-      <c r="D14" s="93"/>
-      <c r="E14" s="93"/>
+      <c r="A14" s="92"/>
+      <c r="B14" s="92"/>
+      <c r="C14" s="92"/>
+      <c r="D14" s="92"/>
+      <c r="E14" s="92"/>
       <c r="F14" s="42" t="s">
         <v>14</v>
       </c>
@@ -2436,8 +2457,8 @@
       <c r="H14" s="44"/>
       <c r="I14" s="44"/>
       <c r="J14" s="44"/>
-      <c r="K14" s="90"/>
-      <c r="L14" s="90"/>
+      <c r="K14" s="89"/>
+      <c r="L14" s="89"/>
       <c r="M14" s="44"/>
       <c r="N14" s="44"/>
       <c r="O14" s="44"/>
@@ -2466,13 +2487,13 @@
       <c r="AL14" s="32"/>
     </row>
     <row r="15" spans="1:38" ht="12" customHeight="1">
-      <c r="A15" s="92">
+      <c r="A15" s="93">
         <v>4</v>
       </c>
-      <c r="B15" s="94"/>
-      <c r="C15" s="94"/>
-      <c r="D15" s="94"/>
-      <c r="E15" s="94"/>
+      <c r="B15" s="91"/>
+      <c r="C15" s="91"/>
+      <c r="D15" s="91"/>
+      <c r="E15" s="91"/>
       <c r="F15" s="33" t="s">
         <v>13</v>
       </c>
@@ -2510,11 +2531,11 @@
       <c r="AL15" s="10"/>
     </row>
     <row r="16" spans="1:38" ht="12" customHeight="1">
-      <c r="A16" s="93"/>
-      <c r="B16" s="93"/>
-      <c r="C16" s="93"/>
-      <c r="D16" s="93"/>
-      <c r="E16" s="93"/>
+      <c r="A16" s="92"/>
+      <c r="B16" s="92"/>
+      <c r="C16" s="92"/>
+      <c r="D16" s="92"/>
+      <c r="E16" s="92"/>
       <c r="F16" s="37" t="s">
         <v>14</v>
       </c>
@@ -2552,17 +2573,17 @@
       <c r="AL16" s="41"/>
     </row>
     <row r="17" spans="1:38" ht="12" customHeight="1">
-      <c r="A17" s="92">
+      <c r="A17" s="93">
         <v>7</v>
       </c>
-      <c r="B17" s="94" t="s">
+      <c r="B17" s="91" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="94">
+      <c r="C17" s="91">
         <v>1</v>
       </c>
-      <c r="D17" s="94"/>
-      <c r="E17" s="94"/>
+      <c r="D17" s="91"/>
+      <c r="E17" s="91"/>
       <c r="F17" s="54" t="s">
         <v>13</v>
       </c>
@@ -2600,11 +2621,11 @@
       <c r="AL17" s="69"/>
     </row>
     <row r="18" spans="1:38" ht="12" customHeight="1">
-      <c r="A18" s="93"/>
-      <c r="B18" s="95"/>
-      <c r="C18" s="95"/>
-      <c r="D18" s="95"/>
-      <c r="E18" s="95"/>
+      <c r="A18" s="92"/>
+      <c r="B18" s="94"/>
+      <c r="C18" s="94"/>
+      <c r="D18" s="94"/>
+      <c r="E18" s="94"/>
       <c r="F18" s="37" t="s">
         <v>14</v>
       </c>
@@ -2613,7 +2634,7 @@
       <c r="I18" s="48"/>
       <c r="J18" s="48"/>
       <c r="K18" s="48"/>
-      <c r="L18" s="91"/>
+      <c r="L18" s="90"/>
       <c r="M18" s="48"/>
       <c r="N18" s="48"/>
       <c r="O18" s="48"/>
@@ -2642,13 +2663,13 @@
       <c r="AL18" s="12"/>
     </row>
     <row r="19" spans="1:38" ht="12" customHeight="1">
-      <c r="A19" s="92">
+      <c r="A19" s="93">
         <v>4</v>
       </c>
-      <c r="B19" s="94"/>
-      <c r="C19" s="94"/>
-      <c r="D19" s="94"/>
-      <c r="E19" s="94"/>
+      <c r="B19" s="91"/>
+      <c r="C19" s="91"/>
+      <c r="D19" s="91"/>
+      <c r="E19" s="91"/>
       <c r="F19" s="54" t="s">
         <v>13</v>
       </c>
@@ -2686,11 +2707,11 @@
       <c r="AL19" s="69"/>
     </row>
     <row r="20" spans="1:38" ht="12" customHeight="1">
-      <c r="A20" s="93"/>
-      <c r="B20" s="93"/>
-      <c r="C20" s="93"/>
-      <c r="D20" s="93"/>
-      <c r="E20" s="93"/>
+      <c r="A20" s="92"/>
+      <c r="B20" s="92"/>
+      <c r="C20" s="92"/>
+      <c r="D20" s="92"/>
+      <c r="E20" s="92"/>
       <c r="F20" s="37" t="s">
         <v>14</v>
       </c>
@@ -2728,15 +2749,15 @@
       <c r="AL20" s="41"/>
     </row>
     <row r="21" spans="1:38" ht="12" customHeight="1">
-      <c r="A21" s="92">
+      <c r="A21" s="93">
         <v>4</v>
       </c>
-      <c r="B21" s="94" t="s">
+      <c r="B21" s="91" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="94"/>
-      <c r="D21" s="94"/>
-      <c r="E21" s="94"/>
+      <c r="C21" s="91"/>
+      <c r="D21" s="91"/>
+      <c r="E21" s="91"/>
       <c r="F21" s="54" t="s">
         <v>13</v>
       </c>
@@ -2774,11 +2795,11 @@
       <c r="AL21" s="69"/>
     </row>
     <row r="22" spans="1:38" ht="12" customHeight="1">
-      <c r="A22" s="93"/>
-      <c r="B22" s="93"/>
-      <c r="C22" s="93"/>
-      <c r="D22" s="93"/>
-      <c r="E22" s="93"/>
+      <c r="A22" s="92"/>
+      <c r="B22" s="92"/>
+      <c r="C22" s="92"/>
+      <c r="D22" s="92"/>
+      <c r="E22" s="92"/>
       <c r="F22" s="37" t="s">
         <v>14</v>
       </c>
@@ -2789,7 +2810,7 @@
       <c r="K22" s="39"/>
       <c r="L22" s="39"/>
       <c r="M22" s="39"/>
-      <c r="N22" s="89"/>
+      <c r="N22" s="88"/>
       <c r="O22" s="39"/>
       <c r="P22" s="39"/>
       <c r="Q22" s="39"/>
@@ -2816,13 +2837,13 @@
       <c r="AL22" s="41"/>
     </row>
     <row r="23" spans="1:38" ht="12" customHeight="1">
-      <c r="A23" s="92">
+      <c r="A23" s="93">
         <v>8</v>
       </c>
-      <c r="B23" s="94"/>
-      <c r="C23" s="94"/>
-      <c r="D23" s="94"/>
-      <c r="E23" s="94"/>
+      <c r="B23" s="91"/>
+      <c r="C23" s="91"/>
+      <c r="D23" s="91"/>
+      <c r="E23" s="91"/>
       <c r="F23" s="54" t="s">
         <v>13</v>
       </c>
@@ -2860,11 +2881,11 @@
       <c r="AL23" s="69"/>
     </row>
     <row r="24" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A24" s="93"/>
-      <c r="B24" s="95"/>
-      <c r="C24" s="95"/>
-      <c r="D24" s="95"/>
-      <c r="E24" s="95"/>
+      <c r="A24" s="92"/>
+      <c r="B24" s="94"/>
+      <c r="C24" s="94"/>
+      <c r="D24" s="94"/>
+      <c r="E24" s="94"/>
       <c r="F24" s="37" t="s">
         <v>14</v>
       </c>
@@ -2902,17 +2923,17 @@
       <c r="AL24" s="12"/>
     </row>
     <row r="25" spans="1:38" ht="12" customHeight="1">
-      <c r="A25" s="92">
+      <c r="A25" s="93">
         <v>9</v>
       </c>
-      <c r="B25" s="94" t="s">
+      <c r="B25" s="91" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="94">
+      <c r="C25" s="91">
         <v>2</v>
       </c>
-      <c r="D25" s="94"/>
-      <c r="E25" s="94"/>
+      <c r="D25" s="91"/>
+      <c r="E25" s="91"/>
       <c r="F25" s="21" t="s">
         <v>13</v>
       </c>
@@ -2950,11 +2971,11 @@
       <c r="AL25" s="27"/>
     </row>
     <row r="26" spans="1:38" ht="12" customHeight="1">
-      <c r="A26" s="93"/>
-      <c r="B26" s="93"/>
-      <c r="C26" s="93"/>
-      <c r="D26" s="93"/>
-      <c r="E26" s="93"/>
+      <c r="A26" s="92"/>
+      <c r="B26" s="92"/>
+      <c r="C26" s="92"/>
+      <c r="D26" s="92"/>
+      <c r="E26" s="92"/>
       <c r="F26" s="42" t="s">
         <v>14</v>
       </c>
@@ -2965,7 +2986,7 @@
       <c r="K26" s="30"/>
       <c r="L26" s="30"/>
       <c r="M26" s="30"/>
-      <c r="N26" s="86"/>
+      <c r="N26" s="85"/>
       <c r="O26" s="30"/>
       <c r="P26" s="30"/>
       <c r="Q26" s="30"/>
@@ -2992,17 +3013,17 @@
       <c r="AL26" s="46"/>
     </row>
     <row r="27" spans="1:38" ht="12" customHeight="1">
-      <c r="A27" s="92">
+      <c r="A27" s="93">
         <v>10</v>
       </c>
-      <c r="B27" s="94" t="s">
+      <c r="B27" s="91" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="94">
+      <c r="C27" s="91">
         <v>2</v>
       </c>
-      <c r="D27" s="94"/>
-      <c r="E27" s="94"/>
+      <c r="D27" s="91"/>
+      <c r="E27" s="91"/>
       <c r="F27" s="33" t="s">
         <v>13</v>
       </c>
@@ -3040,11 +3061,11 @@
       <c r="AL27" s="10"/>
     </row>
     <row r="28" spans="1:38" ht="12" customHeight="1">
-      <c r="A28" s="93"/>
-      <c r="B28" s="95"/>
-      <c r="C28" s="95"/>
-      <c r="D28" s="95"/>
-      <c r="E28" s="95"/>
+      <c r="A28" s="92"/>
+      <c r="B28" s="94"/>
+      <c r="C28" s="94"/>
+      <c r="D28" s="94"/>
+      <c r="E28" s="94"/>
       <c r="F28" s="37" t="s">
         <v>14</v>
       </c>
@@ -3055,7 +3076,7 @@
       <c r="K28" s="48"/>
       <c r="L28" s="48"/>
       <c r="M28" s="48"/>
-      <c r="N28" s="91"/>
+      <c r="N28" s="90"/>
       <c r="O28" s="48"/>
       <c r="P28" s="48"/>
       <c r="Q28" s="48"/>
@@ -3082,17 +3103,17 @@
       <c r="AL28" s="12"/>
     </row>
     <row r="29" spans="1:38" ht="12" customHeight="1">
-      <c r="A29" s="92">
+      <c r="A29" s="93">
         <v>11</v>
       </c>
-      <c r="B29" s="94" t="s">
+      <c r="B29" s="91" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="94">
+      <c r="C29" s="91">
         <v>1</v>
       </c>
-      <c r="D29" s="94"/>
-      <c r="E29" s="94"/>
+      <c r="D29" s="91"/>
+      <c r="E29" s="91"/>
       <c r="F29" s="54" t="s">
         <v>13</v>
       </c>
@@ -3130,11 +3151,11 @@
       <c r="AL29" s="69"/>
     </row>
     <row r="30" spans="1:38" ht="12" customHeight="1">
-      <c r="A30" s="93"/>
-      <c r="B30" s="95"/>
-      <c r="C30" s="95"/>
-      <c r="D30" s="95"/>
-      <c r="E30" s="95"/>
+      <c r="A30" s="92"/>
+      <c r="B30" s="94"/>
+      <c r="C30" s="94"/>
+      <c r="D30" s="94"/>
+      <c r="E30" s="94"/>
       <c r="F30" s="37" t="s">
         <v>14</v>
       </c>
@@ -3145,7 +3166,7 @@
       <c r="K30" s="48"/>
       <c r="L30" s="48"/>
       <c r="M30" s="48"/>
-      <c r="N30" s="91"/>
+      <c r="N30" s="90"/>
       <c r="O30" s="48"/>
       <c r="P30" s="48"/>
       <c r="Q30" s="48"/>
@@ -3172,13 +3193,13 @@
       <c r="AL30" s="12"/>
     </row>
     <row r="31" spans="1:38" ht="12" customHeight="1">
-      <c r="A31" s="92">
+      <c r="A31" s="93">
         <v>12</v>
       </c>
-      <c r="B31" s="94"/>
-      <c r="C31" s="94"/>
-      <c r="D31" s="94"/>
-      <c r="E31" s="94"/>
+      <c r="B31" s="91"/>
+      <c r="C31" s="91"/>
+      <c r="D31" s="91"/>
+      <c r="E31" s="91"/>
       <c r="F31" s="54" t="s">
         <v>13</v>
       </c>
@@ -3216,11 +3237,11 @@
       <c r="AL31" s="69"/>
     </row>
     <row r="32" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A32" s="93"/>
-      <c r="B32" s="95"/>
-      <c r="C32" s="95"/>
-      <c r="D32" s="95"/>
-      <c r="E32" s="95"/>
+      <c r="A32" s="92"/>
+      <c r="B32" s="94"/>
+      <c r="C32" s="94"/>
+      <c r="D32" s="94"/>
+      <c r="E32" s="94"/>
       <c r="F32" s="37" t="s">
         <v>14</v>
       </c>
@@ -3258,15 +3279,15 @@
       <c r="AL32" s="12"/>
     </row>
     <row r="33" spans="1:38" ht="12" customHeight="1">
-      <c r="A33" s="92">
+      <c r="A33" s="93">
         <v>12</v>
       </c>
-      <c r="B33" s="94" t="s">
+      <c r="B33" s="91" t="s">
         <v>35</v>
       </c>
-      <c r="C33" s="94"/>
-      <c r="D33" s="94"/>
-      <c r="E33" s="94"/>
+      <c r="C33" s="91"/>
+      <c r="D33" s="91"/>
+      <c r="E33" s="91"/>
       <c r="F33" s="54" t="s">
         <v>13</v>
       </c>
@@ -3304,11 +3325,11 @@
       <c r="AL33" s="69"/>
     </row>
     <row r="34" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A34" s="93"/>
-      <c r="B34" s="95"/>
-      <c r="C34" s="95"/>
-      <c r="D34" s="95"/>
-      <c r="E34" s="95"/>
+      <c r="A34" s="92"/>
+      <c r="B34" s="94"/>
+      <c r="C34" s="94"/>
+      <c r="D34" s="94"/>
+      <c r="E34" s="94"/>
       <c r="F34" s="37" t="s">
         <v>14</v>
       </c>
@@ -3319,7 +3340,7 @@
       <c r="K34" s="48"/>
       <c r="L34" s="48"/>
       <c r="M34" s="48"/>
-      <c r="N34" s="91"/>
+      <c r="N34" s="90"/>
       <c r="O34" s="48"/>
       <c r="P34" s="48"/>
       <c r="Q34" s="48"/>
@@ -3388,17 +3409,17 @@
       <c r="AL35" s="20"/>
     </row>
     <row r="36" spans="1:38" ht="12" customHeight="1">
-      <c r="A36" s="92">
+      <c r="A36" s="93">
         <v>1</v>
       </c>
-      <c r="B36" s="94" t="s">
+      <c r="B36" s="91" t="s">
         <v>36</v>
       </c>
-      <c r="C36" s="94">
+      <c r="C36" s="91">
         <v>0.5</v>
       </c>
-      <c r="D36" s="94"/>
-      <c r="E36" s="94"/>
+      <c r="D36" s="91"/>
+      <c r="E36" s="91"/>
       <c r="F36" s="21" t="s">
         <v>13</v>
       </c>
@@ -3435,11 +3456,11 @@
       <c r="AL36" s="27"/>
     </row>
     <row r="37" spans="1:38" ht="12" customHeight="1">
-      <c r="A37" s="93"/>
-      <c r="B37" s="95"/>
-      <c r="C37" s="93"/>
-      <c r="D37" s="93"/>
-      <c r="E37" s="93"/>
+      <c r="A37" s="92"/>
+      <c r="B37" s="94"/>
+      <c r="C37" s="92"/>
+      <c r="D37" s="92"/>
+      <c r="E37" s="92"/>
       <c r="F37" s="28" t="s">
         <v>14</v>
       </c>
@@ -3447,15 +3468,15 @@
       <c r="H37" s="30"/>
       <c r="I37" s="30"/>
       <c r="J37" s="30"/>
-      <c r="K37" s="83"/>
+      <c r="K37" s="82"/>
       <c r="L37" s="30"/>
       <c r="M37" s="30"/>
-      <c r="N37" s="30"/>
-      <c r="O37" s="30"/>
+      <c r="N37" s="85"/>
+      <c r="O37" s="117"/>
       <c r="P37" s="30"/>
       <c r="Q37" s="30"/>
       <c r="R37" s="31"/>
-      <c r="S37" s="29"/>
+      <c r="S37" s="123"/>
       <c r="T37" s="30"/>
       <c r="U37" s="30"/>
       <c r="V37" s="30"/>
@@ -3477,17 +3498,17 @@
       <c r="AL37" s="32"/>
     </row>
     <row r="38" spans="1:38" ht="12" customHeight="1">
-      <c r="A38" s="92">
+      <c r="A38" s="93">
         <v>2</v>
       </c>
-      <c r="B38" s="94" t="s">
+      <c r="B38" s="91" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="94">
+      <c r="C38" s="91">
         <v>4</v>
       </c>
-      <c r="D38" s="94"/>
-      <c r="E38" s="94"/>
+      <c r="D38" s="91"/>
+      <c r="E38" s="91"/>
       <c r="F38" s="33" t="s">
         <v>13</v>
       </c>
@@ -3495,11 +3516,11 @@
       <c r="H38" s="34"/>
       <c r="I38" s="34"/>
       <c r="J38" s="34"/>
-      <c r="K38" s="84"/>
+      <c r="K38" s="83"/>
       <c r="L38" s="53"/>
       <c r="M38" s="53"/>
       <c r="N38" s="23"/>
-      <c r="O38" s="23"/>
+      <c r="O38" s="118"/>
       <c r="P38" s="23"/>
       <c r="Q38" s="23"/>
       <c r="R38" s="51"/>
@@ -3525,11 +3546,11 @@
       <c r="AL38" s="10"/>
     </row>
     <row r="39" spans="1:38" ht="12" customHeight="1">
-      <c r="A39" s="93"/>
-      <c r="B39" s="95"/>
-      <c r="C39" s="93"/>
-      <c r="D39" s="93"/>
-      <c r="E39" s="93"/>
+      <c r="A39" s="92"/>
+      <c r="B39" s="94"/>
+      <c r="C39" s="92"/>
+      <c r="D39" s="92"/>
+      <c r="E39" s="92"/>
       <c r="F39" s="37" t="s">
         <v>14</v>
       </c>
@@ -3537,11 +3558,11 @@
       <c r="H39" s="39"/>
       <c r="I39" s="39"/>
       <c r="J39" s="39"/>
-      <c r="K39" s="83"/>
+      <c r="K39" s="82"/>
       <c r="L39" s="39"/>
       <c r="M39" s="39"/>
-      <c r="N39" s="39"/>
-      <c r="O39" s="39"/>
+      <c r="N39" s="88"/>
+      <c r="O39" s="119"/>
       <c r="P39" s="39"/>
       <c r="Q39" s="39"/>
       <c r="R39" s="40"/>
@@ -3567,17 +3588,17 @@
       <c r="AL39" s="41"/>
     </row>
     <row r="40" spans="1:38" ht="12" customHeight="1">
-      <c r="A40" s="92">
+      <c r="A40" s="93">
         <v>3</v>
       </c>
-      <c r="B40" s="94" t="s">
+      <c r="B40" s="91" t="s">
         <v>38</v>
       </c>
-      <c r="C40" s="94">
+      <c r="C40" s="91">
         <v>4</v>
       </c>
-      <c r="D40" s="94"/>
-      <c r="E40" s="94"/>
+      <c r="D40" s="91"/>
+      <c r="E40" s="91"/>
       <c r="F40" s="21" t="s">
         <v>13</v>
       </c>
@@ -3585,11 +3606,11 @@
       <c r="H40" s="24"/>
       <c r="I40" s="24"/>
       <c r="J40" s="24"/>
-      <c r="K40" s="84"/>
+      <c r="K40" s="83"/>
       <c r="L40" s="24"/>
       <c r="M40" s="52"/>
       <c r="N40" s="52"/>
-      <c r="O40" s="24"/>
+      <c r="O40" s="120"/>
       <c r="P40" s="24"/>
       <c r="Q40" s="24"/>
       <c r="R40" s="25"/>
@@ -3615,11 +3636,11 @@
       <c r="AL40" s="27"/>
     </row>
     <row r="41" spans="1:38" ht="12" customHeight="1">
-      <c r="A41" s="93"/>
-      <c r="B41" s="95"/>
-      <c r="C41" s="93"/>
-      <c r="D41" s="93"/>
-      <c r="E41" s="93"/>
+      <c r="A41" s="92"/>
+      <c r="B41" s="94"/>
+      <c r="C41" s="92"/>
+      <c r="D41" s="92"/>
+      <c r="E41" s="92"/>
       <c r="F41" s="42" t="s">
         <v>14</v>
       </c>
@@ -3629,12 +3650,12 @@
       <c r="J41" s="44"/>
       <c r="L41" s="44"/>
       <c r="M41" s="44"/>
-      <c r="N41" s="44"/>
-      <c r="O41" s="44"/>
+      <c r="N41" s="89"/>
+      <c r="O41" s="121"/>
       <c r="P41" s="44"/>
       <c r="Q41" s="44"/>
       <c r="R41" s="45"/>
-      <c r="S41" s="43"/>
+      <c r="S41" s="122"/>
       <c r="T41" s="44"/>
       <c r="U41" s="44"/>
       <c r="V41" s="44"/>
@@ -3656,13 +3677,13 @@
       <c r="AL41" s="32"/>
     </row>
     <row r="42" spans="1:38" ht="12" customHeight="1">
-      <c r="A42" s="92">
+      <c r="A42" s="93">
         <v>4</v>
       </c>
-      <c r="B42" s="94"/>
-      <c r="C42" s="94"/>
-      <c r="D42" s="94"/>
-      <c r="E42" s="94"/>
+      <c r="B42" s="91"/>
+      <c r="C42" s="91"/>
+      <c r="D42" s="91"/>
+      <c r="E42" s="91"/>
       <c r="F42" s="33" t="s">
         <v>13</v>
       </c>
@@ -3670,7 +3691,7 @@
       <c r="H42" s="34"/>
       <c r="I42" s="34"/>
       <c r="J42" s="34"/>
-      <c r="K42" s="84"/>
+      <c r="K42" s="83"/>
       <c r="L42" s="34"/>
       <c r="M42" s="34"/>
       <c r="N42" s="34"/>
@@ -3700,32 +3721,32 @@
       <c r="AL42" s="10"/>
     </row>
     <row r="43" spans="1:38" ht="12" customHeight="1">
-      <c r="A43" s="93"/>
-      <c r="B43" s="95"/>
-      <c r="C43" s="95"/>
-      <c r="D43" s="95"/>
-      <c r="E43" s="95"/>
+      <c r="A43" s="92"/>
+      <c r="B43" s="94"/>
+      <c r="C43" s="94"/>
+      <c r="D43" s="94"/>
+      <c r="E43" s="94"/>
       <c r="F43" s="37" t="s">
         <v>14</v>
       </c>
       <c r="G43" s="38"/>
-      <c r="H43" s="87"/>
-      <c r="I43" s="87"/>
-      <c r="J43" s="87"/>
-      <c r="K43" s="83"/>
-      <c r="L43" s="87"/>
-      <c r="M43" s="87"/>
-      <c r="N43" s="87"/>
-      <c r="O43" s="87"/>
-      <c r="P43" s="87"/>
-      <c r="Q43" s="87"/>
+      <c r="H43" s="86"/>
+      <c r="I43" s="86"/>
+      <c r="J43" s="86"/>
+      <c r="K43" s="82"/>
+      <c r="L43" s="86"/>
+      <c r="M43" s="86"/>
+      <c r="N43" s="86"/>
+      <c r="O43" s="86"/>
+      <c r="P43" s="86"/>
+      <c r="Q43" s="86"/>
       <c r="R43" s="40"/>
       <c r="S43" s="38"/>
-      <c r="T43" s="87"/>
-      <c r="U43" s="87"/>
-      <c r="V43" s="87"/>
-      <c r="W43" s="87"/>
-      <c r="X43" s="87"/>
+      <c r="T43" s="86"/>
+      <c r="U43" s="86"/>
+      <c r="V43" s="86"/>
+      <c r="W43" s="86"/>
+      <c r="X43" s="86"/>
       <c r="Y43" s="10"/>
       <c r="Z43" s="10"/>
       <c r="AA43" s="10"/>
@@ -3742,17 +3763,17 @@
       <c r="AL43" s="41"/>
     </row>
     <row r="44" spans="1:38" ht="12" customHeight="1">
-      <c r="A44" s="92">
+      <c r="A44" s="93">
         <v>5</v>
       </c>
-      <c r="B44" s="94" t="s">
+      <c r="B44" s="91" t="s">
         <v>39</v>
       </c>
-      <c r="C44" s="94">
+      <c r="C44" s="91">
         <v>0.5</v>
       </c>
-      <c r="D44" s="94"/>
-      <c r="E44" s="94"/>
+      <c r="D44" s="91"/>
+      <c r="E44" s="91"/>
       <c r="F44" s="54" t="s">
         <v>13</v>
       </c>
@@ -3760,10 +3781,10 @@
       <c r="H44" s="56"/>
       <c r="I44" s="56"/>
       <c r="J44" s="56"/>
-      <c r="K44" s="84"/>
+      <c r="K44" s="83"/>
       <c r="L44" s="56"/>
       <c r="M44" s="56"/>
-      <c r="N44" s="88"/>
+      <c r="N44" s="87"/>
       <c r="O44" s="56"/>
       <c r="P44" s="56"/>
       <c r="Q44" s="56"/>
@@ -3780,21 +3801,21 @@
       <c r="AB44" s="10"/>
       <c r="AC44" s="10"/>
       <c r="AD44" s="10"/>
-      <c r="AE44" s="79"/>
-      <c r="AF44" s="79"/>
-      <c r="AG44" s="79"/>
-      <c r="AH44" s="79"/>
-      <c r="AI44" s="79"/>
-      <c r="AJ44" s="79"/>
-      <c r="AK44" s="79"/>
-      <c r="AL44" s="79"/>
+      <c r="AE44" s="78"/>
+      <c r="AF44" s="78"/>
+      <c r="AG44" s="78"/>
+      <c r="AH44" s="78"/>
+      <c r="AI44" s="78"/>
+      <c r="AJ44" s="78"/>
+      <c r="AK44" s="78"/>
+      <c r="AL44" s="78"/>
     </row>
     <row r="45" spans="1:38" ht="12" customHeight="1">
-      <c r="A45" s="93"/>
-      <c r="B45" s="95"/>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="A45" s="92"/>
+      <c r="B45" s="94"/>
+      <c r="C45" s="94"/>
+      <c r="D45" s="94"/>
+      <c r="E45" s="94"/>
       <c r="F45" s="37" t="s">
         <v>14</v>
       </c>
@@ -3802,7 +3823,7 @@
       <c r="H45" s="39"/>
       <c r="I45" s="39"/>
       <c r="J45" s="39"/>
-      <c r="K45" s="85"/>
+      <c r="K45" s="84"/>
       <c r="L45" s="39"/>
       <c r="M45" s="39"/>
       <c r="N45" s="39"/>
@@ -3832,13 +3853,13 @@
       <c r="AL45" s="41"/>
     </row>
     <row r="46" spans="1:38" ht="12" customHeight="1">
-      <c r="A46" s="92">
+      <c r="A46" s="93">
         <v>6</v>
       </c>
-      <c r="B46" s="94"/>
-      <c r="C46" s="94"/>
-      <c r="D46" s="94"/>
-      <c r="E46" s="94"/>
+      <c r="B46" s="91"/>
+      <c r="C46" s="91"/>
+      <c r="D46" s="91"/>
+      <c r="E46" s="91"/>
       <c r="F46" s="21" t="s">
         <v>13</v>
       </c>
@@ -3875,11 +3896,11 @@
       <c r="AL46" s="27"/>
     </row>
     <row r="47" spans="1:38" ht="12" customHeight="1">
-      <c r="A47" s="93"/>
-      <c r="B47" s="95"/>
-      <c r="C47" s="93"/>
-      <c r="D47" s="93"/>
-      <c r="E47" s="93"/>
+      <c r="A47" s="92"/>
+      <c r="B47" s="94"/>
+      <c r="C47" s="92"/>
+      <c r="D47" s="92"/>
+      <c r="E47" s="92"/>
       <c r="F47" s="42" t="s">
         <v>14</v>
       </c>
@@ -3887,7 +3908,7 @@
       <c r="H47" s="30"/>
       <c r="I47" s="30"/>
       <c r="J47" s="30"/>
-      <c r="K47" s="83"/>
+      <c r="K47" s="82"/>
       <c r="L47" s="30"/>
       <c r="M47" s="30"/>
       <c r="N47" s="30"/>
@@ -3917,17 +3938,17 @@
       <c r="AL47" s="46"/>
     </row>
     <row r="48" spans="1:38" ht="12" customHeight="1">
-      <c r="A48" s="92">
+      <c r="A48" s="93">
         <v>7</v>
       </c>
-      <c r="B48" s="94" t="s">
+      <c r="B48" s="91" t="s">
         <v>40</v>
       </c>
-      <c r="C48" s="94">
+      <c r="C48" s="91">
         <v>0.5</v>
       </c>
-      <c r="D48" s="94"/>
-      <c r="E48" s="94"/>
+      <c r="D48" s="91"/>
+      <c r="E48" s="91"/>
       <c r="F48" s="21" t="s">
         <v>13</v>
       </c>
@@ -3935,7 +3956,7 @@
       <c r="H48" s="24"/>
       <c r="I48" s="24"/>
       <c r="J48" s="24"/>
-      <c r="K48" s="84"/>
+      <c r="K48" s="83"/>
       <c r="L48" s="24"/>
       <c r="M48" s="24"/>
       <c r="N48" s="24"/>
@@ -3965,11 +3986,11 @@
       <c r="AL48" s="27"/>
     </row>
     <row r="49" spans="1:38" ht="12" customHeight="1">
-      <c r="A49" s="93"/>
-      <c r="B49" s="95"/>
-      <c r="C49" s="93"/>
-      <c r="D49" s="93"/>
-      <c r="E49" s="93"/>
+      <c r="A49" s="92"/>
+      <c r="B49" s="94"/>
+      <c r="C49" s="92"/>
+      <c r="D49" s="92"/>
+      <c r="E49" s="92"/>
       <c r="F49" s="42" t="s">
         <v>14</v>
       </c>
@@ -3977,13 +3998,13 @@
       <c r="H49" s="30"/>
       <c r="I49" s="30"/>
       <c r="J49" s="30"/>
-      <c r="K49" s="85"/>
+      <c r="K49" s="84"/>
       <c r="L49" s="30"/>
       <c r="M49" s="30"/>
       <c r="N49" s="30"/>
       <c r="O49" s="30"/>
       <c r="P49" s="30"/>
-      <c r="Q49" s="30"/>
+      <c r="Q49" s="85"/>
       <c r="R49" s="31"/>
       <c r="S49" s="29"/>
       <c r="T49" s="30"/>
@@ -4007,17 +4028,17 @@
       <c r="AL49" s="46"/>
     </row>
     <row r="50" spans="1:38" ht="12" customHeight="1">
-      <c r="A50" s="92">
+      <c r="A50" s="93">
         <v>8</v>
       </c>
-      <c r="B50" s="94" t="s">
+      <c r="B50" s="91" t="s">
         <v>41</v>
       </c>
-      <c r="C50" s="94">
+      <c r="C50" s="91">
         <v>4</v>
       </c>
-      <c r="D50" s="94"/>
-      <c r="E50" s="94"/>
+      <c r="D50" s="91"/>
+      <c r="E50" s="91"/>
       <c r="F50" s="21" t="s">
         <v>13</v>
       </c>
@@ -4054,11 +4075,11 @@
       <c r="AL50" s="27"/>
     </row>
     <row r="51" spans="1:38" ht="12" customHeight="1">
-      <c r="A51" s="93"/>
-      <c r="B51" s="95"/>
-      <c r="C51" s="93"/>
-      <c r="D51" s="93"/>
-      <c r="E51" s="93"/>
+      <c r="A51" s="92"/>
+      <c r="B51" s="94"/>
+      <c r="C51" s="92"/>
+      <c r="D51" s="92"/>
+      <c r="E51" s="92"/>
       <c r="F51" s="42" t="s">
         <v>14</v>
       </c>
@@ -4066,13 +4087,13 @@
       <c r="H51" s="30"/>
       <c r="I51" s="30"/>
       <c r="J51" s="30"/>
-      <c r="K51" s="83"/>
+      <c r="K51" s="82"/>
       <c r="L51" s="30"/>
       <c r="M51" s="30"/>
       <c r="N51" s="30"/>
       <c r="O51" s="30"/>
       <c r="P51" s="30"/>
-      <c r="Q51" s="30"/>
+      <c r="Q51" s="85"/>
       <c r="R51" s="31"/>
       <c r="S51" s="29"/>
       <c r="T51" s="30"/>
@@ -4096,13 +4117,13 @@
       <c r="AL51" s="46"/>
     </row>
     <row r="52" spans="1:38" ht="12" customHeight="1">
-      <c r="A52" s="92">
+      <c r="A52" s="93">
         <v>9</v>
       </c>
-      <c r="B52" s="94"/>
-      <c r="C52" s="94"/>
-      <c r="D52" s="94"/>
-      <c r="E52" s="94"/>
+      <c r="B52" s="91"/>
+      <c r="C52" s="91"/>
+      <c r="D52" s="91"/>
+      <c r="E52" s="91"/>
       <c r="F52" s="21" t="s">
         <v>13</v>
       </c>
@@ -4110,7 +4131,7 @@
       <c r="H52" s="24"/>
       <c r="I52" s="24"/>
       <c r="J52" s="24"/>
-      <c r="K52" s="84"/>
+      <c r="K52" s="83"/>
       <c r="L52" s="24"/>
       <c r="M52" s="24"/>
       <c r="N52" s="24"/>
@@ -4140,11 +4161,11 @@
       <c r="AL52" s="27"/>
     </row>
     <row r="53" spans="1:38" ht="12" customHeight="1">
-      <c r="A53" s="93"/>
-      <c r="B53" s="95"/>
-      <c r="C53" s="93"/>
-      <c r="D53" s="93"/>
-      <c r="E53" s="93"/>
+      <c r="A53" s="92"/>
+      <c r="B53" s="94"/>
+      <c r="C53" s="92"/>
+      <c r="D53" s="92"/>
+      <c r="E53" s="92"/>
       <c r="F53" s="42" t="s">
         <v>14</v>
       </c>
@@ -4152,7 +4173,7 @@
       <c r="H53" s="30"/>
       <c r="I53" s="30"/>
       <c r="J53" s="30"/>
-      <c r="K53" s="83"/>
+      <c r="K53" s="82"/>
       <c r="L53" s="30"/>
       <c r="M53" s="30"/>
       <c r="N53" s="30"/>
@@ -4182,15 +4203,15 @@
       <c r="AL53" s="46"/>
     </row>
     <row r="54" spans="1:38" ht="11.25" customHeight="1">
-      <c r="A54" s="92">
+      <c r="A54" s="93">
         <v>10</v>
       </c>
-      <c r="B54" s="94" t="s">
+      <c r="B54" s="91" t="s">
         <v>35</v>
       </c>
-      <c r="C54" s="94"/>
-      <c r="D54" s="94"/>
-      <c r="E54" s="94"/>
+      <c r="C54" s="91"/>
+      <c r="D54" s="91"/>
+      <c r="E54" s="91"/>
       <c r="F54" s="33" t="s">
         <v>13</v>
       </c>
@@ -4198,13 +4219,13 @@
       <c r="H54" s="34"/>
       <c r="I54" s="34"/>
       <c r="J54" s="34"/>
-      <c r="K54" s="84"/>
+      <c r="K54" s="83"/>
       <c r="L54" s="34"/>
       <c r="M54" s="34"/>
       <c r="N54" s="34"/>
       <c r="O54" s="34"/>
       <c r="P54" s="34"/>
-      <c r="Q54" s="82"/>
+      <c r="Q54" s="81"/>
       <c r="R54" s="35"/>
       <c r="S54" s="36"/>
       <c r="T54" s="34"/>
@@ -4228,11 +4249,11 @@
       <c r="AL54" s="10"/>
     </row>
     <row r="55" spans="1:38" ht="12" customHeight="1">
-      <c r="A55" s="93"/>
-      <c r="B55" s="95"/>
-      <c r="C55" s="93"/>
-      <c r="D55" s="93"/>
-      <c r="E55" s="93"/>
+      <c r="A55" s="92"/>
+      <c r="B55" s="94"/>
+      <c r="C55" s="92"/>
+      <c r="D55" s="92"/>
+      <c r="E55" s="92"/>
       <c r="F55" s="37" t="s">
         <v>14</v>
       </c>
@@ -4310,15 +4331,15 @@
       <c r="AL56" s="20"/>
     </row>
     <row r="57" spans="1:38" ht="12" customHeight="1">
-      <c r="A57" s="92">
+      <c r="A57" s="93">
         <v>1</v>
       </c>
-      <c r="B57" s="94" t="s">
+      <c r="B57" s="91" t="s">
         <v>23</v>
       </c>
-      <c r="C57" s="94"/>
-      <c r="D57" s="94"/>
-      <c r="E57" s="94"/>
+      <c r="C57" s="91"/>
+      <c r="D57" s="91"/>
+      <c r="E57" s="91"/>
       <c r="F57" s="21" t="s">
         <v>13</v>
       </c>
@@ -4334,7 +4355,7 @@
       <c r="P57" s="24"/>
       <c r="Q57" s="62"/>
       <c r="R57" s="70"/>
-      <c r="S57" s="77"/>
+      <c r="S57" s="124"/>
       <c r="T57" s="24"/>
       <c r="U57" s="24"/>
       <c r="V57" s="24"/>
@@ -4356,11 +4377,11 @@
       <c r="AL57" s="27"/>
     </row>
     <row r="58" spans="1:38" ht="12" customHeight="1">
-      <c r="A58" s="93"/>
-      <c r="B58" s="93"/>
-      <c r="C58" s="93"/>
-      <c r="D58" s="93"/>
-      <c r="E58" s="93"/>
+      <c r="A58" s="92"/>
+      <c r="B58" s="92"/>
+      <c r="C58" s="92"/>
+      <c r="D58" s="92"/>
+      <c r="E58" s="92"/>
       <c r="F58" s="28" t="s">
         <v>14</v>
       </c>
@@ -4376,7 +4397,7 @@
       <c r="P58" s="30"/>
       <c r="Q58" s="63"/>
       <c r="R58" s="71"/>
-      <c r="S58" s="78"/>
+      <c r="S58" s="77"/>
       <c r="T58" s="30"/>
       <c r="U58" s="30"/>
       <c r="V58" s="30"/>
@@ -4398,15 +4419,15 @@
       <c r="AL58" s="32"/>
     </row>
     <row r="59" spans="1:38" ht="12" customHeight="1">
-      <c r="A59" s="92">
+      <c r="A59" s="93">
         <v>2</v>
       </c>
-      <c r="B59" s="94" t="s">
+      <c r="B59" s="91" t="s">
         <v>24</v>
       </c>
-      <c r="C59" s="94"/>
-      <c r="D59" s="94"/>
-      <c r="E59" s="94"/>
+      <c r="C59" s="91"/>
+      <c r="D59" s="91"/>
+      <c r="E59" s="91"/>
       <c r="F59" s="33" t="s">
         <v>13</v>
       </c>
@@ -4421,8 +4442,8 @@
       <c r="O59" s="34"/>
       <c r="P59" s="34"/>
       <c r="Q59" s="64"/>
-      <c r="R59" s="81"/>
-      <c r="S59" s="80"/>
+      <c r="R59" s="80"/>
+      <c r="S59" s="79"/>
       <c r="T59" s="34"/>
       <c r="U59" s="34"/>
       <c r="V59" s="34"/>
@@ -4444,11 +4465,11 @@
       <c r="AL59" s="10"/>
     </row>
     <row r="60" spans="1:38" ht="12" customHeight="1">
-      <c r="A60" s="93"/>
-      <c r="B60" s="93"/>
-      <c r="C60" s="93"/>
-      <c r="D60" s="93"/>
-      <c r="E60" s="93"/>
+      <c r="A60" s="92"/>
+      <c r="B60" s="92"/>
+      <c r="C60" s="92"/>
+      <c r="D60" s="92"/>
+      <c r="E60" s="92"/>
       <c r="F60" s="37" t="s">
         <v>14</v>
       </c>
@@ -4464,7 +4485,7 @@
       <c r="P60" s="39"/>
       <c r="Q60" s="65"/>
       <c r="R60" s="4"/>
-      <c r="S60" s="78"/>
+      <c r="S60" s="77"/>
       <c r="T60" s="39"/>
       <c r="U60" s="39"/>
       <c r="V60" s="39"/>
@@ -4486,15 +4507,15 @@
       <c r="AL60" s="41"/>
     </row>
     <row r="61" spans="1:38" ht="12" customHeight="1">
-      <c r="A61" s="92">
+      <c r="A61" s="93">
         <v>3</v>
       </c>
-      <c r="B61" s="94" t="s">
+      <c r="B61" s="91" t="s">
         <v>25</v>
       </c>
-      <c r="C61" s="94"/>
-      <c r="D61" s="94"/>
-      <c r="E61" s="94"/>
+      <c r="C61" s="91"/>
+      <c r="D61" s="91"/>
+      <c r="E61" s="91"/>
       <c r="F61" s="21" t="s">
         <v>13</v>
       </c>
@@ -4532,11 +4553,11 @@
       <c r="AL61" s="27"/>
     </row>
     <row r="62" spans="1:38" ht="12" customHeight="1">
-      <c r="A62" s="93"/>
-      <c r="B62" s="93"/>
-      <c r="C62" s="93"/>
-      <c r="D62" s="93"/>
-      <c r="E62" s="93"/>
+      <c r="A62" s="92"/>
+      <c r="B62" s="92"/>
+      <c r="C62" s="92"/>
+      <c r="D62" s="92"/>
+      <c r="E62" s="92"/>
       <c r="F62" s="42" t="s">
         <v>14</v>
       </c>
@@ -4574,15 +4595,15 @@
       <c r="AL62" s="32"/>
     </row>
     <row r="63" spans="1:38" ht="12" customHeight="1">
-      <c r="A63" s="92">
+      <c r="A63" s="93">
         <v>4</v>
       </c>
-      <c r="B63" s="94" t="s">
+      <c r="B63" s="91" t="s">
         <v>26</v>
       </c>
-      <c r="C63" s="94"/>
-      <c r="D63" s="94"/>
-      <c r="E63" s="94"/>
+      <c r="C63" s="91"/>
+      <c r="D63" s="91"/>
+      <c r="E63" s="91"/>
       <c r="F63" s="21" t="s">
         <v>13</v>
       </c>
@@ -4620,11 +4641,11 @@
       <c r="AL63" s="27"/>
     </row>
     <row r="64" spans="1:38" ht="12" customHeight="1">
-      <c r="A64" s="93"/>
-      <c r="B64" s="93"/>
-      <c r="C64" s="93"/>
-      <c r="D64" s="93"/>
-      <c r="E64" s="93"/>
+      <c r="A64" s="92"/>
+      <c r="B64" s="92"/>
+      <c r="C64" s="92"/>
+      <c r="D64" s="92"/>
+      <c r="E64" s="92"/>
       <c r="F64" s="42" t="s">
         <v>14</v>
       </c>
@@ -4662,13 +4683,13 @@
       <c r="AL64" s="46"/>
     </row>
     <row r="65" spans="1:38" ht="12" customHeight="1">
-      <c r="A65" s="92">
+      <c r="A65" s="93">
         <v>5</v>
       </c>
-      <c r="B65" s="94"/>
-      <c r="C65" s="94"/>
-      <c r="D65" s="94"/>
-      <c r="E65" s="94"/>
+      <c r="B65" s="91"/>
+      <c r="C65" s="91"/>
+      <c r="D65" s="91"/>
+      <c r="E65" s="91"/>
       <c r="F65" s="33" t="s">
         <v>13</v>
       </c>
@@ -4706,11 +4727,11 @@
       <c r="AL65" s="10"/>
     </row>
     <row r="66" spans="1:38" ht="12" customHeight="1">
-      <c r="A66" s="93"/>
-      <c r="B66" s="93"/>
-      <c r="C66" s="93"/>
-      <c r="D66" s="93"/>
-      <c r="E66" s="93"/>
+      <c r="A66" s="92"/>
+      <c r="B66" s="92"/>
+      <c r="C66" s="92"/>
+      <c r="D66" s="92"/>
+      <c r="E66" s="92"/>
       <c r="F66" s="37" t="s">
         <v>14</v>
       </c>
@@ -4790,13 +4811,13 @@
       <c r="AL67" s="20"/>
     </row>
     <row r="68" spans="1:38" ht="12" customHeight="1">
-      <c r="A68" s="92">
+      <c r="A68" s="93">
         <v>1</v>
       </c>
-      <c r="B68" s="94"/>
-      <c r="C68" s="94"/>
-      <c r="D68" s="94"/>
-      <c r="E68" s="94"/>
+      <c r="B68" s="91"/>
+      <c r="C68" s="91"/>
+      <c r="D68" s="91"/>
+      <c r="E68" s="91"/>
       <c r="F68" s="21" t="s">
         <v>13</v>
       </c>
@@ -4834,11 +4855,11 @@
       <c r="AL68" s="27"/>
     </row>
     <row r="69" spans="1:38" ht="12" customHeight="1">
-      <c r="A69" s="93"/>
-      <c r="B69" s="93"/>
-      <c r="C69" s="93"/>
-      <c r="D69" s="93"/>
-      <c r="E69" s="93"/>
+      <c r="A69" s="92"/>
+      <c r="B69" s="92"/>
+      <c r="C69" s="92"/>
+      <c r="D69" s="92"/>
+      <c r="E69" s="92"/>
       <c r="F69" s="28" t="s">
         <v>14</v>
       </c>
@@ -4876,13 +4897,13 @@
       <c r="AL69" s="32"/>
     </row>
     <row r="70" spans="1:38" ht="12" customHeight="1">
-      <c r="A70" s="92">
+      <c r="A70" s="93">
         <v>2</v>
       </c>
-      <c r="B70" s="94"/>
-      <c r="C70" s="94"/>
-      <c r="D70" s="94"/>
-      <c r="E70" s="94"/>
+      <c r="B70" s="91"/>
+      <c r="C70" s="91"/>
+      <c r="D70" s="91"/>
+      <c r="E70" s="91"/>
       <c r="F70" s="33" t="s">
         <v>13</v>
       </c>
@@ -4920,11 +4941,11 @@
       <c r="AL70" s="10"/>
     </row>
     <row r="71" spans="1:38" ht="12" customHeight="1">
-      <c r="A71" s="93"/>
-      <c r="B71" s="93"/>
-      <c r="C71" s="93"/>
-      <c r="D71" s="93"/>
-      <c r="E71" s="93"/>
+      <c r="A71" s="92"/>
+      <c r="B71" s="92"/>
+      <c r="C71" s="92"/>
+      <c r="D71" s="92"/>
+      <c r="E71" s="92"/>
       <c r="F71" s="37" t="s">
         <v>14</v>
       </c>
@@ -4962,13 +4983,13 @@
       <c r="AL71" s="41"/>
     </row>
     <row r="72" spans="1:38" ht="12" customHeight="1">
-      <c r="A72" s="92">
+      <c r="A72" s="93">
         <v>3</v>
       </c>
-      <c r="B72" s="94"/>
-      <c r="C72" s="94"/>
-      <c r="D72" s="94"/>
-      <c r="E72" s="94"/>
+      <c r="B72" s="91"/>
+      <c r="C72" s="91"/>
+      <c r="D72" s="91"/>
+      <c r="E72" s="91"/>
       <c r="F72" s="21" t="s">
         <v>13</v>
       </c>
@@ -5006,11 +5027,11 @@
       <c r="AL72" s="27"/>
     </row>
     <row r="73" spans="1:38" ht="12" customHeight="1">
-      <c r="A73" s="93"/>
-      <c r="B73" s="93"/>
-      <c r="C73" s="93"/>
-      <c r="D73" s="93"/>
-      <c r="E73" s="93"/>
+      <c r="A73" s="92"/>
+      <c r="B73" s="92"/>
+      <c r="C73" s="92"/>
+      <c r="D73" s="92"/>
+      <c r="E73" s="92"/>
       <c r="F73" s="42" t="s">
         <v>14</v>
       </c>
@@ -5048,13 +5069,13 @@
       <c r="AL73" s="32"/>
     </row>
     <row r="74" spans="1:38" ht="12" customHeight="1">
-      <c r="A74" s="92">
+      <c r="A74" s="93">
         <v>4</v>
       </c>
-      <c r="B74" s="94"/>
-      <c r="C74" s="94"/>
-      <c r="D74" s="94"/>
-      <c r="E74" s="94"/>
+      <c r="B74" s="91"/>
+      <c r="C74" s="91"/>
+      <c r="D74" s="91"/>
+      <c r="E74" s="91"/>
       <c r="F74" s="33" t="s">
         <v>13</v>
       </c>
@@ -5092,11 +5113,11 @@
       <c r="AL74" s="10"/>
     </row>
     <row r="75" spans="1:38" ht="12" customHeight="1">
-      <c r="A75" s="93"/>
-      <c r="B75" s="93"/>
-      <c r="C75" s="93"/>
-      <c r="D75" s="93"/>
-      <c r="E75" s="93"/>
+      <c r="A75" s="92"/>
+      <c r="B75" s="92"/>
+      <c r="C75" s="92"/>
+      <c r="D75" s="92"/>
+      <c r="E75" s="92"/>
       <c r="F75" s="37" t="s">
         <v>14</v>
       </c>
@@ -5134,13 +5155,13 @@
       <c r="AL75" s="41"/>
     </row>
     <row r="76" spans="1:38" ht="12" customHeight="1">
-      <c r="A76" s="92">
+      <c r="A76" s="93">
         <v>5</v>
       </c>
-      <c r="B76" s="94"/>
-      <c r="C76" s="94"/>
-      <c r="D76" s="94"/>
-      <c r="E76" s="94"/>
+      <c r="B76" s="91"/>
+      <c r="C76" s="91"/>
+      <c r="D76" s="91"/>
+      <c r="E76" s="91"/>
       <c r="F76" s="21" t="s">
         <v>13</v>
       </c>
@@ -5178,11 +5199,11 @@
       <c r="AL76" s="27"/>
     </row>
     <row r="77" spans="1:38" ht="12" customHeight="1">
-      <c r="A77" s="93"/>
-      <c r="B77" s="93"/>
-      <c r="C77" s="93"/>
-      <c r="D77" s="93"/>
-      <c r="E77" s="93"/>
+      <c r="A77" s="92"/>
+      <c r="B77" s="92"/>
+      <c r="C77" s="92"/>
+      <c r="D77" s="92"/>
+      <c r="E77" s="92"/>
       <c r="F77" s="42" t="s">
         <v>14</v>
       </c>
@@ -5220,13 +5241,13 @@
       <c r="AL77" s="46"/>
     </row>
     <row r="78" spans="1:38" ht="12" customHeight="1">
-      <c r="A78" s="92">
+      <c r="A78" s="93">
         <v>6</v>
       </c>
-      <c r="B78" s="94"/>
-      <c r="C78" s="94"/>
-      <c r="D78" s="94"/>
-      <c r="E78" s="94"/>
+      <c r="B78" s="91"/>
+      <c r="C78" s="91"/>
+      <c r="D78" s="91"/>
+      <c r="E78" s="91"/>
       <c r="F78" s="33" t="s">
         <v>13</v>
       </c>
@@ -5264,11 +5285,11 @@
       <c r="AL78" s="10"/>
     </row>
     <row r="79" spans="1:38" ht="12" customHeight="1">
-      <c r="A79" s="93"/>
-      <c r="B79" s="93"/>
-      <c r="C79" s="93"/>
-      <c r="D79" s="93"/>
-      <c r="E79" s="93"/>
+      <c r="A79" s="92"/>
+      <c r="B79" s="92"/>
+      <c r="C79" s="92"/>
+      <c r="D79" s="92"/>
+      <c r="E79" s="92"/>
       <c r="F79" s="37" t="s">
         <v>14</v>
       </c>
@@ -5346,13 +5367,13 @@
       <c r="AL80" s="20"/>
     </row>
     <row r="81" spans="1:38" ht="12" customHeight="1">
-      <c r="A81" s="92">
+      <c r="A81" s="93">
         <v>1</v>
       </c>
-      <c r="B81" s="94"/>
-      <c r="C81" s="94"/>
-      <c r="D81" s="94"/>
-      <c r="E81" s="94"/>
+      <c r="B81" s="91"/>
+      <c r="C81" s="91"/>
+      <c r="D81" s="91"/>
+      <c r="E81" s="91"/>
       <c r="F81" s="21" t="s">
         <v>13</v>
       </c>
@@ -5390,11 +5411,11 @@
       <c r="AL81" s="27"/>
     </row>
     <row r="82" spans="1:38" ht="12" customHeight="1">
-      <c r="A82" s="93"/>
-      <c r="B82" s="93"/>
-      <c r="C82" s="93"/>
-      <c r="D82" s="93"/>
-      <c r="E82" s="93"/>
+      <c r="A82" s="92"/>
+      <c r="B82" s="92"/>
+      <c r="C82" s="92"/>
+      <c r="D82" s="92"/>
+      <c r="E82" s="92"/>
       <c r="F82" s="28" t="s">
         <v>14</v>
       </c>
@@ -5432,13 +5453,13 @@
       <c r="AL82" s="32"/>
     </row>
     <row r="83" spans="1:38" ht="12" customHeight="1">
-      <c r="A83" s="92">
+      <c r="A83" s="93">
         <v>2</v>
       </c>
-      <c r="B83" s="94"/>
-      <c r="C83" s="94"/>
-      <c r="D83" s="94"/>
-      <c r="E83" s="94"/>
+      <c r="B83" s="91"/>
+      <c r="C83" s="91"/>
+      <c r="D83" s="91"/>
+      <c r="E83" s="91"/>
       <c r="F83" s="33" t="s">
         <v>13</v>
       </c>
@@ -5476,11 +5497,11 @@
       <c r="AL83" s="10"/>
     </row>
     <row r="84" spans="1:38" ht="12" customHeight="1">
-      <c r="A84" s="93"/>
-      <c r="B84" s="93"/>
-      <c r="C84" s="93"/>
-      <c r="D84" s="93"/>
-      <c r="E84" s="93"/>
+      <c r="A84" s="92"/>
+      <c r="B84" s="92"/>
+      <c r="C84" s="92"/>
+      <c r="D84" s="92"/>
+      <c r="E84" s="92"/>
       <c r="F84" s="37" t="s">
         <v>14</v>
       </c>
@@ -5518,13 +5539,13 @@
       <c r="AL84" s="41"/>
     </row>
     <row r="85" spans="1:38" ht="12" customHeight="1">
-      <c r="A85" s="92">
+      <c r="A85" s="93">
         <v>3</v>
       </c>
-      <c r="B85" s="94"/>
-      <c r="C85" s="94"/>
-      <c r="D85" s="94"/>
-      <c r="E85" s="94"/>
+      <c r="B85" s="91"/>
+      <c r="C85" s="91"/>
+      <c r="D85" s="91"/>
+      <c r="E85" s="91"/>
       <c r="F85" s="21" t="s">
         <v>13</v>
       </c>
@@ -5562,11 +5583,11 @@
       <c r="AL85" s="27"/>
     </row>
     <row r="86" spans="1:38" ht="12" customHeight="1">
-      <c r="A86" s="93"/>
-      <c r="B86" s="93"/>
-      <c r="C86" s="93"/>
-      <c r="D86" s="93"/>
-      <c r="E86" s="93"/>
+      <c r="A86" s="92"/>
+      <c r="B86" s="92"/>
+      <c r="C86" s="92"/>
+      <c r="D86" s="92"/>
+      <c r="E86" s="92"/>
       <c r="F86" s="42" t="s">
         <v>14</v>
       </c>
@@ -5604,13 +5625,13 @@
       <c r="AL86" s="32"/>
     </row>
     <row r="87" spans="1:38" ht="12" customHeight="1">
-      <c r="A87" s="92">
+      <c r="A87" s="93">
         <v>4</v>
       </c>
-      <c r="B87" s="94"/>
-      <c r="C87" s="94"/>
-      <c r="D87" s="94"/>
-      <c r="E87" s="94"/>
+      <c r="B87" s="91"/>
+      <c r="C87" s="91"/>
+      <c r="D87" s="91"/>
+      <c r="E87" s="91"/>
       <c r="F87" s="33" t="s">
         <v>13</v>
       </c>
@@ -5648,11 +5669,11 @@
       <c r="AL87" s="10"/>
     </row>
     <row r="88" spans="1:38" ht="12" customHeight="1">
-      <c r="A88" s="93"/>
-      <c r="B88" s="93"/>
-      <c r="C88" s="93"/>
-      <c r="D88" s="93"/>
-      <c r="E88" s="93"/>
+      <c r="A88" s="92"/>
+      <c r="B88" s="92"/>
+      <c r="C88" s="92"/>
+      <c r="D88" s="92"/>
+      <c r="E88" s="92"/>
       <c r="F88" s="42" t="s">
         <v>14</v>
       </c>
@@ -42331,6 +42352,197 @@
     </row>
   </sheetData>
   <mergeCells count="215">
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="E52:E53"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="E57:E58"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="D74:D75"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="E74:E75"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C65:C66"/>
+    <mergeCell ref="D65:D66"/>
+    <mergeCell ref="E65:E66"/>
+    <mergeCell ref="D63:D64"/>
+    <mergeCell ref="E63:E64"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="D78:D79"/>
+    <mergeCell ref="E78:E79"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="D76:D77"/>
+    <mergeCell ref="E76:E77"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="C81:C82"/>
+    <mergeCell ref="D81:D82"/>
+    <mergeCell ref="E81:E82"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="C83:C84"/>
+    <mergeCell ref="D83:D84"/>
+    <mergeCell ref="E83:E84"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="E85:E86"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="U5:V5"/>
+    <mergeCell ref="W5:X5"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G3:AL4"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="U6:V6"/>
+    <mergeCell ref="W6:X6"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="Q5:R5"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="D59:D60"/>
+    <mergeCell ref="E59:E60"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="E61:E62"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="E68:E69"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="E70:E71"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E19:E20"/>
     <mergeCell ref="E50:E51"/>
     <mergeCell ref="A31:A32"/>
     <mergeCell ref="B31:B32"/>
@@ -42355,197 +42567,6 @@
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="B25:B26"/>
     <mergeCell ref="C25:C26"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="E68:E69"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="E70:E71"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="D61:D62"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="B59:B60"/>
-    <mergeCell ref="C59:C60"/>
-    <mergeCell ref="D59:D60"/>
-    <mergeCell ref="E59:E60"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="E61:E62"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="Q5:R5"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="W5:X5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G3:AL4"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="Q6:R6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="U6:V6"/>
-    <mergeCell ref="W6:X6"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="A81:A82"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="C81:C82"/>
-    <mergeCell ref="D81:D82"/>
-    <mergeCell ref="E81:E82"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="C83:C84"/>
-    <mergeCell ref="D83:D84"/>
-    <mergeCell ref="E83:E84"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="E85:E86"/>
-    <mergeCell ref="D78:D79"/>
-    <mergeCell ref="E78:E79"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="C76:C77"/>
-    <mergeCell ref="D76:D77"/>
-    <mergeCell ref="E76:E77"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="D57:D58"/>
-    <mergeCell ref="E57:E58"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="D74:D75"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="E74:E75"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C65:C66"/>
-    <mergeCell ref="D65:D66"/>
-    <mergeCell ref="E65:E66"/>
-    <mergeCell ref="D63:D64"/>
-    <mergeCell ref="E63:E64"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="E54:E55"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="E52:E53"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:D51"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <dataValidations count="1">
